--- a/cloudflare-deploy/public/library/branch/hq-kr.xlsx
+++ b/cloudflare-deploy/public/library/branch/hq-kr.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1835,6 +1835,60 @@
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>상담 → 레벨테스트 → 수강신청 링크 전달 순서로 안내하면 등록 전환이 매끄럽습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>🗂️</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>강사 통합 관리 개편 (명부 필터 · 그룹 · 상세 탭)</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>관리자 메뉴 강사 통합을 열어요(메뉴가 네 묶음으로 정리돼 있어요). → 명부 위 상태·그룹 드롭다운으로 원하는 강사만 걸러요. → 적용된 필터는 칩으로 표시되고, 칩을 지우면 해제돼요. → 강사를 누르면 프로필 / 급여 / 평가 탭 상세가 열려요. → 급여·평가 탭의 요약 숫자는 열 때 필요한 만큼만 불러옵니다.</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>강사가 많을수록 상태·그룹 필터가 큰 힘을 발휘해요. 자주 보는 조건은 필터를 걸어 두고 쓰세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>🌟</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>학부모 월간 성적표 (오각형) 발송</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>월간 리포트 화면을 열어요. → 학생 ID와 월을 넣고 레포트 보기를 눌러 미리봐요. → 오각형과 담임의 한마디를 확인하고, 필요하면 평가를 보완해요. → 주소에 ?uid=학생ID&amp;period=YYYY-MM 를 붙여 카카오톡 링크로 보냅니다.</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>상담 예약과 함께 성적표 링크를 미리 보내면 상담이 훨씬 매끄러워요.</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F241"/>
+  <dimension ref="A1:F269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4538,8 +4592,330 @@
       <c r="E241" s="33" t="n"/>
       <c r="F241" s="33" t="n"/>
     </row>
+    <row r="243" ht="26" customHeight="1">
+      <c r="A243" s="21" t="inlineStr">
+        <is>
+          <t>22  🗂️ 강사 통합 관리 개편 (명부 필터 · 그룹 · 상세 탭)  —  찾기 쉬운 명부 · 한눈에 보는 상세</t>
+        </is>
+      </c>
+      <c r="B243" s="22" t="n"/>
+      <c r="C243" s="22" t="n"/>
+      <c r="D243" s="22" t="n"/>
+      <c r="E243" s="22" t="n"/>
+      <c r="F243" s="22" t="n"/>
+    </row>
+    <row r="244" ht="42" customHeight="1">
+      <c r="A244" s="23" t="inlineStr">
+        <is>
+          <t>📖 강사 관리 화면이 찾기 쉽고 보기 편하게 정리됐어요. 흩어져 있던 메뉴를 네 묶음으로 그룹지어 사이드바에 담았고, 강사 명부 위에는 구분·상태·그룹 드롭다운 필터와 적용된 필터 칩이 생겼어요. 강사를 누르면 프로필·급여·평가 탭으로 나뉜 상세 화면이 열리고, 매니저 배지와 재직 상태(재직·휴직·퇴사) 가 한눈에 표시돼요.</t>
+        </is>
+      </c>
+      <c r="B244" s="24" t="n"/>
+      <c r="C244" s="24" t="n"/>
+      <c r="D244" s="24" t="n"/>
+      <c r="E244" s="24" t="n"/>
+      <c r="F244" s="24" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B245" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="30" customHeight="1">
+      <c r="A246" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B246" s="28" t="inlineStr">
+        <is>
+          <t>관리자 메뉴 강사 통합을 열어요(메뉴가 네 묶음으로 정리돼 있어요).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="30" customHeight="1">
+      <c r="A247" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B247" s="28" t="inlineStr">
+        <is>
+          <t>명부 위 상태·그룹 드롭다운으로 원하는 강사만 걸러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="30" customHeight="1">
+      <c r="A248" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B248" s="28" t="inlineStr">
+        <is>
+          <t>적용된 필터는 칩으로 표시되고, 칩을 지우면 해제돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="30" customHeight="1">
+      <c r="A249" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B249" s="28" t="inlineStr">
+        <is>
+          <t>강사를 누르면 프로필 / 급여 / 평가 탭 상세가 열려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="30" customHeight="1">
+      <c r="A250" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B250" s="28" t="inlineStr">
+        <is>
+          <t>급여·평가 탭의 요약 숫자는 열 때 필요한 만큼만 불러옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="24" customHeight="1">
+      <c r="A251" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B251" s="30" t="inlineStr">
+        <is>
+          <t>매니저는 배지로 구분되고, 재직 상태가 재직·휴직·퇴사 3가지로 표시돼요.</t>
+        </is>
+      </c>
+      <c r="C251" s="31" t="n"/>
+      <c r="D251" s="31" t="n"/>
+      <c r="E251" s="31" t="n"/>
+      <c r="F251" s="31" t="n"/>
+    </row>
+    <row r="252" ht="24" customHeight="1">
+      <c r="A252" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B252" s="30" t="inlineStr">
+        <is>
+          <t>이름이 비어도 아이디로 대체 표기돼 빈칸이 없어요.</t>
+        </is>
+      </c>
+      <c r="C252" s="31" t="n"/>
+      <c r="D252" s="31" t="n"/>
+      <c r="E252" s="31" t="n"/>
+      <c r="F252" s="31" t="n"/>
+    </row>
+    <row r="253" ht="24" customHeight="1">
+      <c r="A253" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B253" s="30" t="inlineStr">
+        <is>
+          <t>상세 탭은 기존 API를 재사용해 빠르게 뜨고, 화면은 한/영 병기예요.</t>
+        </is>
+      </c>
+      <c r="C253" s="31" t="n"/>
+      <c r="D253" s="31" t="n"/>
+      <c r="E253" s="31" t="n"/>
+      <c r="F253" s="31" t="n"/>
+    </row>
+    <row r="254" ht="24" customHeight="1">
+      <c r="A254" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B254" s="30" t="inlineStr">
+        <is>
+          <t>중복이던 급여 입구를 정리하고 버그 접수는 별도 시스템으로 옮겼어요.</t>
+        </is>
+      </c>
+      <c r="C254" s="31" t="n"/>
+      <c r="D254" s="31" t="n"/>
+      <c r="E254" s="31" t="n"/>
+      <c r="F254" s="31" t="n"/>
+    </row>
+    <row r="255" ht="26" customHeight="1">
+      <c r="A255" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 필터·상세 정리 작업이에요. 강사 등록·수정·삭제 기능 자체는 그대로예요.</t>
+        </is>
+      </c>
+      <c r="B255" s="35" t="n"/>
+      <c r="C255" s="35" t="n"/>
+      <c r="D255" s="35" t="n"/>
+      <c r="E255" s="35" t="n"/>
+      <c r="F255" s="35" t="n"/>
+    </row>
+    <row r="256" ht="30" customHeight="1">
+      <c r="A256" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 강사가 많을수록 상태·그룹 필터가 큰 힘을 발휘해요. 자주 보는 조건은 필터를 걸어 두고 쓰세요.</t>
+        </is>
+      </c>
+      <c r="B256" s="33" t="n"/>
+      <c r="C256" s="33" t="n"/>
+      <c r="D256" s="33" t="n"/>
+      <c r="E256" s="33" t="n"/>
+      <c r="F256" s="33" t="n"/>
+    </row>
+    <row r="258" ht="26" customHeight="1">
+      <c r="A258" s="21" t="inlineStr">
+        <is>
+          <t>23  🌟 학부모 월간 성적표 (오각형) 발송  —  5축 그래프 성적표를 미리보고 링크로</t>
+        </is>
+      </c>
+      <c r="B258" s="22" t="n"/>
+      <c r="C258" s="22" t="n"/>
+      <c r="D258" s="22" t="n"/>
+      <c r="E258" s="22" t="n"/>
+      <c r="F258" s="22" t="n"/>
+    </row>
+    <row r="259" ht="42" customHeight="1">
+      <c r="A259" s="23" t="inlineStr">
+        <is>
+          <t>📖 학부모에게 보내는 월간 성적표가 오각형 5축 그래프로 새로워졌어요. 발음·유창성 / 어휘 / 문장 구성력 / 수업 태도 / 참여도 를 한눈에 보여 주고, 출결·판단력·담임의 한마디가 함께 담깁니다. 관리자·교사는 학생 ID와 월을 넣어 미리보기한 뒤 카카오톡 링크로 보냅니다.</t>
+        </is>
+      </c>
+      <c r="B259" s="24" t="n"/>
+      <c r="C259" s="24" t="n"/>
+      <c r="D259" s="24" t="n"/>
+      <c r="E259" s="24" t="n"/>
+      <c r="F259" s="24" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B260" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="30" customHeight="1">
+      <c r="A261" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B261" s="28" t="inlineStr">
+        <is>
+          <t>월간 리포트 화면을 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="30" customHeight="1">
+      <c r="A262" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B262" s="28" t="inlineStr">
+        <is>
+          <t>학생 ID와 월을 넣고 레포트 보기를 눌러 미리봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="30" customHeight="1">
+      <c r="A263" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B263" s="28" t="inlineStr">
+        <is>
+          <t>오각형과 담임의 한마디를 확인하고, 필요하면 평가를 보완해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="30" customHeight="1">
+      <c r="A264" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B264" s="28" t="inlineStr">
+        <is>
+          <t>주소에 ?uid=학생ID&amp;period=YYYY-MM 를 붙여 카카오톡 링크로 보냅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="24" customHeight="1">
+      <c r="A265" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B265" s="30" t="inlineStr">
+        <is>
+          <t>실제 기록이 있는 축만 채워져 신뢰할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C265" s="31" t="n"/>
+      <c r="D265" s="31" t="n"/>
+      <c r="E265" s="31" t="n"/>
+      <c r="F265" s="31" t="n"/>
+    </row>
+    <row r="266" ht="24" customHeight="1">
+      <c r="A266" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B266" s="30" t="inlineStr">
+        <is>
+          <t>2개월 주기로 정리해 학부모 피로 없이 변화를 전달해요.</t>
+        </is>
+      </c>
+      <c r="C266" s="31" t="n"/>
+      <c r="D266" s="31" t="n"/>
+      <c r="E266" s="31" t="n"/>
+      <c r="F266" s="31" t="n"/>
+    </row>
+    <row r="267" ht="24" customHeight="1">
+      <c r="A267" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B267" s="30" t="inlineStr">
+        <is>
+          <t>인쇄/PDF 버튼으로 상담용 종이 성적표도 즉시 만들 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C267" s="31" t="n"/>
+      <c r="D267" s="31" t="n"/>
+      <c r="E267" s="31" t="n"/>
+      <c r="F267" s="31" t="n"/>
+    </row>
+    <row r="268" ht="26" customHeight="1">
+      <c r="A268" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 성적표 열람은 승인 게이트를 거쳐요. 관리자는 로그인 세션으로, 학부모는 발급된 링크(토큰)로만 열립니다.</t>
+        </is>
+      </c>
+      <c r="B268" s="35" t="n"/>
+      <c r="C268" s="35" t="n"/>
+      <c r="D268" s="35" t="n"/>
+      <c r="E268" s="35" t="n"/>
+      <c r="F268" s="35" t="n"/>
+    </row>
+    <row r="269" ht="30" customHeight="1">
+      <c r="A269" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 상담 예약과 함께 성적표 링크를 미리 보내면 상담이 훨씬 매끄러워요.</t>
+        </is>
+      </c>
+      <c r="B269" s="33" t="n"/>
+      <c r="C269" s="33" t="n"/>
+      <c r="D269" s="33" t="n"/>
+      <c r="E269" s="33" t="n"/>
+      <c r="F269" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="220">
+  <mergeCells count="246">
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="A205:F205"/>
     <mergeCell ref="B7:F7"/>
@@ -4547,9 +4923,11 @@
     <mergeCell ref="B200:F200"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B252:F252"/>
     <mergeCell ref="B209:F209"/>
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="A133:F133"/>
+    <mergeCell ref="B261:F261"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="B184:F184"/>
     <mergeCell ref="A3:F3"/>
@@ -4562,6 +4940,7 @@
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B253:F253"/>
     <mergeCell ref="A144:F144"/>
     <mergeCell ref="B231:F231"/>
     <mergeCell ref="B170:F170"/>
@@ -4571,6 +4950,7 @@
     <mergeCell ref="A81:F81"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B250:F250"/>
     <mergeCell ref="A121:F121"/>
     <mergeCell ref="B234:F234"/>
     <mergeCell ref="B34:F34"/>
@@ -4581,6 +4961,7 @@
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B186:F186"/>
     <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A258:F258"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="B118:F118"/>
     <mergeCell ref="B30:F30"/>
@@ -4594,10 +4975,12 @@
     <mergeCell ref="A241:F241"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B213:F213"/>
+    <mergeCell ref="B265:F265"/>
     <mergeCell ref="B160:F160"/>
     <mergeCell ref="A124:F124"/>
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B233:F233"/>
+    <mergeCell ref="A243:F243"/>
     <mergeCell ref="B224:F224"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B125:F125"/>
@@ -4614,8 +4997,10 @@
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B176:F176"/>
     <mergeCell ref="B219:F219"/>
+    <mergeCell ref="A269:F269"/>
     <mergeCell ref="B210:F210"/>
     <mergeCell ref="B120:F120"/>
+    <mergeCell ref="A259:F259"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="A141:F141"/>
     <mergeCell ref="B107:F107"/>
@@ -4629,6 +5014,7 @@
     <mergeCell ref="B148:F148"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B267:F267"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="B171:F171"/>
     <mergeCell ref="A230:F230"/>
@@ -4644,6 +5030,7 @@
     <mergeCell ref="B187:F187"/>
     <mergeCell ref="B68:F68"/>
     <mergeCell ref="B239:F239"/>
+    <mergeCell ref="B254:F254"/>
     <mergeCell ref="A216:F216"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A178:F178"/>
@@ -4652,6 +5039,7 @@
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B189:F189"/>
     <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B251:F251"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="B198:F198"/>
     <mergeCell ref="A153:F153"/>
@@ -4664,6 +5052,7 @@
     <mergeCell ref="A177:F177"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B218:F218"/>
+    <mergeCell ref="A268:F268"/>
     <mergeCell ref="A217:F217"/>
     <mergeCell ref="B232:F232"/>
     <mergeCell ref="A164:F164"/>
@@ -4675,6 +5064,7 @@
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A71:F71"/>
+    <mergeCell ref="B263:F263"/>
     <mergeCell ref="B152:F152"/>
     <mergeCell ref="B161:F161"/>
     <mergeCell ref="A181:F181"/>
@@ -4682,13 +5072,16 @@
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="A131:F131"/>
     <mergeCell ref="B145:F145"/>
+    <mergeCell ref="A244:F244"/>
     <mergeCell ref="B225:F225"/>
     <mergeCell ref="A165:F165"/>
     <mergeCell ref="A180:F180"/>
     <mergeCell ref="A63:F63"/>
+    <mergeCell ref="B249:F249"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B245:F245"/>
     <mergeCell ref="A229:F229"/>
     <mergeCell ref="A111:F111"/>
     <mergeCell ref="B128:F128"/>
@@ -4696,6 +5089,7 @@
     <mergeCell ref="B137:F137"/>
     <mergeCell ref="A143:F143"/>
     <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B260:F260"/>
     <mergeCell ref="B183:F183"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B139:F139"/>
@@ -4711,9 +5105,11 @@
     <mergeCell ref="B221:F221"/>
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B237:F237"/>
+    <mergeCell ref="A256:F256"/>
     <mergeCell ref="B138:F138"/>
     <mergeCell ref="B100:F100"/>
     <mergeCell ref="A193:F193"/>
+    <mergeCell ref="A255:F255"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="A12:F12"/>
@@ -4721,14 +5117,18 @@
     <mergeCell ref="B115:F115"/>
     <mergeCell ref="B140:F140"/>
     <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B264:F264"/>
     <mergeCell ref="B220:F220"/>
     <mergeCell ref="A104:F104"/>
+    <mergeCell ref="B247:F247"/>
     <mergeCell ref="A113:F113"/>
     <mergeCell ref="B130:F130"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="B117:F117"/>
+    <mergeCell ref="B248:F248"/>
+    <mergeCell ref="B262:F262"/>
     <mergeCell ref="B151:F151"/>
     <mergeCell ref="A194:F194"/>
     <mergeCell ref="B235:F235"/>
@@ -4742,6 +5142,7 @@
     <mergeCell ref="B196:F196"/>
     <mergeCell ref="B78:F78"/>
     <mergeCell ref="A155:F155"/>
+    <mergeCell ref="B246:F246"/>
     <mergeCell ref="B127:F127"/>
     <mergeCell ref="A201:F201"/>
     <mergeCell ref="B211:F211"/>
@@ -4752,6 +5153,7 @@
     <mergeCell ref="B95:F95"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B266:F266"/>
     <mergeCell ref="B169:F169"/>
     <mergeCell ref="B79:F79"/>
     <mergeCell ref="B32:F32"/>

--- a/cloudflare-deploy/public/library/branch/hq-kr.xlsx
+++ b/cloudflare-deploy/public/library/branch/hq-kr.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,6 +113,12 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000D9488"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="000D9488"/>
       <sz val="11"/>
     </font>
     <font>
@@ -181,7 +187,7 @@
       <sz val="11.5"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -216,6 +222,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF2FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -265,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -331,25 +342,25 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -358,10 +369,14 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -370,7 +385,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -379,26 +394,26 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -410,17 +425,17 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -709,6 +724,761 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="514350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>78</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>90</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>126</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>138</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>150</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2476500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>162</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>175</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="1152525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>188</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>202</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>216</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>228</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>241</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>255</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>270</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>286</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>300</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>315</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>330</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>343</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>355</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>368</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>381</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1227,7 +1997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1441,7 +2211,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>🧑‍🎓</t>
+          <t>🎓</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -1889,6 +2659,195 @@
       <c r="E26" s="15" t="inlineStr">
         <is>
           <t>상담 예약과 함께 성적표 링크를 미리 보내면 상담이 훨씬 매끄러워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>📅</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>학부모 주간 리포트 (재등록을 잇는 무기)</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 📅 학부모 주간 리포트를 열어요. → 학생 ID를 넣고 미리보기로 내용을 확인해요. → 필요하면 이 학부모에게 실제 발송으로 한 명에게만 테스트해요. → 발송 대상 집계로 지금 받을 수 있는 학생 수(전화번호 등록자)를 확인해요. → 최근 발송 로그로 실제로 나간 기록을 확인해요.</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>먼저 미리보기 → 한 명 테스트 발송까지만 해 보세요. 문구가 확정되면 그때 전체 스위치를 켜면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>🏠</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>홈 첫 화면 개편 (처음 온 학부모 · 기존 회원 자동 분리)</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>새 창(시크릿 모드)으로 홈 주소를 열어 비회원 화면을 확인해요. → 무료 체험 신청 · 강사 둘러보기 두 버튼이 크게 보이는지 봐요. → 로그인한 뒤 같은 화면을 열면 수업 입장 · AI와 친구하기로 바뀌어요. → 홍보물·문자에는 홈 주소 그대로 넣으면 됩니다 — 별도 랜딩페이지가 필요 없어요.</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>체험 신청 전환을 보고 싶다면 시크릿 창으로 홈에 들어가 보세요. 학부모가 처음 보는 화면이 그대로 나옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>관리자 화면이 훨씬 빨라졌어요</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>관리자 화면을 평소처럼 사용해요. → 메뉴·카드를 눌렀을 때 멈춤 없이 바로 열리는지 확인해요. → 느리게 느껴지면 브라우저에서 새로고침(Ctrl+F5) 을 한 번 해 주세요.</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>그래도 느리다면 브라우저 탭을 너무 많이 열어 두지 않았는지 확인해 보세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>🔎</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>학원 검색칸 (이름으로 바로 찾기)</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 학원 목록 화면을 열어요. → 목록 위 검색칸에 학원 이름 일부를 입력해요. → 입력하는 즉시 해당 학원만 목록에 남아요. → 검색칸을 비우면 전체 목록으로 돌아와요.</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>자주 확인하는 학원이 있다면 이름 두세 글자만 외워 두세요. 클릭 없이 바로 걸러집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>💳</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>신규 결제 화면 단계형 개편</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>학부모에게 신규 결제 화면을 안내해요. → 대상(키즈·일반 1:1·그룹·비즈니스·시험·기업)을 먼저 고르게 해요. → 고른 대상에 맞는 상품만 화면에 남아요. → 전체를 비교하고 싶어 하면 전체 요금표 보기를 눌러 주세요.</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>상담 전화에서 ‘어떤 걸 고를지 모르겠다’는 말이 나오면, 대상만 먼저 고르게 안내하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>📋</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>계정 없는 학부모용 샘플 평가표</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>상담 중 학부모에게 평가표 화면을 열어 보여 줘요. → 계정이 없어요 — 샘플 평가표 먼저 보기를 눌러요. → 5축 점수·강사 코멘트·AI 분석 구성을 함께 보며 설명해요. → ‘우리 아이 것도 이렇게 나옵니다’로 체험 신청을 연결해요.</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>상담 첫 3분에 샘플 평가표를 보여 주면 ‘무엇을 받게 되는지’가 명확해져 체험 전환이 올라갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>📞</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>상담 창구·운영시간 통일 (카카오 1순위)</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>문의하기 화면에서 카드 순서가 카카오 → 전화 인지 확인해요. → 학부모 안내 시 카카오 채널을 먼저 안내해요. → 운영시간은 10:00~23:00 (주말·공휴일 휴무) 로 통일해 안내해요.</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>필리핀 콜센터 번호가 필요하면 실번호를 알려 주세요 — 자리표시자였던 번호는 삭제된 상태입니다.</t>
         </is>
       </c>
     </row>
@@ -1906,7 +2865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F269"/>
+  <dimension ref="A1:F393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1915,6 +2874,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1948,1086 +2909,1074 @@
       <c r="E4" s="24" t="n"/>
       <c r="F4" s="24" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
         <is>
+          <t>🧭  1 아이디·비밀번호   ›   2 권한(지사)   ›   3 ‘비밀번호 찾기’   ›   4 권한 범위</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="27" t="n">
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>아이디·비밀번호로 로그인해요. (카카오·네이버·구글도 가능)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="27" t="n">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>로그인하면 권한(지사) 에 맞는 메뉴·데이터가 자동으로 적용돼요.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="27" t="n">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>비밀번호를 잊었으면 ‘비밀번호 찾기’로 재설정해요.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="27" t="n">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>직원에게는 권한 범위를 나눠 부여할 수 있어요.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>내 지사·산하 대리점 데이터만 보여요.</t>
         </is>
       </c>
-      <c r="C10" s="31" t="n"/>
-      <c r="D10" s="31" t="n"/>
-      <c r="E10" s="31" t="n"/>
-      <c r="F10" s="31" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="C11" s="33" t="n"/>
+      <c r="D11" s="33" t="n"/>
+      <c r="E11" s="33" t="n"/>
+      <c r="F11" s="33" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>안전한 내 PC에서만 ‘아이디 저장’을 켜세요.</t>
         </is>
       </c>
-      <c r="C11" s="31" t="n"/>
-      <c r="D11" s="31" t="n"/>
-      <c r="E11" s="31" t="n"/>
-      <c r="F11" s="31" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 공용 PC에서는 자동 로그인을 끄고 사용 후 꼭 로그아웃하세요.</t>
-        </is>
-      </c>
-      <c r="B12" s="33" t="n"/>
       <c r="C12" s="33" t="n"/>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n"/>
     </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 공용 PC에서는 자동 로그인을 끄고 사용 후 꼭 로그아웃하세요.</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>02  👤 마이페이지 &amp; 관리자 대시보드  —  마이페이지에서 관리 화면 열기</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>📖 지사 운영은 ‘마이페이지’에서 시작해요. 로그인 후 마이페이지의 메뉴 중 📊 ‘관리자’ 버튼을 누르면 우리 지사 범위의 관리자(운영) 대시보드로 들어가, 매출·재원·대리점·정산을 관리할 수 있어요.</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="24" t="n"/>
-      <c r="E15" s="24" t="n"/>
-      <c r="F15" s="24" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 ‘👤 마이페이지’   ›   2 📊 ‘관리자’   ›   3 관리자 대시보드   ›   4 마이페이지에는 연기/변경…   ›   5 EN</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="26" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="27" t="n">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>로그인 후 화면에서 ‘👤 마이페이지’를 열어요.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="27" t="n">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>마이페이지 메뉴에서 📊 ‘관리자’ 버튼을 눌러요. (관리자 대시보드로 이동)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="27" t="n">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>관리자 대시보드에서 우리 지사 매출·재원·출석·산하 대리점을 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="27" t="n">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="28" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>마이페이지에는 연기/변경·신규상담·전체메뉴·수업 진단 등도 함께 있어요.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="27" t="n">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>글자가 영어로 보이면 EN 버튼으로 한국어로 바꿔요.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="29" t="inlineStr">
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>‘관리자’ 버튼 하나로 바로 운영 대시보드에 들어가요.</t>
         </is>
       </c>
-      <c r="C22" s="31" t="n"/>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="31" t="n"/>
-      <c r="F22" s="31" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>대시보드 데이터는 모두 ‘우리 지사 범위’로 자동 집계돼요.</t>
         </is>
       </c>
-      <c r="C23" s="31" t="n"/>
-      <c r="D23" s="31" t="n"/>
-      <c r="E23" s="31" t="n"/>
-      <c r="F23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="C25" s="33" t="n"/>
+      <c r="D25" s="33" t="n"/>
+      <c r="E25" s="33" t="n"/>
+      <c r="F25" s="33" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>권한(지사)에 따라 보이는 메뉴·데이터가 자동으로 정해져요.</t>
         </is>
       </c>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 마이페이지·관리자 대시보드 모두 로그인한 지사 계정의 권한 범위 안에서만 열려요.</t>
-        </is>
-      </c>
-      <c r="B25" s="35" t="n"/>
-      <c r="C25" s="35" t="n"/>
-      <c r="D25" s="35" t="n"/>
-      <c r="E25" s="35" t="n"/>
-      <c r="F25" s="35" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 매일 마이페이지 → 관리자 대시보드 순서로 지사 지표를 5분만 점검하세요.</t>
-        </is>
-      </c>
-      <c r="B26" s="33" t="n"/>
       <c r="C26" s="33" t="n"/>
       <c r="D26" s="33" t="n"/>
       <c r="E26" s="33" t="n"/>
       <c r="F26" s="33" t="n"/>
     </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 마이페이지·관리자 대시보드 모두 로그인한 지사 계정의 권한 범위 안에서만 열려요.</t>
+        </is>
+      </c>
+      <c r="B27" s="37" t="n"/>
+      <c r="C27" s="37" t="n"/>
+      <c r="D27" s="37" t="n"/>
+      <c r="E27" s="37" t="n"/>
+      <c r="F27" s="37" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 매일 마이페이지 → 관리자 대시보드 순서로 지사 지표를 5분만 점검하세요.</t>
+        </is>
+      </c>
+      <c r="B28" s="35" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="35" t="n"/>
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="35" t="n"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>03  🏠 지사 대시보드  —  우리 지사 현황 한눈에</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="22" t="n"/>
-      <c r="F28" s="22" t="n"/>
-    </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>📖 로그인하면 우리 지사의 매출·재원생·출석률과 산하 대리점 현황이 카드로 정리돼 있어요. 상단 검색창에 단어만 넣어도 원하는 기능으로 바로 이동해요.</t>
         </is>
       </c>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="24" t="n"/>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="24" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 오늘 매출·재원생·출석률   ›   2 카테고리 카드   ›   3 기능 검색창   ›   4 AI 인사이트</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="27" t="n">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="28" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>상단에서 오늘 매출·재원생·출석률(우리 지사 합계)을 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="27" t="n">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="28" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>카테고리 카드(대리점·강사·회계·학생·콘텐츠)에서 기능을 눌러요.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="27" t="n">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="28" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>기능 검색창에 단어를 넣으면 바로 이동해요.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="27" t="n">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B34" s="28" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>AI 인사이트가 우리 지사 상태를 요약해줘요.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="29" t="inlineStr">
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B35" s="30" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>숫자는 모두 ‘우리 지사 범위’로 자동 집계돼요.</t>
         </is>
       </c>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="29" t="inlineStr">
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B39" s="32" t="inlineStr">
         <is>
           <t>찾는 기능이 안 보이면 검색이 가장 빨라요.</t>
         </is>
       </c>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="32" t="inlineStr">
+      <c r="C39" s="33" t="n"/>
+      <c r="D39" s="33" t="n"/>
+      <c r="E39" s="33" t="n"/>
+      <c r="F39" s="33" t="n"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 매일 아침 지사 지표 5분 점검으로 이상 신호를 빨리 잡으세요.</t>
         </is>
       </c>
-      <c r="B37" s="33" t="n"/>
-      <c r="C37" s="33" t="n"/>
-      <c r="D37" s="33" t="n"/>
-      <c r="E37" s="33" t="n"/>
-      <c r="F37" s="33" t="n"/>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="B40" s="35" t="n"/>
+      <c r="C40" s="35" t="n"/>
+      <c r="D40" s="35" t="n"/>
+      <c r="E40" s="35" t="n"/>
+      <c r="F40" s="35" t="n"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>04  🤖 AI 운영비서 활용  —  말·글로 조회·처리</t>
         </is>
       </c>
-      <c r="B39" s="22" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="22" t="n"/>
-      <c r="F39" s="22" t="n"/>
-    </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="B42" s="22" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>📖 검색/마이크에 말하거나 글로 시키면 AI가 우리 지사 범위에서 숫자를 조회하거나 화면을 열어줘요. 중요한 처리는 먼저 확인하고, 권한이 있는 일만 실행해요.</t>
         </is>
       </c>
-      <c r="B40" s="24" t="n"/>
-      <c r="C40" s="24" t="n"/>
-      <c r="D40" s="24" t="n"/>
-      <c r="E40" s="24" t="n"/>
-      <c r="F40" s="24" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="B43" s="24" t="n"/>
+      <c r="C43" s="24" t="n"/>
+      <c r="D43" s="24" t="n"/>
+      <c r="E43" s="24" t="n"/>
+      <c r="F43" s="24" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 검색/마이크   ›   2 숫자를 조회   ›   3 ‘할까요?’로 먼저 확인   ›   4 권한이 있는 일만</t>
+        </is>
+      </c>
+      <c r="B44" s="26" t="n"/>
+      <c r="C44" s="26" t="n"/>
+      <c r="D44" s="26" t="n"/>
+      <c r="E44" s="26" t="n"/>
+      <c r="F44" s="26" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="27" t="n">
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B42" s="28" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>가운데 검색/마이크에 말하거나 입력해요. 예) “이번 달 지사 매출 어때?”</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="27" t="n">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B43" s="28" t="inlineStr">
+      <c r="B47" s="30" t="inlineStr">
         <is>
           <t>AI가 숫자를 조회하거나 화면을 열어줘요. 예) “대리점 목록 열어줘”</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="27" t="n">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B44" s="28" t="inlineStr">
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>중요한 처리는 ‘할까요?’로 먼저 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="27" t="n">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B45" s="28" t="inlineStr">
+      <c r="B49" s="30" t="inlineStr">
         <is>
           <t>권한이 있는 일만 비서가 실행해요.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="29" t="inlineStr">
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B46" s="30" t="inlineStr">
+      <c r="B50" s="32" t="inlineStr">
         <is>
           <t>바쁜 시간엔 말로 시키는 게 훨씬 빨라요.</t>
         </is>
       </c>
-      <c r="C46" s="31" t="n"/>
-      <c r="D46" s="31" t="n"/>
-      <c r="E46" s="31" t="n"/>
-      <c r="F46" s="31" t="n"/>
-    </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="C50" s="33" t="n"/>
+      <c r="D50" s="33" t="n"/>
+      <c r="E50" s="33" t="n"/>
+      <c r="F50" s="33" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B47" s="30" t="inlineStr">
+      <c r="B51" s="32" t="inlineStr">
         <is>
           <t>조회 결과도 우리 지사 범위로 한정돼요.</t>
         </is>
       </c>
-      <c r="C47" s="31" t="n"/>
-      <c r="D47" s="31" t="n"/>
-      <c r="E47" s="31" t="n"/>
-      <c r="F47" s="31" t="n"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="32" t="inlineStr">
+      <c r="C51" s="33" t="n"/>
+      <c r="D51" s="33" t="n"/>
+      <c r="E51" s="33" t="n"/>
+      <c r="F51" s="33" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · ‘○○ 보여줘/열어줘’ 한마디면 원하는 화면으로 바로 이동해요.</t>
         </is>
       </c>
-      <c r="B48" s="33" t="n"/>
-      <c r="C48" s="33" t="n"/>
-      <c r="D48" s="33" t="n"/>
-      <c r="E48" s="33" t="n"/>
-      <c r="F48" s="33" t="n"/>
-    </row>
-    <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="21" t="inlineStr">
+      <c r="B52" s="35" t="n"/>
+      <c r="C52" s="35" t="n"/>
+      <c r="D52" s="35" t="n"/>
+      <c r="E52" s="35" t="n"/>
+      <c r="F52" s="35" t="n"/>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>05  🏬 산하 대리점 관리  —  대리점 목록·성과·모집</t>
         </is>
       </c>
-      <c r="B50" s="22" t="n"/>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="22" t="n"/>
-      <c r="E50" s="22" t="n"/>
-      <c r="F50" s="22" t="n"/>
-    </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="23" t="inlineStr">
+      <c r="B54" s="22" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="22" t="n"/>
+      <c r="F54" s="22" t="n"/>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t>📖 우리 지사에 속한 대리점들을 목록으로 관리하고, 각 대리점의 재원생·매출·성과를 비교해요. 신규 대리점 모집·온보딩도 여기서 챙겨요.</t>
         </is>
       </c>
-      <c r="B51" s="24" t="n"/>
-      <c r="C51" s="24" t="n"/>
-      <c r="D51" s="24" t="n"/>
-      <c r="E51" s="24" t="n"/>
-      <c r="F51" s="24" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="25" t="inlineStr">
+      <c r="B55" s="24" t="n"/>
+      <c r="C55" s="24" t="n"/>
+      <c r="D55" s="24" t="n"/>
+      <c r="E55" s="24" t="n"/>
+      <c r="F55" s="24" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 대리점 목록   ›   2 지원 우선순위   ›   3 신규 대리점 모집·온보딩   ›   4 목표·인센티브</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="n"/>
+      <c r="C56" s="26" t="n"/>
+      <c r="D56" s="26" t="n"/>
+      <c r="E56" s="26" t="n"/>
+      <c r="F56" s="26" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B52" s="26" t="inlineStr">
+      <c r="B57" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="27" t="n">
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B53" s="28" t="inlineStr">
+      <c r="B58" s="30" t="inlineStr">
         <is>
           <t>대리점 목록에서 각 대리점의 재원생·매출·활동을 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="27" t="n">
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B54" s="28" t="inlineStr">
+      <c r="B59" s="30" t="inlineStr">
         <is>
           <t>성과가 좋은/부진한 대리점을 비교해 지원 우선순위를 정해요.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="27" t="n">
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B55" s="28" t="inlineStr">
+      <c r="B60" s="30" t="inlineStr">
         <is>
           <t>신규 대리점 모집·온보딩 진행 상황을 관리해요.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="27" t="n">
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B56" s="28" t="inlineStr">
+      <c r="B61" s="30" t="inlineStr">
         <is>
           <t>필요하면 대리점별 목표·인센티브를 설정해요.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="29" t="inlineStr">
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B57" s="30" t="inlineStr">
+      <c r="B62" s="32" t="inlineStr">
         <is>
           <t>성과 편차가 큰 대리점은 코칭·지원을 연결하세요.</t>
         </is>
       </c>
-      <c r="C57" s="31" t="n"/>
-      <c r="D57" s="31" t="n"/>
-      <c r="E57" s="31" t="n"/>
-      <c r="F57" s="31" t="n"/>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="29" t="inlineStr">
+      <c r="C62" s="33" t="n"/>
+      <c r="D62" s="33" t="n"/>
+      <c r="E62" s="33" t="n"/>
+      <c r="F62" s="33" t="n"/>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B58" s="30" t="inlineStr">
+      <c r="B63" s="32" t="inlineStr">
         <is>
           <t>우수 대리점의 방식을 다른 대리점에 공유하면 좋아요.</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-    </row>
-    <row r="59" ht="26" customHeight="1">
-      <c r="A59" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 대리점 데이터는 해당 대리점 권한에서도 각자 관리돼요. 지사는 전체를 조망해요.</t>
-        </is>
-      </c>
-      <c r="B59" s="35" t="n"/>
-      <c r="C59" s="35" t="n"/>
-      <c r="D59" s="35" t="n"/>
-      <c r="E59" s="35" t="n"/>
-      <c r="F59" s="35" t="n"/>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="32" t="inlineStr">
+      <c r="C63" s="33" t="n"/>
+      <c r="D63" s="33" t="n"/>
+      <c r="E63" s="33" t="n"/>
+      <c r="F63" s="33" t="n"/>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 대리점 데이터는 해당 대리점 권한에서도 각자 관리돼요. 지사는 전체를 조망해요.</t>
+        </is>
+      </c>
+      <c r="B64" s="37" t="n"/>
+      <c r="C64" s="37" t="n"/>
+      <c r="D64" s="37" t="n"/>
+      <c r="E64" s="37" t="n"/>
+      <c r="F64" s="37" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 월초에 대리점별 성과 리포트를 공유하면 파트너 동기부여가 커져요.</t>
         </is>
       </c>
-      <c r="B60" s="33" t="n"/>
-      <c r="C60" s="33" t="n"/>
-      <c r="D60" s="33" t="n"/>
-      <c r="E60" s="33" t="n"/>
-      <c r="F60" s="33" t="n"/>
-    </row>
-    <row r="62" ht="26" customHeight="1">
-      <c r="A62" s="21" t="inlineStr">
+      <c r="B65" s="35" t="n"/>
+      <c r="C65" s="35" t="n"/>
+      <c r="D65" s="35" t="n"/>
+      <c r="E65" s="35" t="n"/>
+      <c r="F65" s="35" t="n"/>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="21" t="inlineStr">
         <is>
           <t>06  🌳 지사 정산 (수령·배분)  —  본사→지사→대리점</t>
         </is>
       </c>
-      <c r="B62" s="22" t="n"/>
-      <c r="C62" s="22" t="n"/>
-      <c r="D62" s="22" t="n"/>
-      <c r="E62" s="22" t="n"/>
-      <c r="F62" s="22" t="n"/>
-    </row>
-    <row r="63" ht="42" customHeight="1">
-      <c r="A63" s="23" t="inlineStr">
+      <c r="B67" s="22" t="n"/>
+      <c r="C67" s="22" t="n"/>
+      <c r="D67" s="22" t="n"/>
+      <c r="E67" s="22" t="n"/>
+      <c r="F67" s="22" t="n"/>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="23" t="inlineStr">
         <is>
           <t>📖 본사에서 지사로 내려오는 정산을 수령하고, 지사에서 산하 대리점으로 배분되는 금액을 확인해요. 조직 트리 구조를 따라 매출·수수료가 자동 계산돼요.</t>
         </is>
       </c>
-      <c r="B63" s="24" t="n"/>
-      <c r="C63" s="24" t="n"/>
-      <c r="D63" s="24" t="n"/>
-      <c r="E63" s="24" t="n"/>
-      <c r="F63" s="24" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="25" t="inlineStr">
+      <c r="B68" s="24" t="n"/>
+      <c r="C68" s="24" t="n"/>
+      <c r="D68" s="24" t="n"/>
+      <c r="E68" s="24" t="n"/>
+      <c r="F68" s="24" t="n"/>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 본사→지사 정산   ›   2 지사→대리점 배분   ›   3 월간 리포트   ›   4 이상 항목이 있으면 내역…</t>
+        </is>
+      </c>
+      <c r="B69" s="26" t="n"/>
+      <c r="C69" s="26" t="n"/>
+      <c r="D69" s="26" t="n"/>
+      <c r="E69" s="26" t="n"/>
+      <c r="F69" s="26" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B64" s="26" t="inlineStr">
+      <c r="B70" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="27" t="n">
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B65" s="28" t="inlineStr">
+      <c r="B71" s="30" t="inlineStr">
         <is>
           <t>본사→지사 정산(수령액)을 월별로 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="27" t="n">
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B66" s="28" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>지사→대리점 배분이 트리 구조로 자동 계산돼요.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="27" t="n">
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B67" s="28" t="inlineStr">
+      <c r="B73" s="30" t="inlineStr">
         <is>
           <t>정산 내역을 월간 리포트로 확인·저장(PDF)해요.</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="27" t="n">
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B68" s="28" t="inlineStr">
+      <c r="B74" s="30" t="inlineStr">
         <is>
           <t>이상 항목이 있으면 내역을 조회해 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B75" s="32" t="inlineStr">
         <is>
           <t>정산은 조직 트리(본사·지사·대리점)를 따라 자동 계산돼요.</t>
         </is>
       </c>
-      <c r="C69" s="31" t="n"/>
-      <c r="D69" s="31" t="n"/>
-      <c r="E69" s="31" t="n"/>
-      <c r="F69" s="31" t="n"/>
-    </row>
-    <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="29" t="inlineStr">
+      <c r="C75" s="33" t="n"/>
+      <c r="D75" s="33" t="n"/>
+      <c r="E75" s="33" t="n"/>
+      <c r="F75" s="33" t="n"/>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B70" s="30" t="inlineStr">
+      <c r="B76" s="32" t="inlineStr">
         <is>
           <t>월초 정산 리포트 배포로 대리점 신뢰가 올라가요.</t>
         </is>
       </c>
-      <c r="C70" s="31" t="n"/>
-      <c r="D70" s="31" t="n"/>
-      <c r="E70" s="31" t="n"/>
-      <c r="F70" s="31" t="n"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="32" t="inlineStr">
+      <c r="C76" s="33" t="n"/>
+      <c r="D76" s="33" t="n"/>
+      <c r="E76" s="33" t="n"/>
+      <c r="F76" s="33" t="n"/>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 정산 기준(수수료율·시기)을 대리점에 미리 공지하면 분쟁이 줄어요.</t>
         </is>
       </c>
-      <c r="B71" s="33" t="n"/>
-      <c r="C71" s="33" t="n"/>
-      <c r="D71" s="33" t="n"/>
-      <c r="E71" s="33" t="n"/>
-      <c r="F71" s="33" t="n"/>
-    </row>
-    <row r="73" ht="26" customHeight="1">
-      <c r="A73" s="21" t="inlineStr">
-        <is>
-          <t>07  🧑‍🎓 학생·학부모 현황  —  지사 범위 재원·출결·성적</t>
-        </is>
-      </c>
-      <c r="B73" s="22" t="n"/>
-      <c r="C73" s="22" t="n"/>
-      <c r="D73" s="22" t="n"/>
-      <c r="E73" s="22" t="n"/>
-      <c r="F73" s="22" t="n"/>
-    </row>
-    <row r="74" ht="42" customHeight="1">
-      <c r="A74" s="23" t="inlineStr">
+      <c r="B77" s="35" t="n"/>
+      <c r="C77" s="35" t="n"/>
+      <c r="D77" s="35" t="n"/>
+      <c r="E77" s="35" t="n"/>
+      <c r="F77" s="35" t="n"/>
+    </row>
+    <row r="79" ht="26" customHeight="1">
+      <c r="A79" s="21" t="inlineStr">
+        <is>
+          <t>07  🎓 학생·학부모 현황  —  지사 범위 재원·출결·성적</t>
+        </is>
+      </c>
+      <c r="B79" s="22" t="n"/>
+      <c r="C79" s="22" t="n"/>
+      <c r="D79" s="22" t="n"/>
+      <c r="E79" s="22" t="n"/>
+      <c r="F79" s="22" t="n"/>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="23" t="inlineStr">
         <is>
           <t>📖 우리 지사에 속한 학생 현황(재원·출결·성적)을 확인해요. 대리점별로 나눠 보거나 지사 전체로 합산해 볼 수 있어요.</t>
         </is>
       </c>
-      <c r="B74" s="24" t="n"/>
-      <c r="C74" s="24" t="n"/>
-      <c r="D74" s="24" t="n"/>
-      <c r="E74" s="24" t="n"/>
-      <c r="F74" s="24" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="25" t="inlineStr">
+      <c r="B80" s="24" t="n"/>
+      <c r="C80" s="24" t="n"/>
+      <c r="D80" s="24" t="n"/>
+      <c r="E80" s="24" t="n"/>
+      <c r="F80" s="24" t="n"/>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 학생/학부모   ›   2 대리점별·전체   ›   3 관리가 필요한 학생·대리…</t>
+        </is>
+      </c>
+      <c r="B81" s="26" t="n"/>
+      <c r="C81" s="26" t="n"/>
+      <c r="D81" s="26" t="n"/>
+      <c r="E81" s="26" t="n"/>
+      <c r="F81" s="26" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B75" s="26" t="inlineStr">
+      <c r="B82" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="27" t="n">
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B76" s="28" t="inlineStr">
+      <c r="B83" s="30" t="inlineStr">
         <is>
           <t>학생/학부모에서 지사 범위 재원생을 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="27" t="n">
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B77" s="28" t="inlineStr">
+      <c r="B84" s="30" t="inlineStr">
         <is>
           <t>대리점별·전체 출결·성적을 비교해요.</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="27" t="n">
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B78" s="28" t="inlineStr">
+      <c r="B85" s="30" t="inlineStr">
         <is>
           <t>관리가 필요한 학생·대리점을 표시해요.</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="29" t="inlineStr">
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B79" s="30" t="inlineStr">
+      <c r="B86" s="32" t="inlineStr">
         <is>
           <t>학생 목록은 실제 회원 데이터와 연동돼 있어요.</t>
         </is>
       </c>
-      <c r="C79" s="31" t="n"/>
-      <c r="D79" s="31" t="n"/>
-      <c r="E79" s="31" t="n"/>
-      <c r="F79" s="31" t="n"/>
-    </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="29" t="inlineStr">
+      <c r="C86" s="33" t="n"/>
+      <c r="D86" s="33" t="n"/>
+      <c r="E86" s="33" t="n"/>
+      <c r="F86" s="33" t="n"/>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B80" s="30" t="inlineStr">
+      <c r="B87" s="32" t="inlineStr">
         <is>
           <t>이탈위험 학생은 리텐션 센터와 연결돼요.</t>
         </is>
       </c>
-      <c r="C80" s="31" t="n"/>
-      <c r="D80" s="31" t="n"/>
-      <c r="E80" s="31" t="n"/>
-      <c r="F80" s="31" t="n"/>
-    </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="32" t="inlineStr">
+      <c r="C87" s="33" t="n"/>
+      <c r="D87" s="33" t="n"/>
+      <c r="E87" s="33" t="n"/>
+      <c r="F87" s="33" t="n"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 출석·재원 추이가 꺾이는 대리점을 빨리 찾아 지원하세요.</t>
         </is>
       </c>
-      <c r="B81" s="33" t="n"/>
-      <c r="C81" s="33" t="n"/>
-      <c r="D81" s="33" t="n"/>
-      <c r="E81" s="33" t="n"/>
-      <c r="F81" s="33" t="n"/>
-    </row>
-    <row r="83" ht="26" customHeight="1">
-      <c r="A83" s="21" t="inlineStr">
+      <c r="B88" s="35" t="n"/>
+      <c r="C88" s="35" t="n"/>
+      <c r="D88" s="35" t="n"/>
+      <c r="E88" s="35" t="n"/>
+      <c r="F88" s="35" t="n"/>
+    </row>
+    <row r="89" ht="18" customHeight="1"/>
+    <row r="91" ht="26" customHeight="1">
+      <c r="A91" s="21" t="inlineStr">
         <is>
           <t>08  💳 결제·미납·환불 (지사)  —  지사 범위 회계</t>
         </is>
       </c>
-      <c r="B83" s="22" t="n"/>
-      <c r="C83" s="22" t="n"/>
-      <c r="D83" s="22" t="n"/>
-      <c r="E83" s="22" t="n"/>
-      <c r="F83" s="22" t="n"/>
-    </row>
-    <row r="84" ht="42" customHeight="1">
-      <c r="A84" s="23" t="inlineStr">
+      <c r="B91" s="22" t="n"/>
+      <c r="C91" s="22" t="n"/>
+      <c r="D91" s="22" t="n"/>
+      <c r="E91" s="22" t="n"/>
+      <c r="F91" s="22" t="n"/>
+    </row>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="23" t="inlineStr">
         <is>
           <t>📖 우리 지사 범위의 결제·미납·환불을 확인하고, 규정에 따라 자동 계산되는 금액을 점검해요. 대리점별 수납 현황도 함께 봐요.</t>
         </is>
       </c>
-      <c r="B84" s="24" t="n"/>
-      <c r="C84" s="24" t="n"/>
-      <c r="D84" s="24" t="n"/>
-      <c r="E84" s="24" t="n"/>
-      <c r="F84" s="24" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="25" t="inlineStr">
+      <c r="B92" s="24" t="n"/>
+      <c r="C92" s="24" t="n"/>
+      <c r="D92" s="24" t="n"/>
+      <c r="E92" s="24" t="n"/>
+      <c r="F92" s="24" t="n"/>
+    </row>
+    <row r="93" ht="24" customHeight="1">
+      <c r="A93" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 회계/포인트   ›   2 대리점별 수납률   ›   3 환불 규정표</t>
+        </is>
+      </c>
+      <c r="B93" s="26" t="n"/>
+      <c r="C93" s="26" t="n"/>
+      <c r="D93" s="26" t="n"/>
+      <c r="E93" s="26" t="n"/>
+      <c r="F93" s="26" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B85" s="26" t="inlineStr">
+      <c r="B94" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="27" t="n">
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B86" s="28" t="inlineStr">
+      <c r="B95" s="30" t="inlineStr">
         <is>
           <t>회계/포인트에서 지사 범위 결제·미납·환불을 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="27" t="n">
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B87" s="28" t="inlineStr">
+      <c r="B96" s="30" t="inlineStr">
         <is>
           <t>대리점별 수납률을 비교해요.</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="27" t="n">
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B88" s="28" t="inlineStr">
+      <c r="B97" s="30" t="inlineStr">
         <is>
           <t>환불 규정표에 따라 금액이 자동 계산돼요.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="24" customHeight="1">
-      <c r="A89" s="29" t="inlineStr">
+    <row r="98" ht="24" customHeight="1">
+      <c r="A98" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B89" s="30" t="inlineStr">
+      <c r="B98" s="32" t="inlineStr">
         <is>
           <t>미납이 많은 대리점은 알림·지원을 강화하세요.</t>
         </is>
       </c>
-      <c r="C89" s="31" t="n"/>
-      <c r="D89" s="31" t="n"/>
-      <c r="E89" s="31" t="n"/>
-      <c r="F89" s="31" t="n"/>
-    </row>
-    <row r="90" ht="24" customHeight="1">
-      <c r="A90" s="29" t="inlineStr">
+      <c r="C98" s="33" t="n"/>
+      <c r="D98" s="33" t="n"/>
+      <c r="E98" s="33" t="n"/>
+      <c r="F98" s="33" t="n"/>
+    </row>
+    <row r="99" ht="24" customHeight="1">
+      <c r="A99" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B90" s="30" t="inlineStr">
+      <c r="B99" s="32" t="inlineStr">
         <is>
           <t>할인 결제 환불은 정가 기준으로 재정산돼요.</t>
         </is>
       </c>
-      <c r="C90" s="31" t="n"/>
-      <c r="D90" s="31" t="n"/>
-      <c r="E90" s="31" t="n"/>
-      <c r="F90" s="31" t="n"/>
-    </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="32" t="inlineStr">
+      <c r="C99" s="33" t="n"/>
+      <c r="D99" s="33" t="n"/>
+      <c r="E99" s="33" t="n"/>
+      <c r="F99" s="33" t="n"/>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 수납률이 낮은 대리점에 알림 자동화를 안내하면 개선돼요.</t>
         </is>
       </c>
-      <c r="B91" s="33" t="n"/>
-      <c r="C91" s="33" t="n"/>
-      <c r="D91" s="33" t="n"/>
-      <c r="E91" s="33" t="n"/>
-      <c r="F91" s="33" t="n"/>
-    </row>
-    <row r="93" ht="26" customHeight="1">
-      <c r="A93" s="21" t="inlineStr">
-        <is>
-          <t>09  🧲 지사 리텐션 관리  —  이탈위험·전염·코칭</t>
-        </is>
-      </c>
-      <c r="B93" s="22" t="n"/>
-      <c r="C93" s="22" t="n"/>
-      <c r="D93" s="22" t="n"/>
-      <c r="E93" s="22" t="n"/>
-      <c r="F93" s="22" t="n"/>
-    </row>
-    <row r="94" ht="42" customHeight="1">
-      <c r="A94" s="23" t="inlineStr">
-        <is>
-          <t>📖 우리 지사·대리점에서 이탈 위험이 있는 학생을 미리 찾고, 가족·추천으로 이어지는 연쇄 이탈을 예방해요. 대리점·강사 코칭과도 연결돼요.</t>
-        </is>
-      </c>
-      <c r="B94" s="24" t="n"/>
-      <c r="C94" s="24" t="n"/>
-      <c r="D94" s="24" t="n"/>
-      <c r="E94" s="24" t="n"/>
-      <c r="F94" s="24" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="25" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="B95" s="26" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B96" s="28" t="inlineStr">
-        <is>
-          <t>이탈위험 그래프로 위험 학생·대리점을 찾아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B97" s="28" t="inlineStr">
-        <is>
-          <t>이탈 전염 관계망으로 연쇄 이탈을 예방해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B98" s="28" t="inlineStr">
-        <is>
-          <t>위험이 높은 곳에 알림톡·상담·코칭을 연결해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="24" customHeight="1">
-      <c r="A99" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B99" s="30" t="inlineStr">
-        <is>
-          <t>빨리 개입할수록 잔존율이 올라가요.</t>
-        </is>
-      </c>
-      <c r="C99" s="31" t="n"/>
-      <c r="D99" s="31" t="n"/>
-      <c r="E99" s="31" t="n"/>
-      <c r="F99" s="31" t="n"/>
-    </row>
-    <row r="100" ht="24" customHeight="1">
-      <c r="A100" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B100" s="30" t="inlineStr">
-        <is>
-          <t>대리점별 이탈 패턴을 비교해 지원하세요.</t>
-        </is>
-      </c>
-      <c r="C100" s="31" t="n"/>
-      <c r="D100" s="31" t="n"/>
-      <c r="E100" s="31" t="n"/>
-      <c r="F100" s="31" t="n"/>
-    </row>
-    <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 매주 위험 상위 대리점·학생만이라도 챙기면 이탈이 눈에 띄게 줄어요.</t>
-        </is>
-      </c>
-      <c r="B101" s="33" t="n"/>
-      <c r="C101" s="33" t="n"/>
-      <c r="D101" s="33" t="n"/>
-      <c r="E101" s="33" t="n"/>
-      <c r="F101" s="33" t="n"/>
-    </row>
+      <c r="B100" s="35" t="n"/>
+      <c r="C100" s="35" t="n"/>
+      <c r="D100" s="35" t="n"/>
+      <c r="E100" s="35" t="n"/>
+      <c r="F100" s="35" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1"/>
     <row r="103" ht="26" customHeight="1">
       <c r="A103" s="21" t="inlineStr">
         <is>
-          <t>10  📊 월간 리포트·성과 분석  —  지사·대리점 성과</t>
+          <t>09  🧲 지사 리텐션 관리  —  이탈위험·전염·코칭</t>
         </is>
       </c>
       <c r="B103" s="22" t="n"/>
@@ -3039,7 +3988,7 @@
     <row r="104" ht="42" customHeight="1">
       <c r="A104" s="23" t="inlineStr">
         <is>
-          <t>📖 지사와 산하 대리점의 성과를 월간 리포트로 정리해요. 매출·재원·출석·정산을 한눈에 보고, 인쇄·PDF로 저장해 공유해요.</t>
+          <t>📖 우리 지사·대리점에서 이탈 위험이 있는 학생을 미리 찾고, 가족·추천으로 이어지는 연쇄 이탈을 예방해요. 대리점·강사 코칭과도 연결돼요.</t>
         </is>
       </c>
       <c r="B104" s="24" t="n"/>
@@ -3048,1088 +3997,1041 @@
       <c r="E104" s="24" t="n"/>
       <c r="F104" s="24" t="n"/>
     </row>
-    <row r="105">
+    <row r="105" ht="24" customHeight="1">
       <c r="A105" s="25" t="inlineStr">
         <is>
+          <t>🧭  1 이탈위험 그래프   ›   2 이탈 전염 관계망   ›   3 알림톡·상담·코칭</t>
+        </is>
+      </c>
+      <c r="B105" s="26" t="n"/>
+      <c r="C105" s="26" t="n"/>
+      <c r="D105" s="26" t="n"/>
+      <c r="E105" s="26" t="n"/>
+      <c r="F105" s="26" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="27" t="inlineStr">
+        <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B105" s="26" t="inlineStr">
+      <c r="B106" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="30" customHeight="1">
-      <c r="A106" s="27" t="n">
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B106" s="28" t="inlineStr">
-        <is>
-          <t>월간 리포트로 지사·대리점 성과를 확인해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="30" customHeight="1">
-      <c r="A107" s="27" t="n">
+      <c r="B107" s="30" t="inlineStr">
+        <is>
+          <t>이탈위험 그래프로 위험 학생·대리점을 찾아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B107" s="28" t="inlineStr">
-        <is>
-          <t>지표(매출·재원·출석·정산)를 전월/전년과 비교해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="30" customHeight="1">
-      <c r="A108" s="27" t="n">
+      <c r="B108" s="30" t="inlineStr">
+        <is>
+          <t>이탈 전염 관계망으로 연쇄 이탈을 예방해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B108" s="28" t="inlineStr">
-        <is>
-          <t>리포트를 인쇄·PDF로 저장해 공유해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="24" customHeight="1">
-      <c r="A109" s="29" t="inlineStr">
+      <c r="B109" s="30" t="inlineStr">
+        <is>
+          <t>위험이 높은 곳에 알림톡·상담·코칭을 연결해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="24" customHeight="1">
+      <c r="A110" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B109" s="30" t="inlineStr">
-        <is>
-          <t>AI 인사이트가 성과 요약을 도와줘요.</t>
-        </is>
-      </c>
-      <c r="C109" s="31" t="n"/>
-      <c r="D109" s="31" t="n"/>
-      <c r="E109" s="31" t="n"/>
-      <c r="F109" s="31" t="n"/>
-    </row>
-    <row r="110" ht="24" customHeight="1">
-      <c r="A110" s="29" t="inlineStr">
+      <c r="B110" s="32" t="inlineStr">
+        <is>
+          <t>빨리 개입할수록 잔존율이 올라가요.</t>
+        </is>
+      </c>
+      <c r="C110" s="33" t="n"/>
+      <c r="D110" s="33" t="n"/>
+      <c r="E110" s="33" t="n"/>
+      <c r="F110" s="33" t="n"/>
+    </row>
+    <row r="111" ht="24" customHeight="1">
+      <c r="A111" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B110" s="30" t="inlineStr">
-        <is>
-          <t>성과 리포트는 대리점 동기부여 자료로도 좋아요.</t>
-        </is>
-      </c>
-      <c r="C110" s="31" t="n"/>
-      <c r="D110" s="31" t="n"/>
-      <c r="E110" s="31" t="n"/>
-      <c r="F110" s="31" t="n"/>
-    </row>
-    <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 월초 리포트 공유를 정례화하면 지사 운영이 투명해져요.</t>
-        </is>
-      </c>
-      <c r="B111" s="33" t="n"/>
+      <c r="B111" s="32" t="inlineStr">
+        <is>
+          <t>대리점별 이탈 패턴을 비교해 지원하세요.</t>
+        </is>
+      </c>
       <c r="C111" s="33" t="n"/>
       <c r="D111" s="33" t="n"/>
       <c r="E111" s="33" t="n"/>
       <c r="F111" s="33" t="n"/>
     </row>
-    <row r="113" ht="26" customHeight="1">
-      <c r="A113" s="21" t="inlineStr">
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 매주 위험 상위 대리점·학생만이라도 챙기면 이탈이 눈에 띄게 줄어요.</t>
+        </is>
+      </c>
+      <c r="B112" s="35" t="n"/>
+      <c r="C112" s="35" t="n"/>
+      <c r="D112" s="35" t="n"/>
+      <c r="E112" s="35" t="n"/>
+      <c r="F112" s="35" t="n"/>
+    </row>
+    <row r="113" ht="18" customHeight="1"/>
+    <row r="115" ht="26" customHeight="1">
+      <c r="A115" s="21" t="inlineStr">
+        <is>
+          <t>10  📊 월간 리포트·성과 분석  —  지사·대리점 성과</t>
+        </is>
+      </c>
+      <c r="B115" s="22" t="n"/>
+      <c r="C115" s="22" t="n"/>
+      <c r="D115" s="22" t="n"/>
+      <c r="E115" s="22" t="n"/>
+      <c r="F115" s="22" t="n"/>
+    </row>
+    <row r="116" ht="42" customHeight="1">
+      <c r="A116" s="23" t="inlineStr">
+        <is>
+          <t>📖 지사와 산하 대리점의 성과를 월간 리포트로 정리해요. 매출·재원·출석·정산을 한눈에 보고, 인쇄·PDF로 저장해 공유해요.</t>
+        </is>
+      </c>
+      <c r="B116" s="24" t="n"/>
+      <c r="C116" s="24" t="n"/>
+      <c r="D116" s="24" t="n"/>
+      <c r="E116" s="24" t="n"/>
+      <c r="F116" s="24" t="n"/>
+    </row>
+    <row r="117" ht="24" customHeight="1">
+      <c r="A117" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 월간 리포트   ›   2 전월/전년과 비교   ›   3 인쇄·PDF</t>
+        </is>
+      </c>
+      <c r="B117" s="26" t="n"/>
+      <c r="C117" s="26" t="n"/>
+      <c r="D117" s="26" t="n"/>
+      <c r="E117" s="26" t="n"/>
+      <c r="F117" s="26" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B118" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B119" s="30" t="inlineStr">
+        <is>
+          <t>월간 리포트로 지사·대리점 성과를 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="30" customHeight="1">
+      <c r="A120" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B120" s="30" t="inlineStr">
+        <is>
+          <t>지표(매출·재원·출석·정산)를 전월/전년과 비교해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="30" customHeight="1">
+      <c r="A121" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B121" s="30" t="inlineStr">
+        <is>
+          <t>리포트를 인쇄·PDF로 저장해 공유해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="24" customHeight="1">
+      <c r="A122" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B122" s="32" t="inlineStr">
+        <is>
+          <t>AI 인사이트가 성과 요약을 도와줘요.</t>
+        </is>
+      </c>
+      <c r="C122" s="33" t="n"/>
+      <c r="D122" s="33" t="n"/>
+      <c r="E122" s="33" t="n"/>
+      <c r="F122" s="33" t="n"/>
+    </row>
+    <row r="123" ht="24" customHeight="1">
+      <c r="A123" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B123" s="32" t="inlineStr">
+        <is>
+          <t>성과 리포트는 대리점 동기부여 자료로도 좋아요.</t>
+        </is>
+      </c>
+      <c r="C123" s="33" t="n"/>
+      <c r="D123" s="33" t="n"/>
+      <c r="E123" s="33" t="n"/>
+      <c r="F123" s="33" t="n"/>
+    </row>
+    <row r="124" ht="30" customHeight="1">
+      <c r="A124" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 월초 리포트 공유를 정례화하면 지사 운영이 투명해져요.</t>
+        </is>
+      </c>
+      <c r="B124" s="35" t="n"/>
+      <c r="C124" s="35" t="n"/>
+      <c r="D124" s="35" t="n"/>
+      <c r="E124" s="35" t="n"/>
+      <c r="F124" s="35" t="n"/>
+    </row>
+    <row r="125" ht="18" customHeight="1"/>
+    <row r="127" ht="26" customHeight="1">
+      <c r="A127" s="21" t="inlineStr">
         <is>
           <t>11  🎓 대리점 지원·교육  —  온보딩·운영 코칭</t>
         </is>
       </c>
-      <c r="B113" s="22" t="n"/>
-      <c r="C113" s="22" t="n"/>
-      <c r="D113" s="22" t="n"/>
-      <c r="E113" s="22" t="n"/>
-      <c r="F113" s="22" t="n"/>
-    </row>
-    <row r="114" ht="42" customHeight="1">
-      <c r="A114" s="23" t="inlineStr">
+      <c r="B127" s="22" t="n"/>
+      <c r="C127" s="22" t="n"/>
+      <c r="D127" s="22" t="n"/>
+      <c r="E127" s="22" t="n"/>
+      <c r="F127" s="22" t="n"/>
+    </row>
+    <row r="128" ht="42" customHeight="1">
+      <c r="A128" s="23" t="inlineStr">
         <is>
           <t>📖 산하 대리점이 잘 운영하도록 온보딩과 운영 코칭을 지원해요. 사용설명서·FAQ·상담 채널을 안내하고, 우수 사례를 공유해요.</t>
         </is>
       </c>
-      <c r="B114" s="24" t="n"/>
-      <c r="C114" s="24" t="n"/>
-      <c r="D114" s="24" t="n"/>
-      <c r="E114" s="24" t="n"/>
-      <c r="F114" s="24" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="25" t="inlineStr">
+      <c r="B128" s="24" t="n"/>
+      <c r="C128" s="24" t="n"/>
+      <c r="D128" s="24" t="n"/>
+      <c r="E128" s="24" t="n"/>
+      <c r="F128" s="24" t="n"/>
+    </row>
+    <row r="129" ht="24" customHeight="1">
+      <c r="A129" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 사용설명서·운영 가이드   ›   2 FAQ   ›   3 상향 평준화</t>
+        </is>
+      </c>
+      <c r="B129" s="26" t="n"/>
+      <c r="C129" s="26" t="n"/>
+      <c r="D129" s="26" t="n"/>
+      <c r="E129" s="26" t="n"/>
+      <c r="F129" s="26" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B115" s="26" t="inlineStr">
+      <c r="B130" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="30" customHeight="1">
-      <c r="A116" s="27" t="n">
+    <row r="131" ht="30" customHeight="1">
+      <c r="A131" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B116" s="28" t="inlineStr">
+      <c r="B131" s="30" t="inlineStr">
         <is>
           <t>신규 대리점에 사용설명서·운영 가이드를 안내해요.</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="30" customHeight="1">
-      <c r="A117" s="27" t="n">
+    <row r="132" ht="30" customHeight="1">
+      <c r="A132" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B117" s="28" t="inlineStr">
+      <c r="B132" s="30" t="inlineStr">
         <is>
           <t>자주 묻는 질문은 FAQ로 정리해 배포해요.</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="30" customHeight="1">
-      <c r="A118" s="27" t="n">
+    <row r="133" ht="30" customHeight="1">
+      <c r="A133" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B118" s="28" t="inlineStr">
+      <c r="B133" s="30" t="inlineStr">
         <is>
           <t>우수 대리점 사례를 공유해 상향 평준화해요.</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="24" customHeight="1">
-      <c r="A119" s="29" t="inlineStr">
+    <row r="134" ht="24" customHeight="1">
+      <c r="A134" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B119" s="30" t="inlineStr">
+      <c r="B134" s="32" t="inlineStr">
         <is>
           <t>초기 온보딩이 대리점 성패를 크게 좌우해요.</t>
         </is>
       </c>
-      <c r="C119" s="31" t="n"/>
-      <c r="D119" s="31" t="n"/>
-      <c r="E119" s="31" t="n"/>
-      <c r="F119" s="31" t="n"/>
-    </row>
-    <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="29" t="inlineStr">
+      <c r="C134" s="33" t="n"/>
+      <c r="D134" s="33" t="n"/>
+      <c r="E134" s="33" t="n"/>
+      <c r="F134" s="33" t="n"/>
+    </row>
+    <row r="135" ht="24" customHeight="1">
+      <c r="A135" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B120" s="30" t="inlineStr">
+      <c r="B135" s="32" t="inlineStr">
         <is>
           <t>반복 문의는 FAQ로 만들어 지원 부담을 줄이세요.</t>
         </is>
       </c>
-      <c r="C120" s="31" t="n"/>
-      <c r="D120" s="31" t="n"/>
-      <c r="E120" s="31" t="n"/>
-      <c r="F120" s="31" t="n"/>
-    </row>
-    <row r="121" ht="30" customHeight="1">
-      <c r="A121" s="32" t="inlineStr">
+      <c r="C135" s="33" t="n"/>
+      <c r="D135" s="33" t="n"/>
+      <c r="E135" s="33" t="n"/>
+      <c r="F135" s="33" t="n"/>
+    </row>
+    <row r="136" ht="30" customHeight="1">
+      <c r="A136" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 분기별 대리점 미팅으로 성과·애로사항을 함께 점검하세요.</t>
         </is>
       </c>
-      <c r="B121" s="33" t="n"/>
-      <c r="C121" s="33" t="n"/>
-      <c r="D121" s="33" t="n"/>
-      <c r="E121" s="33" t="n"/>
-      <c r="F121" s="33" t="n"/>
-    </row>
-    <row r="123" ht="26" customHeight="1">
-      <c r="A123" s="21" t="inlineStr">
+      <c r="B136" s="35" t="n"/>
+      <c r="C136" s="35" t="n"/>
+      <c r="D136" s="35" t="n"/>
+      <c r="E136" s="35" t="n"/>
+      <c r="F136" s="35" t="n"/>
+    </row>
+    <row r="137" ht="18" customHeight="1"/>
+    <row r="139" ht="26" customHeight="1">
+      <c r="A139" s="21" t="inlineStr">
         <is>
           <t>12  🎧 고객센터·문의  —  본사 지원 받기</t>
         </is>
       </c>
-      <c r="B123" s="22" t="n"/>
-      <c r="C123" s="22" t="n"/>
-      <c r="D123" s="22" t="n"/>
-      <c r="E123" s="22" t="n"/>
-      <c r="F123" s="22" t="n"/>
-    </row>
-    <row r="124" ht="42" customHeight="1">
-      <c r="A124" s="23" t="inlineStr">
+      <c r="B139" s="22" t="n"/>
+      <c r="C139" s="22" t="n"/>
+      <c r="D139" s="22" t="n"/>
+      <c r="E139" s="22" t="n"/>
+      <c r="F139" s="22" t="n"/>
+    </row>
+    <row r="140" ht="42" customHeight="1">
+      <c r="A140" s="23" t="inlineStr">
         <is>
           <t>📖 운영 중 문제가 생기면 본사 고객센터·지원 채널로 문의해요. 시스템·정산·정책 관련 문의를 빠르게 해결할 수 있어요.</t>
         </is>
       </c>
-      <c r="B124" s="24" t="n"/>
-      <c r="C124" s="24" t="n"/>
-      <c r="D124" s="24" t="n"/>
-      <c r="E124" s="24" t="n"/>
-      <c r="F124" s="24" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="25" t="inlineStr">
+      <c r="B140" s="24" t="n"/>
+      <c r="C140" s="24" t="n"/>
+      <c r="D140" s="24" t="n"/>
+      <c r="E140" s="24" t="n"/>
+      <c r="F140" s="24" t="n"/>
+    </row>
+    <row r="141" ht="24" customHeight="1">
+      <c r="A141" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 고객센터   ›   2 본사 담당   ›   3 대응 방법을 메모</t>
+        </is>
+      </c>
+      <c r="B141" s="26" t="n"/>
+      <c r="C141" s="26" t="n"/>
+      <c r="D141" s="26" t="n"/>
+      <c r="E141" s="26" t="n"/>
+      <c r="F141" s="26" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B125" s="26" t="inlineStr">
+      <c r="B142" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="30" customHeight="1">
-      <c r="A126" s="27" t="n">
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B126" s="28" t="inlineStr">
+      <c r="B143" s="30" t="inlineStr">
         <is>
           <t>고객센터에서 전화·이메일·카카오·원격지원을 이용해요.</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="30" customHeight="1">
-      <c r="A127" s="27" t="n">
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B127" s="28" t="inlineStr">
+      <c r="B144" s="30" t="inlineStr">
         <is>
           <t>정산·정책 문의는 본사 담당과 연결해요.</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="30" customHeight="1">
-      <c r="A128" s="27" t="n">
+    <row r="145" ht="30" customHeight="1">
+      <c r="A145" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B128" s="28" t="inlineStr">
+      <c r="B145" s="30" t="inlineStr">
         <is>
           <t>반복 문제는 대응 방법을 메모해 둬요.</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="24" customHeight="1">
-      <c r="A129" s="29" t="inlineStr">
+    <row r="146" ht="24" customHeight="1">
+      <c r="A146" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B129" s="30" t="inlineStr">
+      <c r="B146" s="32" t="inlineStr">
         <is>
           <t>시스템 문제는 원격지원으로 빠르게 해결돼요.</t>
         </is>
       </c>
-      <c r="C129" s="31" t="n"/>
-      <c r="D129" s="31" t="n"/>
-      <c r="E129" s="31" t="n"/>
-      <c r="F129" s="31" t="n"/>
-    </row>
-    <row r="130" ht="24" customHeight="1">
-      <c r="A130" s="29" t="inlineStr">
+      <c r="C146" s="33" t="n"/>
+      <c r="D146" s="33" t="n"/>
+      <c r="E146" s="33" t="n"/>
+      <c r="F146" s="33" t="n"/>
+    </row>
+    <row r="147" ht="24" customHeight="1">
+      <c r="A147" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B130" s="30" t="inlineStr">
+      <c r="B147" s="32" t="inlineStr">
         <is>
           <t>운영시간 내 문의가 빨라요.</t>
         </is>
       </c>
-      <c r="C130" s="31" t="n"/>
-      <c r="D130" s="31" t="n"/>
-      <c r="E130" s="31" t="n"/>
-      <c r="F130" s="31" t="n"/>
-    </row>
-    <row r="131" ht="30" customHeight="1">
-      <c r="A131" s="32" t="inlineStr">
+      <c r="C147" s="33" t="n"/>
+      <c r="D147" s="33" t="n"/>
+      <c r="E147" s="33" t="n"/>
+      <c r="F147" s="33" t="n"/>
+    </row>
+    <row r="148" ht="30" customHeight="1">
+      <c r="A148" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 자주 겪는 문의와 해결법을 정리해 대리점에도 공유하세요.</t>
         </is>
       </c>
-      <c r="B131" s="33" t="n"/>
-      <c r="C131" s="33" t="n"/>
-      <c r="D131" s="33" t="n"/>
-      <c r="E131" s="33" t="n"/>
-      <c r="F131" s="33" t="n"/>
-    </row>
-    <row r="133" ht="26" customHeight="1">
-      <c r="A133" s="21" t="inlineStr">
+      <c r="B148" s="35" t="n"/>
+      <c r="C148" s="35" t="n"/>
+      <c r="D148" s="35" t="n"/>
+      <c r="E148" s="35" t="n"/>
+      <c r="F148" s="35" t="n"/>
+    </row>
+    <row r="149" ht="18" customHeight="1"/>
+    <row r="151" ht="26" customHeight="1">
+      <c r="A151" s="21" t="inlineStr">
         <is>
           <t>13  🕐 한국·필리핀 듀얼 시계  —  화면에 뜨는 두 나라 시간</t>
         </is>
       </c>
-      <c r="B133" s="22" t="n"/>
-      <c r="C133" s="22" t="n"/>
-      <c r="D133" s="22" t="n"/>
-      <c r="E133" s="22" t="n"/>
-      <c r="F133" s="22" t="n"/>
-    </row>
-    <row r="134" ht="42" customHeight="1">
-      <c r="A134" s="23" t="inlineStr">
+      <c r="B151" s="22" t="n"/>
+      <c r="C151" s="22" t="n"/>
+      <c r="D151" s="22" t="n"/>
+      <c r="E151" s="22" t="n"/>
+      <c r="F151" s="22" t="n"/>
+    </row>
+    <row r="152" ht="42" customHeight="1">
+      <c r="A152" s="23" t="inlineStr">
         <is>
           <t>📖 화면에 🇰🇷 한국·🇵🇭 필리핀 시간이 함께 뜨는 시계예요. 필리핀 현지 강사와 한국 학생의 수업 시간을 조율할 때 시차를 바로 확인할 수 있어요.</t>
         </is>
       </c>
-      <c r="B134" s="24" t="n"/>
-      <c r="C134" s="24" t="n"/>
-      <c r="D134" s="24" t="n"/>
-      <c r="E134" s="24" t="n"/>
-      <c r="F134" s="24" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="25" t="inlineStr">
+      <c r="B152" s="24" t="n"/>
+      <c r="C152" s="24" t="n"/>
+      <c r="D152" s="24" t="n"/>
+      <c r="E152" s="24" t="n"/>
+      <c r="F152" s="24" t="n"/>
+    </row>
+    <row r="153" ht="24" customHeight="1">
+      <c r="A153" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 듀얼 시계   ›   2 드래그   ›   3 탭(클릭)</t>
+        </is>
+      </c>
+      <c r="B153" s="26" t="n"/>
+      <c r="C153" s="26" t="n"/>
+      <c r="D153" s="26" t="n"/>
+      <c r="E153" s="26" t="n"/>
+      <c r="F153" s="26" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B135" s="26" t="inlineStr">
+      <c r="B154" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="30" customHeight="1">
-      <c r="A136" s="27" t="n">
+    <row r="155" ht="30" customHeight="1">
+      <c r="A155" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B136" s="28" t="inlineStr">
+      <c r="B155" s="30" t="inlineStr">
         <is>
           <t>화면에 떠 있는 듀얼 시계에서 🇰🇷 한국·🇵🇭 필리핀 시간을 동시에 봐요.</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="30" customHeight="1">
-      <c r="A137" s="27" t="n">
+    <row r="156" ht="30" customHeight="1">
+      <c r="A156" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B137" s="28" t="inlineStr">
+      <c r="B156" s="30" t="inlineStr">
         <is>
           <t>시계를 드래그하면 원하는 위치로 옮길 수 있어요.</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="30" customHeight="1">
-      <c r="A138" s="27" t="n">
+    <row r="157" ht="30" customHeight="1">
+      <c r="A157" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B138" s="28" t="inlineStr">
+      <c r="B157" s="30" t="inlineStr">
         <is>
           <t>시계를 탭(클릭)하면 홈으로 이동해요.</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="24" customHeight="1">
-      <c r="A139" s="29" t="inlineStr">
+    <row r="158" ht="24" customHeight="1">
+      <c r="A158" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B139" s="30" t="inlineStr">
+      <c r="B158" s="32" t="inlineStr">
         <is>
           <t>필리핀은 한국보다 1시간 느려요(시차 −1시간).</t>
         </is>
       </c>
-      <c r="C139" s="31" t="n"/>
-      <c r="D139" s="31" t="n"/>
-      <c r="E139" s="31" t="n"/>
-      <c r="F139" s="31" t="n"/>
-    </row>
-    <row r="140" ht="24" customHeight="1">
-      <c r="A140" s="29" t="inlineStr">
+      <c r="C158" s="33" t="n"/>
+      <c r="D158" s="33" t="n"/>
+      <c r="E158" s="33" t="n"/>
+      <c r="F158" s="33" t="n"/>
+    </row>
+    <row r="159" ht="24" customHeight="1">
+      <c r="A159" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B140" s="30" t="inlineStr">
+      <c r="B159" s="32" t="inlineStr">
         <is>
           <t>수업 예약·입장 시간을 두 나라 시간으로 확인할 수 있어요.</t>
         </is>
       </c>
-      <c r="C140" s="31" t="n"/>
-      <c r="D140" s="31" t="n"/>
-      <c r="E140" s="31" t="n"/>
-      <c r="F140" s="31" t="n"/>
-    </row>
-    <row r="141" ht="30" customHeight="1">
-      <c r="A141" s="32" t="inlineStr">
+      <c r="C159" s="33" t="n"/>
+      <c r="D159" s="33" t="n"/>
+      <c r="E159" s="33" t="n"/>
+      <c r="F159" s="33" t="n"/>
+    </row>
+    <row r="160" ht="30" customHeight="1">
+      <c r="A160" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 시차 때문에 수업 시간이 헷갈릴 때 이 시계를 보면 바로 확인돼요.</t>
         </is>
       </c>
-      <c r="B141" s="33" t="n"/>
-      <c r="C141" s="33" t="n"/>
-      <c r="D141" s="33" t="n"/>
-      <c r="E141" s="33" t="n"/>
-      <c r="F141" s="33" t="n"/>
-    </row>
-    <row r="143" ht="26" customHeight="1">
-      <c r="A143" s="21" t="inlineStr">
+      <c r="B160" s="35" t="n"/>
+      <c r="C160" s="35" t="n"/>
+      <c r="D160" s="35" t="n"/>
+      <c r="E160" s="35" t="n"/>
+      <c r="F160" s="35" t="n"/>
+    </row>
+    <row r="161" ht="18" customHeight="1"/>
+    <row r="163" ht="26" customHeight="1">
+      <c r="A163" s="21" t="inlineStr">
         <is>
           <t>14  🇨🇳 중국어 발음 코치  —  다락원 중국어 마스터 Lv1~20</t>
         </is>
       </c>
-      <c r="B143" s="22" t="n"/>
-      <c r="C143" s="22" t="n"/>
-      <c r="D143" s="22" t="n"/>
-      <c r="E143" s="22" t="n"/>
-      <c r="F143" s="22" t="n"/>
-    </row>
-    <row r="144" ht="42" customHeight="1">
-      <c r="A144" s="23" t="inlineStr">
+      <c r="B163" s="22" t="n"/>
+      <c r="C163" s="22" t="n"/>
+      <c r="D163" s="22" t="n"/>
+      <c r="E163" s="22" t="n"/>
+      <c r="F163" s="22" t="n"/>
+    </row>
+    <row r="164" ht="42" customHeight="1">
+      <c r="A164" s="23" t="inlineStr">
         <is>
           <t>📖 망고아이는 영어뿐 아니라 중국어 과정도 제공해요. 다락원 중국어 마스터(Lv 1~20) 기반 발음 코치(한자+병음·AI 음성인식·원어민 비교)로, 중국어 수요가 있는 학생을 유치·관리할 수 있어요.</t>
         </is>
       </c>
-      <c r="B144" s="24" t="n"/>
-      <c r="C144" s="24" t="n"/>
-      <c r="D144" s="24" t="n"/>
-      <c r="E144" s="24" t="n"/>
-      <c r="F144" s="24" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="25" t="inlineStr">
+      <c r="B164" s="24" t="n"/>
+      <c r="C164" s="24" t="n"/>
+      <c r="D164" s="24" t="n"/>
+      <c r="E164" s="24" t="n"/>
+      <c r="F164" s="24" t="n"/>
+    </row>
+    <row r="165" ht="24" customHeight="1">
+      <c r="A165" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 CN 중국어   ›   2 다락원 마스터 시리즈(1…   ›   3 한자 + 병음   ›   4 반복·느리게(0.85x)</t>
+        </is>
+      </c>
+      <c r="B165" s="26" t="n"/>
+      <c r="C165" s="26" t="n"/>
+      <c r="D165" s="26" t="n"/>
+      <c r="E165" s="26" t="n"/>
+      <c r="F165" s="26" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B145" s="26" t="inlineStr">
+      <c r="B166" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="30" customHeight="1">
-      <c r="A146" s="27" t="n">
+    <row r="167" ht="30" customHeight="1">
+      <c r="A167" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B146" s="28" t="inlineStr">
+      <c r="B167" s="30" t="inlineStr">
         <is>
           <t>AI 음성코치에서 CN 중국어 레벨을 골라요. (또는 중국어 발음 코치로 이동)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="30" customHeight="1">
-      <c r="A147" s="27" t="n">
+    <row r="168" ht="30" customHeight="1">
+      <c r="A168" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B147" s="28" t="inlineStr">
+      <c r="B168" s="30" t="inlineStr">
         <is>
           <t>다락원 마스터 시리즈(1~6, HSK 1~6)와 단원을 선택해요.</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="30" customHeight="1">
-      <c r="A148" s="27" t="n">
+    <row r="169" ht="30" customHeight="1">
+      <c r="A169" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B148" s="28" t="inlineStr">
+      <c r="B169" s="30" t="inlineStr">
         <is>
           <t>화면의 문장(한자 + 병음)을 따라 읽고, ‘원어민 발음 듣기’로 비교해요.</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="30" customHeight="1">
-      <c r="A149" s="27" t="n">
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B149" s="28" t="inlineStr">
+      <c r="B170" s="30" t="inlineStr">
         <is>
           <t>반복·느리게(0.85x) 기능으로 어려운 발음·성조를 연습해요.</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="24" customHeight="1">
-      <c r="A150" s="29" t="inlineStr">
+    <row r="171" ht="24" customHeight="1">
+      <c r="A171" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B150" s="30" t="inlineStr">
+      <c r="B171" s="32" t="inlineStr">
         <is>
           <t>한자와 병음(발음 표기)이 함께 나와 읽기 쉬워요.</t>
         </is>
       </c>
-      <c r="C150" s="31" t="n"/>
-      <c r="D150" s="31" t="n"/>
-      <c r="E150" s="31" t="n"/>
-      <c r="F150" s="31" t="n"/>
-    </row>
-    <row r="151" ht="24" customHeight="1">
-      <c r="A151" s="29" t="inlineStr">
+      <c r="C171" s="33" t="n"/>
+      <c r="D171" s="33" t="n"/>
+      <c r="E171" s="33" t="n"/>
+      <c r="F171" s="33" t="n"/>
+    </row>
+    <row r="172" ht="24" customHeight="1">
+      <c r="A172" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B151" s="30" t="inlineStr">
+      <c r="B172" s="32" t="inlineStr">
         <is>
           <t>AI가 음성을 인식해 원어민과 비교해줘요.</t>
         </is>
       </c>
-      <c r="C151" s="31" t="n"/>
-      <c r="D151" s="31" t="n"/>
-      <c r="E151" s="31" t="n"/>
-      <c r="F151" s="31" t="n"/>
-    </row>
-    <row r="152" ht="24" customHeight="1">
-      <c r="A152" s="29" t="inlineStr">
+      <c r="C172" s="33" t="n"/>
+      <c r="D172" s="33" t="n"/>
+      <c r="E172" s="33" t="n"/>
+      <c r="F172" s="33" t="n"/>
+    </row>
+    <row r="173" ht="24" customHeight="1">
+      <c r="A173" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B152" s="30" t="inlineStr">
+      <c r="B173" s="32" t="inlineStr">
         <is>
           <t>학습 게임 허브에서도 중국어를 지원해요.</t>
         </is>
       </c>
-      <c r="C152" s="31" t="n"/>
-      <c r="D152" s="31" t="n"/>
-      <c r="E152" s="31" t="n"/>
-      <c r="F152" s="31" t="n"/>
-    </row>
-    <row r="153" ht="30" customHeight="1">
-      <c r="A153" s="32" t="inlineStr">
+      <c r="C173" s="33" t="n"/>
+      <c r="D173" s="33" t="n"/>
+      <c r="E173" s="33" t="n"/>
+      <c r="F173" s="33" t="n"/>
+    </row>
+    <row r="174" ht="30" customHeight="1">
+      <c r="A174" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 느리게로 듣고 또박또박 따라 하면 성조(4성)가 잘 잡혀요.</t>
         </is>
       </c>
-      <c r="B153" s="33" t="n"/>
-      <c r="C153" s="33" t="n"/>
-      <c r="D153" s="33" t="n"/>
-      <c r="E153" s="33" t="n"/>
-      <c r="F153" s="33" t="n"/>
-    </row>
-    <row r="155" ht="26" customHeight="1">
-      <c r="A155" s="21" t="inlineStr">
+      <c r="B174" s="35" t="n"/>
+      <c r="C174" s="35" t="n"/>
+      <c r="D174" s="35" t="n"/>
+      <c r="E174" s="35" t="n"/>
+      <c r="F174" s="35" t="n"/>
+    </row>
+    <row r="176" ht="26" customHeight="1">
+      <c r="A176" s="21" t="inlineStr">
         <is>
           <t>15  🌟 수업 중 칭찬 포인트 (이해·활용)  —  학생 동기부여·재등록에 연결</t>
         </is>
       </c>
-      <c r="B155" s="22" t="n"/>
-      <c r="C155" s="22" t="n"/>
-      <c r="D155" s="22" t="n"/>
-      <c r="E155" s="22" t="n"/>
-      <c r="F155" s="22" t="n"/>
-    </row>
-    <row r="156" ht="42" customHeight="1">
-      <c r="A156" s="23" t="inlineStr">
+      <c r="B176" s="22" t="n"/>
+      <c r="C176" s="22" t="n"/>
+      <c r="D176" s="22" t="n"/>
+      <c r="E176" s="22" t="n"/>
+      <c r="F176" s="22" t="n"/>
+    </row>
+    <row r="177" ht="42" customHeight="1">
+      <c r="A177" s="23" t="inlineStr">
         <is>
           <t>📖 수업 중 교사가 학생에게 🌟 칭찬 포인트(+1P)를 즉석 지급하고, 수업 종료 별점(+10P)이 더해져 학생 총포인트로 쌓여요. 포인트는 상점·기프티콘 보상으로 이어져 학생 동기부여와 재등록에 도움이 돼요. 지사는 이 흐름을 이해하고 성과에 활용해요.</t>
         </is>
       </c>
-      <c r="B156" s="24" t="n"/>
-      <c r="C156" s="24" t="n"/>
-      <c r="D156" s="24" t="n"/>
-      <c r="E156" s="24" t="n"/>
-      <c r="F156" s="24" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="25" t="inlineStr">
+      <c r="B177" s="24" t="n"/>
+      <c r="C177" s="24" t="n"/>
+      <c r="D177" s="24" t="n"/>
+      <c r="E177" s="24" t="n"/>
+      <c r="F177" s="24" t="n"/>
+    </row>
+    <row r="178" ht="24" customHeight="1">
+      <c r="A178" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 교사   ›   2 학생   ›   3 수업 종료 별점 평가   ›   4 상점·룰렛·기프티콘</t>
+        </is>
+      </c>
+      <c r="B178" s="26" t="n"/>
+      <c r="C178" s="26" t="n"/>
+      <c r="D178" s="26" t="n"/>
+      <c r="E178" s="26" t="n"/>
+      <c r="F178" s="26" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B157" s="26" t="inlineStr">
+      <c r="B179" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="30" customHeight="1">
-      <c r="A158" s="27" t="n">
+    <row r="180" ht="30" customHeight="1">
+      <c r="A180" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B158" s="28" t="inlineStr">
+      <c r="B180" s="30" t="inlineStr">
         <is>
           <t>교사가 수업 중 학생 화면의 🌟 칭찬 버튼으로 +1P를 지급해요.</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="30" customHeight="1">
-      <c r="A159" s="27" t="n">
+    <row r="181" ht="30" customHeight="1">
+      <c r="A181" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B159" s="28" t="inlineStr">
+      <c r="B181" s="30" t="inlineStr">
         <is>
           <t>학생 🧺 포인트 바구니에 실시간 누적, 총 포인트에 합산돼요.</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="30" customHeight="1">
-      <c r="A160" s="27" t="n">
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B160" s="28" t="inlineStr">
+      <c r="B182" s="30" t="inlineStr">
         <is>
           <t>수업 종료 별점 평가로 학생은 +10P를 더 받아요.</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="30" customHeight="1">
-      <c r="A161" s="27" t="n">
+    <row r="183" ht="30" customHeight="1">
+      <c r="A183" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B161" s="28" t="inlineStr">
+      <c r="B183" s="30" t="inlineStr">
         <is>
           <t>포인트는 상점·룰렛·기프티콘 보상과 연결돼요.</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="24" customHeight="1">
-      <c r="A162" s="29" t="inlineStr">
+    <row r="184" ht="24" customHeight="1">
+      <c r="A184" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B162" s="30" t="inlineStr">
+      <c r="B184" s="32" t="inlineStr">
         <is>
           <t>즉각 보상은 학생 참여·재등록에 긍정적이에요.</t>
         </is>
       </c>
-      <c r="C162" s="31" t="n"/>
-      <c r="D162" s="31" t="n"/>
-      <c r="E162" s="31" t="n"/>
-      <c r="F162" s="31" t="n"/>
-    </row>
-    <row r="163" ht="24" customHeight="1">
-      <c r="A163" s="29" t="inlineStr">
+      <c r="C184" s="33" t="n"/>
+      <c r="D184" s="33" t="n"/>
+      <c r="E184" s="33" t="n"/>
+      <c r="F184" s="33" t="n"/>
+    </row>
+    <row r="185" ht="24" customHeight="1">
+      <c r="A185" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B163" s="30" t="inlineStr">
+      <c r="B185" s="32" t="inlineStr">
         <is>
           <t>우리 지사 학생의 포인트·리워드 반응을 성과로 활용하세요.</t>
         </is>
       </c>
-      <c r="C163" s="31" t="n"/>
-      <c r="D163" s="31" t="n"/>
-      <c r="E163" s="31" t="n"/>
-      <c r="F163" s="31" t="n"/>
-    </row>
-    <row r="164" ht="26" customHeight="1">
-      <c r="A164" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 칭찬 포인트 지급은 교사가, 상점·리워드·기프티콘 정책은 본사(관리자)가 구성해요.</t>
-        </is>
-      </c>
-      <c r="B164" s="35" t="n"/>
-      <c r="C164" s="35" t="n"/>
-      <c r="D164" s="35" t="n"/>
-      <c r="E164" s="35" t="n"/>
-      <c r="F164" s="35" t="n"/>
-    </row>
-    <row r="165" ht="30" customHeight="1">
-      <c r="A165" s="32" t="inlineStr">
+      <c r="C185" s="33" t="n"/>
+      <c r="D185" s="33" t="n"/>
+      <c r="E185" s="33" t="n"/>
+      <c r="F185" s="33" t="n"/>
+    </row>
+    <row r="186" ht="26" customHeight="1">
+      <c r="A186" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 칭찬 포인트 지급은 교사가, 상점·리워드·기프티콘 정책은 본사(관리자)가 구성해요.</t>
+        </is>
+      </c>
+      <c r="B186" s="37" t="n"/>
+      <c r="C186" s="37" t="n"/>
+      <c r="D186" s="37" t="n"/>
+      <c r="E186" s="37" t="n"/>
+      <c r="F186" s="37" t="n"/>
+    </row>
+    <row r="187" ht="30" customHeight="1">
+      <c r="A187" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 칭찬 포인트가 잘 도는 반(교사)일수록 재등록률이 높은 경향이 있어요.</t>
         </is>
       </c>
-      <c r="B165" s="33" t="n"/>
-      <c r="C165" s="33" t="n"/>
-      <c r="D165" s="33" t="n"/>
-      <c r="E165" s="33" t="n"/>
-      <c r="F165" s="33" t="n"/>
-    </row>
-    <row r="167" ht="26" customHeight="1">
-      <c r="A167" s="21" t="inlineStr">
+      <c r="B187" s="35" t="n"/>
+      <c r="C187" s="35" t="n"/>
+      <c r="D187" s="35" t="n"/>
+      <c r="E187" s="35" t="n"/>
+      <c r="F187" s="35" t="n"/>
+    </row>
+    <row r="189" ht="26" customHeight="1">
+      <c r="A189" s="21" t="inlineStr">
         <is>
           <t>16  📢 공지 스튜디오 (포스터 + 팝업)  —  공지·이벤트 포스터를 만들어 학생 앱 팝업으로</t>
         </is>
       </c>
-      <c r="B167" s="22" t="n"/>
-      <c r="C167" s="22" t="n"/>
-      <c r="D167" s="22" t="n"/>
-      <c r="E167" s="22" t="n"/>
-      <c r="F167" s="22" t="n"/>
-    </row>
-    <row r="168" ht="42" customHeight="1">
-      <c r="A168" s="23" t="inlineStr">
+      <c r="B189" s="22" t="n"/>
+      <c r="C189" s="22" t="n"/>
+      <c r="D189" s="22" t="n"/>
+      <c r="E189" s="22" t="n"/>
+      <c r="F189" s="22" t="n"/>
+    </row>
+    <row r="190" ht="42" customHeight="1">
+      <c r="A190" s="23" t="inlineStr">
         <is>
           <t>📖 흩어져 있던 ‘포스터 만들기’와 ‘팝업 공지 관리’를 한 곳으로 통합한 기능이에요. ①만들기 탭에서 공지·이벤트 포스터를 디자인하고, 바로 ②게시·팝업 탭으로 넘겨 우리 지사 학생 앱에 팝업으로 띄울 수 있어요.</t>
         </is>
       </c>
-      <c r="B168" s="24" t="n"/>
-      <c r="C168" s="24" t="n"/>
-      <c r="D168" s="24" t="n"/>
-      <c r="E168" s="24" t="n"/>
-      <c r="F168" s="24" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="25" t="inlineStr">
+      <c r="B190" s="24" t="n"/>
+      <c r="C190" s="24" t="n"/>
+      <c r="D190" s="24" t="n"/>
+      <c r="E190" s="24" t="n"/>
+      <c r="F190" s="24" t="n"/>
+    </row>
+    <row r="191" ht="24" customHeight="1">
+      <c r="A191" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 알림 센터 → 📢 공지…   ›   2 ①만들기   ›   3 ‘📢 팝업으로 게시’   ›   4 노출 기간·중단</t>
+        </is>
+      </c>
+      <c r="B191" s="26" t="n"/>
+      <c r="C191" s="26" t="n"/>
+      <c r="D191" s="26" t="n"/>
+      <c r="E191" s="26" t="n"/>
+      <c r="F191" s="26" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B169" s="26" t="inlineStr">
+      <c r="B192" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="30" customHeight="1">
-      <c r="A170" s="27" t="n">
+    <row r="193" ht="30" customHeight="1">
+      <c r="A193" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B170" s="28" t="inlineStr">
+      <c r="B193" s="30" t="inlineStr">
         <is>
           <t>관리자 메뉴 알림 센터 → 📢 공지 스튜디오로 들어가요.</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="30" customHeight="1">
-      <c r="A171" s="27" t="n">
+    <row r="194" ht="30" customHeight="1">
+      <c r="A194" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B171" s="28" t="inlineStr">
+      <c r="B194" s="30" t="inlineStr">
         <is>
           <t>①만들기 탭에서 문구·이미지·동영상으로 포스터를 꾸며요. (크기 조절·서버 저장·재사용 가능)</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="30" customHeight="1">
-      <c r="A172" s="27" t="n">
+    <row r="195" ht="30" customHeight="1">
+      <c r="A195" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B172" s="28" t="inlineStr">
+      <c r="B195" s="30" t="inlineStr">
         <is>
           <t>완성한 포스터의 ‘📢 팝업으로 게시’ 를 누르면 ②게시·팝업 탭으로 자동 전환돼요.</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="30" customHeight="1">
-      <c r="A173" s="27" t="n">
+    <row r="196" ht="30" customHeight="1">
+      <c r="A196" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B173" s="28" t="inlineStr">
+      <c r="B196" s="30" t="inlineStr">
         <is>
           <t>게시 탭에서 노출 기간·중단을 설정해 학생 앱 팝업으로 발행해요.</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="24" customHeight="1">
-      <c r="A174" s="29" t="inlineStr">
+    <row r="197" ht="24" customHeight="1">
+      <c r="A197" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B174" s="30" t="inlineStr">
+      <c r="B197" s="32" t="inlineStr">
         <is>
           <t>포스터 제작과 팝업 발행이 한 화면 2탭으로 이어져 헷갈리지 않아요.</t>
         </is>
       </c>
-      <c r="C174" s="31" t="n"/>
-      <c r="D174" s="31" t="n"/>
-      <c r="E174" s="31" t="n"/>
-      <c r="F174" s="31" t="n"/>
-    </row>
-    <row r="175" ht="24" customHeight="1">
-      <c r="A175" s="29" t="inlineStr">
+      <c r="C197" s="33" t="n"/>
+      <c r="D197" s="33" t="n"/>
+      <c r="E197" s="33" t="n"/>
+      <c r="F197" s="33" t="n"/>
+    </row>
+    <row r="198" ht="24" customHeight="1">
+      <c r="A198" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B175" s="30" t="inlineStr">
+      <c r="B198" s="32" t="inlineStr">
         <is>
           <t>만든 포스터는 저장해두고 재사용할 수 있어요.</t>
         </is>
       </c>
-      <c r="C175" s="31" t="n"/>
-      <c r="D175" s="31" t="n"/>
-      <c r="E175" s="31" t="n"/>
-      <c r="F175" s="31" t="n"/>
-    </row>
-    <row r="176" ht="24" customHeight="1">
-      <c r="A176" s="29" t="inlineStr">
+      <c r="C198" s="33" t="n"/>
+      <c r="D198" s="33" t="n"/>
+      <c r="E198" s="33" t="n"/>
+      <c r="F198" s="33" t="n"/>
+    </row>
+    <row r="199" ht="24" customHeight="1">
+      <c r="A199" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B176" s="30" t="inlineStr">
+      <c r="B199" s="32" t="inlineStr">
         <is>
           <t>AI 비서·사이드바 검색 어느 경로로 들어와도 올바른 탭이 열려요.</t>
         </is>
       </c>
-      <c r="C176" s="31" t="n"/>
-      <c r="D176" s="31" t="n"/>
-      <c r="E176" s="31" t="n"/>
-      <c r="F176" s="31" t="n"/>
-    </row>
-    <row r="177" ht="26" customHeight="1">
-      <c r="A177" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 기존 포스터·팝업 데이터는 그대로 유지돼요(통합만 됐고 삭제되지 않았어요).</t>
-        </is>
-      </c>
-      <c r="B177" s="35" t="n"/>
-      <c r="C177" s="35" t="n"/>
-      <c r="D177" s="35" t="n"/>
-      <c r="E177" s="35" t="n"/>
-      <c r="F177" s="35" t="n"/>
-    </row>
-    <row r="178" ht="30" customHeight="1">
-      <c r="A178" s="32" t="inlineStr">
+      <c r="C199" s="33" t="n"/>
+      <c r="D199" s="33" t="n"/>
+      <c r="E199" s="33" t="n"/>
+      <c r="F199" s="33" t="n"/>
+    </row>
+    <row r="200" ht="26" customHeight="1">
+      <c r="A200" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 기존 포스터·팝업 데이터는 그대로 유지돼요(통합만 됐고 삭제되지 않았어요).</t>
+        </is>
+      </c>
+      <c r="B200" s="37" t="n"/>
+      <c r="C200" s="37" t="n"/>
+      <c r="D200" s="37" t="n"/>
+      <c r="E200" s="37" t="n"/>
+      <c r="F200" s="37" t="n"/>
+    </row>
+    <row r="201" ht="30" customHeight="1">
+      <c r="A201" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 이벤트 홍보는 ‘만들기 → 바로 팝업 게시’ 흐름 한 번이면 끝나요.</t>
-        </is>
-      </c>
-      <c r="B178" s="33" t="n"/>
-      <c r="C178" s="33" t="n"/>
-      <c r="D178" s="33" t="n"/>
-      <c r="E178" s="33" t="n"/>
-      <c r="F178" s="33" t="n"/>
-    </row>
-    <row r="180" ht="26" customHeight="1">
-      <c r="A180" s="21" t="inlineStr">
-        <is>
-          <t>17  🤖 AI 운영비서에게 시키기  —  “○○ 화면으로 가게 해줘” 한마디로 이동</t>
-        </is>
-      </c>
-      <c r="B180" s="22" t="n"/>
-      <c r="C180" s="22" t="n"/>
-      <c r="D180" s="22" t="n"/>
-      <c r="E180" s="22" t="n"/>
-      <c r="F180" s="22" t="n"/>
-    </row>
-    <row r="181" ht="42" customHeight="1">
-      <c r="A181" s="23" t="inlineStr">
-        <is>
-          <t>📖 상단 통합 검색창(또는 우하단 AI 운영비서) 에 하고 싶은 일을 자연스럽게 말하면, AI가 알아듣고 바로 그 화면으로 이동시켜줘요. 이제 ‘○○ 강사 스케줄로 가게 해줘’, ‘자동 스케줄링 열어줘’ 같은 이동 명령을 정확히 따라요.</t>
-        </is>
-      </c>
-      <c r="B181" s="24" t="n"/>
-      <c r="C181" s="24" t="n"/>
-      <c r="D181" s="24" t="n"/>
-      <c r="E181" s="24" t="n"/>
-      <c r="F181" s="24" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="25" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="B182" s="26" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="30" customHeight="1">
-      <c r="A183" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B183" s="28" t="inlineStr">
-        <is>
-          <t>상단 검색창에 명령을 입력하거나 🎤 마이크로 말해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="30" customHeight="1">
-      <c r="A184" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B184" s="28" t="inlineStr">
-        <is>
-          <t>예: “김민지 강사 스케줄로 가게 해줘” → 주간 스케줄에서 해당 강사를 자동으로 찾아 열어줘요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="30" customHeight="1">
-      <c r="A185" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B185" s="28" t="inlineStr">
-        <is>
-          <t>예: “자동 스케줄링 열어줘”, “정산 화면으로” 처럼 메뉴 이동을 시켜요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="30" customHeight="1">
-      <c r="A186" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B186" s="28" t="inlineStr">
-        <is>
-          <t>AI 응답 카드의 ‘지금 이동 →’ 을 누르면 해당 화면으로 넘어가요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="24" customHeight="1">
-      <c r="A187" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B187" s="30" t="inlineStr">
-        <is>
-          <t>이동 명령은 확실히 이동하고, 설명만 하고 마는 일이 줄었어요.</t>
-        </is>
-      </c>
-      <c r="C187" s="31" t="n"/>
-      <c r="D187" s="31" t="n"/>
-      <c r="E187" s="31" t="n"/>
-      <c r="F187" s="31" t="n"/>
-    </row>
-    <row r="188" ht="24" customHeight="1">
-      <c r="A188" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B188" s="30" t="inlineStr">
-        <is>
-          <t>강사 이름으로 스케줄을 검색하면 검색창 자동 채움 + 필터 + 스크롤까지 돼요.</t>
-        </is>
-      </c>
-      <c r="C188" s="31" t="n"/>
-      <c r="D188" s="31" t="n"/>
-      <c r="E188" s="31" t="n"/>
-      <c r="F188" s="31" t="n"/>
-    </row>
-    <row r="189" ht="24" customHeight="1">
-      <c r="A189" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B189" s="30" t="inlineStr">
-        <is>
-          <t>데이터 조회·통계 질문에는 카드형 답변으로도 도와줘요.</t>
-        </is>
-      </c>
-      <c r="C189" s="31" t="n"/>
-      <c r="D189" s="31" t="n"/>
-      <c r="E189" s="31" t="n"/>
-      <c r="F189" s="31" t="n"/>
-    </row>
-    <row r="190" ht="26" customHeight="1">
-      <c r="A190" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · ‘등록·발송·변경’처럼 실제로 무언가를 바꾸는 명령은 한 번 더 확인해요(안전장치).</t>
-        </is>
-      </c>
-      <c r="B190" s="35" t="n"/>
-      <c r="C190" s="35" t="n"/>
-      <c r="D190" s="35" t="n"/>
-      <c r="E190" s="35" t="n"/>
-      <c r="F190" s="35" t="n"/>
-    </row>
-    <row r="191" ht="30" customHeight="1">
-      <c r="A191" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 메뉴 이름이 기억나지 않을 땐 하고 싶은 일을 그대로 말해보세요 — 알아서 찾아가요.</t>
-        </is>
-      </c>
-      <c r="B191" s="33" t="n"/>
-      <c r="C191" s="33" t="n"/>
-      <c r="D191" s="33" t="n"/>
-      <c r="E191" s="33" t="n"/>
-      <c r="F191" s="33" t="n"/>
-    </row>
-    <row r="193" ht="26" customHeight="1">
-      <c r="A193" s="21" t="inlineStr">
-        <is>
-          <t>18  💬 자료실 카카오톡 링크 공유  —  영상·문서를 원본 화질 그대로 카톡으로</t>
-        </is>
-      </c>
-      <c r="B193" s="22" t="n"/>
-      <c r="C193" s="22" t="n"/>
-      <c r="D193" s="22" t="n"/>
-      <c r="E193" s="22" t="n"/>
-      <c r="F193" s="22" t="n"/>
-    </row>
-    <row r="194" ht="42" customHeight="1">
-      <c r="A194" s="23" t="inlineStr">
-        <is>
-          <t>📖 자료실의 설명서·영상마다 ‘💬 카톡 링크복사’ 버튼이 생겼어요. 카카오톡에 파일을 첨부하면 화질이 눌리지만, 링크로 보내면 원본 화질 그대로 재생돼요. 버튼 한 번으로 링크가 복사되니 학부모·강사 안내가 훨씬 쉬워요.</t>
-        </is>
-      </c>
-      <c r="B194" s="24" t="n"/>
-      <c r="C194" s="24" t="n"/>
-      <c r="D194" s="24" t="n"/>
-      <c r="E194" s="24" t="n"/>
-      <c r="F194" s="24" t="n"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="25" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="B195" s="26" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="30" customHeight="1">
-      <c r="A196" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B196" s="28" t="inlineStr">
-        <is>
-          <t>관리자 자료실에서 공유할 파일 옆 💬 카톡 링크복사를 눌러요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="30" customHeight="1">
-      <c r="A197" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B197" s="28" t="inlineStr">
-        <is>
-          <t>카카오톡 대화방에 붙여넣기로 보내요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="30" customHeight="1">
-      <c r="A198" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B198" s="28" t="inlineStr">
-        <is>
-          <t>받는 사람은 링크를 눌러 원본 화질로 바로 보거나 내려받아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="24" customHeight="1">
-      <c r="A199" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B199" s="30" t="inlineStr">
-        <is>
-          <t>동영상은 링크 공유 = 원본 화질, 파일 첨부는 화질이 떨어져요.</t>
-        </is>
-      </c>
-      <c r="C199" s="31" t="n"/>
-      <c r="D199" s="31" t="n"/>
-      <c r="E199" s="31" t="n"/>
-      <c r="F199" s="31" t="n"/>
-    </row>
-    <row r="200" ht="24" customHeight="1">
-      <c r="A200" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B200" s="30" t="inlineStr">
-        <is>
-          <t>설명서 PDF·PPT·영상 등 자료실 어디서나 같은 방식으로 공유돼요.</t>
-        </is>
-      </c>
-      <c r="C200" s="31" t="n"/>
-      <c r="D200" s="31" t="n"/>
-      <c r="E200" s="31" t="n"/>
-      <c r="F200" s="31" t="n"/>
-    </row>
-    <row r="201" ht="26" customHeight="1">
-      <c r="A201" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 링크를 받은 사람은 누구나 열 수 있어요. 내부용 자료는 공유 대상을 확인하세요.</t>
         </is>
       </c>
       <c r="B201" s="35" t="n"/>
@@ -4138,306 +5040,304 @@
       <c r="E201" s="35" t="n"/>
       <c r="F201" s="35" t="n"/>
     </row>
-    <row r="202" ht="30" customHeight="1">
-      <c r="A202" s="32" t="inlineStr">
+    <row r="203" ht="26" customHeight="1">
+      <c r="A203" s="21" t="inlineStr">
+        <is>
+          <t>17  🤖 AI 운영비서에게 시키기  —  “○○ 화면으로 가게 해줘” 한마디로 이동</t>
+        </is>
+      </c>
+      <c r="B203" s="22" t="n"/>
+      <c r="C203" s="22" t="n"/>
+      <c r="D203" s="22" t="n"/>
+      <c r="E203" s="22" t="n"/>
+      <c r="F203" s="22" t="n"/>
+    </row>
+    <row r="204" ht="42" customHeight="1">
+      <c r="A204" s="23" t="inlineStr">
+        <is>
+          <t>📖 상단 통합 검색창(또는 우하단 AI 운영비서) 에 하고 싶은 일을 자연스럽게 말하면, AI가 알아듣고 바로 그 화면으로 이동시켜줘요. 이제 ‘○○ 강사 스케줄로 가게 해줘’, ‘자동 스케줄링 열어줘’ 같은 이동 명령을 정확히 따라요.</t>
+        </is>
+      </c>
+      <c r="B204" s="24" t="n"/>
+      <c r="C204" s="24" t="n"/>
+      <c r="D204" s="24" t="n"/>
+      <c r="E204" s="24" t="n"/>
+      <c r="F204" s="24" t="n"/>
+    </row>
+    <row r="205" ht="24" customHeight="1">
+      <c r="A205" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 검색창   ›   2 “김민지 강사 스케줄로…   ›   3 “자동 스케줄링 열어줘”…   ›   4 ‘지금 이동 →’</t>
+        </is>
+      </c>
+      <c r="B205" s="26" t="n"/>
+      <c r="C205" s="26" t="n"/>
+      <c r="D205" s="26" t="n"/>
+      <c r="E205" s="26" t="n"/>
+      <c r="F205" s="26" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B206" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="30" customHeight="1">
+      <c r="A207" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B207" s="30" t="inlineStr">
+        <is>
+          <t>상단 검색창에 명령을 입력하거나 🎤 마이크로 말해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="30" customHeight="1">
+      <c r="A208" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B208" s="30" t="inlineStr">
+        <is>
+          <t>예: “김민지 강사 스케줄로 가게 해줘” → 주간 스케줄에서 해당 강사를 자동으로 찾아 열어줘요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="30" customHeight="1">
+      <c r="A209" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B209" s="30" t="inlineStr">
+        <is>
+          <t>예: “자동 스케줄링 열어줘”, “정산 화면으로” 처럼 메뉴 이동을 시켜요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="30" customHeight="1">
+      <c r="A210" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B210" s="30" t="inlineStr">
+        <is>
+          <t>AI 응답 카드의 ‘지금 이동 →’ 을 누르면 해당 화면으로 넘어가요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="24" customHeight="1">
+      <c r="A211" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B211" s="32" t="inlineStr">
+        <is>
+          <t>이동 명령은 확실히 이동하고, 설명만 하고 마는 일이 줄었어요.</t>
+        </is>
+      </c>
+      <c r="C211" s="33" t="n"/>
+      <c r="D211" s="33" t="n"/>
+      <c r="E211" s="33" t="n"/>
+      <c r="F211" s="33" t="n"/>
+    </row>
+    <row r="212" ht="24" customHeight="1">
+      <c r="A212" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B212" s="32" t="inlineStr">
+        <is>
+          <t>강사 이름으로 스케줄을 검색하면 검색창 자동 채움 + 필터 + 스크롤까지 돼요.</t>
+        </is>
+      </c>
+      <c r="C212" s="33" t="n"/>
+      <c r="D212" s="33" t="n"/>
+      <c r="E212" s="33" t="n"/>
+      <c r="F212" s="33" t="n"/>
+    </row>
+    <row r="213" ht="24" customHeight="1">
+      <c r="A213" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B213" s="32" t="inlineStr">
+        <is>
+          <t>데이터 조회·통계 질문에는 카드형 답변으로도 도와줘요.</t>
+        </is>
+      </c>
+      <c r="C213" s="33" t="n"/>
+      <c r="D213" s="33" t="n"/>
+      <c r="E213" s="33" t="n"/>
+      <c r="F213" s="33" t="n"/>
+    </row>
+    <row r="214" ht="26" customHeight="1">
+      <c r="A214" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · ‘등록·발송·변경’처럼 실제로 무언가를 바꾸는 명령은 한 번 더 확인해요(안전장치).</t>
+        </is>
+      </c>
+      <c r="B214" s="37" t="n"/>
+      <c r="C214" s="37" t="n"/>
+      <c r="D214" s="37" t="n"/>
+      <c r="E214" s="37" t="n"/>
+      <c r="F214" s="37" t="n"/>
+    </row>
+    <row r="215" ht="30" customHeight="1">
+      <c r="A215" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 메뉴 이름이 기억나지 않을 땐 하고 싶은 일을 그대로 말해보세요 — 알아서 찾아가요.</t>
+        </is>
+      </c>
+      <c r="B215" s="35" t="n"/>
+      <c r="C215" s="35" t="n"/>
+      <c r="D215" s="35" t="n"/>
+      <c r="E215" s="35" t="n"/>
+      <c r="F215" s="35" t="n"/>
+    </row>
+    <row r="217" ht="26" customHeight="1">
+      <c r="A217" s="21" t="inlineStr">
+        <is>
+          <t>18  💬 자료실 카카오톡 링크 공유  —  영상·문서를 원본 화질 그대로 카톡으로</t>
+        </is>
+      </c>
+      <c r="B217" s="22" t="n"/>
+      <c r="C217" s="22" t="n"/>
+      <c r="D217" s="22" t="n"/>
+      <c r="E217" s="22" t="n"/>
+      <c r="F217" s="22" t="n"/>
+    </row>
+    <row r="218" ht="42" customHeight="1">
+      <c r="A218" s="23" t="inlineStr">
+        <is>
+          <t>📖 자료실의 설명서·영상마다 ‘💬 카톡 링크복사’ 버튼이 생겼어요. 카카오톡에 파일을 첨부하면 화질이 눌리지만, 링크로 보내면 원본 화질 그대로 재생돼요. 버튼 한 번으로 링크가 복사되니 학부모·강사 안내가 훨씬 쉬워요.</t>
+        </is>
+      </c>
+      <c r="B218" s="24" t="n"/>
+      <c r="C218" s="24" t="n"/>
+      <c r="D218" s="24" t="n"/>
+      <c r="E218" s="24" t="n"/>
+      <c r="F218" s="24" t="n"/>
+    </row>
+    <row r="219" ht="24" customHeight="1">
+      <c r="A219" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 자료실   ›   2 붙여넣기   ›   3 원본 화질</t>
+        </is>
+      </c>
+      <c r="B219" s="26" t="n"/>
+      <c r="C219" s="26" t="n"/>
+      <c r="D219" s="26" t="n"/>
+      <c r="E219" s="26" t="n"/>
+      <c r="F219" s="26" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B220" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="30" customHeight="1">
+      <c r="A221" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B221" s="30" t="inlineStr">
+        <is>
+          <t>관리자 자료실에서 공유할 파일 옆 💬 카톡 링크복사를 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="30" customHeight="1">
+      <c r="A222" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B222" s="30" t="inlineStr">
+        <is>
+          <t>카카오톡 대화방에 붙여넣기로 보내요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="30" customHeight="1">
+      <c r="A223" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B223" s="30" t="inlineStr">
+        <is>
+          <t>받는 사람은 링크를 눌러 원본 화질로 바로 보거나 내려받아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="24" customHeight="1">
+      <c r="A224" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B224" s="32" t="inlineStr">
+        <is>
+          <t>동영상은 링크 공유 = 원본 화질, 파일 첨부는 화질이 떨어져요.</t>
+        </is>
+      </c>
+      <c r="C224" s="33" t="n"/>
+      <c r="D224" s="33" t="n"/>
+      <c r="E224" s="33" t="n"/>
+      <c r="F224" s="33" t="n"/>
+    </row>
+    <row r="225" ht="24" customHeight="1">
+      <c r="A225" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B225" s="32" t="inlineStr">
+        <is>
+          <t>설명서 PDF·PPT·영상 등 자료실 어디서나 같은 방식으로 공유돼요.</t>
+        </is>
+      </c>
+      <c r="C225" s="33" t="n"/>
+      <c r="D225" s="33" t="n"/>
+      <c r="E225" s="33" t="n"/>
+      <c r="F225" s="33" t="n"/>
+    </row>
+    <row r="226" ht="26" customHeight="1">
+      <c r="A226" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 링크를 받은 사람은 누구나 열 수 있어요. 내부용 자료는 공유 대상을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="B226" s="37" t="n"/>
+      <c r="C226" s="37" t="n"/>
+      <c r="D226" s="37" t="n"/>
+      <c r="E226" s="37" t="n"/>
+      <c r="F226" s="37" t="n"/>
+    </row>
+    <row r="227" ht="30" customHeight="1">
+      <c r="A227" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 학부모 단체방에는 영상 설명서 링크 하나면 안내가 끝나요.</t>
         </is>
       </c>
-      <c r="B202" s="33" t="n"/>
-      <c r="C202" s="33" t="n"/>
-      <c r="D202" s="33" t="n"/>
-      <c r="E202" s="33" t="n"/>
-      <c r="F202" s="33" t="n"/>
-    </row>
-    <row r="204" ht="26" customHeight="1">
-      <c r="A204" s="21" t="inlineStr">
-        <is>
-          <t>19  🧭 새로워진 관리자 화면  —  사이드바 접기 · 밝은 배경 · 선 아이콘</t>
-        </is>
-      </c>
-      <c r="B204" s="22" t="n"/>
-      <c r="C204" s="22" t="n"/>
-      <c r="D204" s="22" t="n"/>
-      <c r="E204" s="22" t="n"/>
-      <c r="F204" s="22" t="n"/>
-    </row>
-    <row r="205" ht="42" customHeight="1">
-      <c r="A205" s="23" t="inlineStr">
-        <is>
-          <t>📖 관리자 화면이 눈이 편하고 넓게 바뀌었습니다. 왼쪽 메뉴는 ‹ 접기 버튼으로 아이콘만 남는 좁은 띠(레일) 로 접히고, 배경은 밝은 톤으로 통일됐어요. 메뉴 아이콘도 선(라인) 아이콘으로 정리해 글자가 잘 읽힙니다.</t>
-        </is>
-      </c>
-      <c r="B205" s="24" t="n"/>
-      <c r="C205" s="24" t="n"/>
-      <c r="D205" s="24" t="n"/>
-      <c r="E205" s="24" t="n"/>
-      <c r="F205" s="24" t="n"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="25" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="B206" s="26" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="30" customHeight="1">
-      <c r="A207" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B207" s="28" t="inlineStr">
-        <is>
-          <t>왼쪽 메뉴 맨 위의 ‹ 접기를 눌러요. 메뉴가 아이콘 띠로 줄어들며 본문이 넓어져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="30" customHeight="1">
-      <c r="A208" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B208" s="28" t="inlineStr">
-        <is>
-          <t>다시 펼치려면 같은 자리의 › 버튼을 눌러요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="30" customHeight="1">
-      <c r="A209" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B209" s="28" t="inlineStr">
-        <is>
-          <t>접은 상태는 다음 접속 때도 그대로 기억됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="30" customHeight="1">
-      <c r="A210" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B210" s="28" t="inlineStr">
-        <is>
-          <t>메뉴가 많아 찾기 어려우면 위쪽 메뉴 검색에 이름을 쳐 보세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="24" customHeight="1">
-      <c r="A211" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B211" s="30" t="inlineStr">
-        <is>
-          <t>표·목록이 많은 화면에서 가로 공간이 크게 늘어나요.</t>
-        </is>
-      </c>
-      <c r="C211" s="31" t="n"/>
-      <c r="D211" s="31" t="n"/>
-      <c r="E211" s="31" t="n"/>
-      <c r="F211" s="31" t="n"/>
-    </row>
-    <row r="212" ht="24" customHeight="1">
-      <c r="A212" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B212" s="30" t="inlineStr">
-        <is>
-          <t>하위 메뉴 15장까지 밝은 테마로 통일돼 화면 간 색 차이가 사라졌어요.</t>
-        </is>
-      </c>
-      <c r="C212" s="31" t="n"/>
-      <c r="D212" s="31" t="n"/>
-      <c r="E212" s="31" t="n"/>
-      <c r="F212" s="31" t="n"/>
-    </row>
-    <row r="213" ht="24" customHeight="1">
-      <c r="A213" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B213" s="30" t="inlineStr">
-        <is>
-          <t>저사양 PC에서도 버벅이지 않도록 접기 애니메이션을 없앴습니다.</t>
-        </is>
-      </c>
-      <c r="C213" s="31" t="n"/>
-      <c r="D213" s="31" t="n"/>
-      <c r="E213" s="31" t="n"/>
-      <c r="F213" s="31" t="n"/>
-    </row>
-    <row r="214" ht="30" customHeight="1">
-      <c r="A214" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 정산·급여처럼 표가 넓은 화면은 접어 놓고 보면 훨씬 편합니다.</t>
-        </is>
-      </c>
-      <c r="B214" s="33" t="n"/>
-      <c r="C214" s="33" t="n"/>
-      <c r="D214" s="33" t="n"/>
-      <c r="E214" s="33" t="n"/>
-      <c r="F214" s="33" t="n"/>
-    </row>
-    <row r="216" ht="26" customHeight="1">
-      <c r="A216" s="21" t="inlineStr">
-        <is>
-          <t>20  🌐 화면 언어가 자동으로 맞춰져요  —  해외 스태프·강사는 영어로 시작</t>
-        </is>
-      </c>
-      <c r="B216" s="22" t="n"/>
-      <c r="C216" s="22" t="n"/>
-      <c r="D216" s="22" t="n"/>
-      <c r="E216" s="22" t="n"/>
-      <c r="F216" s="22" t="n"/>
-    </row>
-    <row r="217" ht="42" customHeight="1">
-      <c r="A217" s="23" t="inlineStr">
-        <is>
-          <t>📖 필리핀 강사와 해외 스태프가 처음부터 영어 화면으로 시작합니다. 계정의 국적 정보를 기준으로 화면 언어가 정해지고, 강사 계정은 이름·이전 선택과 무관하게 항상 영어로 뜹니다. 물론 상단 🌐 EN / KR 버튼으로 언제든 직접 바꿀 수 있어요.</t>
-        </is>
-      </c>
-      <c r="B217" s="24" t="n"/>
-      <c r="C217" s="24" t="n"/>
-      <c r="D217" s="24" t="n"/>
-      <c r="E217" s="24" t="n"/>
-      <c r="F217" s="24" t="n"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="25" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="B218" s="26" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" ht="30" customHeight="1">
-      <c r="A219" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B219" s="28" t="inlineStr">
-        <is>
-          <t>계정에 국적이 등록돼 있으면 로그인할 때 자동으로 맞는 언어가 뜹니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="30" customHeight="1">
-      <c r="A220" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B220" s="28" t="inlineStr">
-        <is>
-          <t>직접 바꾸려면 상단의 🌐 EN / KR 버튼을 눌러요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="30" customHeight="1">
-      <c r="A221" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B221" s="28" t="inlineStr">
-        <is>
-          <t>직접 고른 언어는 그 계정에만 저장돼요 — 같은 PC를 여러 명이 써도 섞이지 않습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="30" customHeight="1">
-      <c r="A222" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B222" s="28" t="inlineStr">
-        <is>
-          <t>강사용 안내 슬라이드·안내서도 영어판으로 함께 바뀝니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" ht="24" customHeight="1">
-      <c r="A223" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B223" s="30" t="inlineStr">
-        <is>
-          <t>강사 계정은 무조건 영어 — 한국어 화면 때문에 헤매는 일이 없어요.</t>
-        </is>
-      </c>
-      <c r="C223" s="31" t="n"/>
-      <c r="D223" s="31" t="n"/>
-      <c r="E223" s="31" t="n"/>
-      <c r="F223" s="31" t="n"/>
-    </row>
-    <row r="224" ht="24" customHeight="1">
-      <c r="A224" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B224" s="30" t="inlineStr">
-        <is>
-          <t>이름에 붙은 한글 직함 때문에 영문 이름 계정이 한국어로 뜨던 문제도 고쳤어요.</t>
-        </is>
-      </c>
-      <c r="C224" s="31" t="n"/>
-      <c r="D224" s="31" t="n"/>
-      <c r="E224" s="31" t="n"/>
-      <c r="F224" s="31" t="n"/>
-    </row>
-    <row r="225" ht="24" customHeight="1">
-      <c r="A225" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B225" s="30" t="inlineStr">
-        <is>
-          <t>언어 선택이 계정별로 분리돼 해외 계정이 남의 선택에 덮이지 않아요.</t>
-        </is>
-      </c>
-      <c r="C225" s="31" t="n"/>
-      <c r="D225" s="31" t="n"/>
-      <c r="E225" s="31" t="n"/>
-      <c r="F225" s="31" t="n"/>
-    </row>
-    <row r="226" ht="26" customHeight="1">
-      <c r="A226" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 국적이 비어 있는 계정은 기존 방식(이름·아이디 규칙)으로 판단합니다. 강사 등록 시 국적을 꼭 넣어 주세요.</t>
-        </is>
-      </c>
-      <c r="B226" s="35" t="n"/>
-      <c r="C226" s="35" t="n"/>
-      <c r="D226" s="35" t="n"/>
-      <c r="E226" s="35" t="n"/>
-      <c r="F226" s="35" t="n"/>
-    </row>
-    <row r="227" ht="30" customHeight="1">
-      <c r="A227" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 새 강사를 등록할 때 국적을 함께 입력하면 첫 로그인부터 영어 화면으로 시작해 문의가 줄어듭니다.</t>
-        </is>
-      </c>
-      <c r="B227" s="33" t="n"/>
-      <c r="C227" s="33" t="n"/>
-      <c r="D227" s="33" t="n"/>
-      <c r="E227" s="33" t="n"/>
-      <c r="F227" s="33" t="n"/>
+      <c r="B227" s="35" t="n"/>
+      <c r="C227" s="35" t="n"/>
+      <c r="D227" s="35" t="n"/>
+      <c r="E227" s="35" t="n"/>
+      <c r="F227" s="35" t="n"/>
     </row>
     <row r="229" ht="26" customHeight="1">
       <c r="A229" s="21" t="inlineStr">
         <is>
-          <t>21  💳 수강 등록 · 결제 → 수업 자동 생성  —  결제 확정되면 회차 전량이 자동으로 잡힙니다</t>
+          <t>19  🧭 새로워진 관리자 화면  —  사이드바 접기 · 밝은 배경 · 선 아이콘</t>
         </is>
       </c>
       <c r="B229" s="22" t="n"/>
@@ -4449,7 +5349,7 @@
     <row r="230" ht="42" customHeight="1">
       <c r="A230" s="23" t="inlineStr">
         <is>
-          <t>📖 수강신청 화면에서 학생이 강사·요일·시간을 고르고 결제하면, 결제 확정 시점에 수업 회차가 전량 자동 생성됩니다. 예전처럼 결제 확인 후 사람이 일일이 시간표를 넣던 작업이 사라졌어요. 같은 시간에 이미 잡힌 수업이 있으면 결제 전에 충돌을 감지해 알려 줍니다.</t>
+          <t>📖 관리자 화면이 눈이 편하고 넓게 바뀌었습니다. 왼쪽 메뉴는 ‹ 접기 버튼으로 아이콘만 남는 좁은 띠(레일) 로 접히고, 배경은 밝은 톤으로 통일됐어요. 메뉴 아이콘도 선(라인) 아이콘으로 정리해 글자가 잘 읽힙니다.</t>
         </is>
       </c>
       <c r="B230" s="24" t="n"/>
@@ -4458,120 +5358,122 @@
       <c r="E230" s="24" t="n"/>
       <c r="F230" s="24" t="n"/>
     </row>
-    <row r="231">
+    <row r="231" ht="24" customHeight="1">
       <c r="A231" s="25" t="inlineStr">
         <is>
+          <t>🧭  1 ‹ 접기   ›   2 › 버튼   ›   3 다음 접속 때도 그대로…   ›   4 메뉴 검색</t>
+        </is>
+      </c>
+      <c r="B231" s="26" t="n"/>
+      <c r="C231" s="26" t="n"/>
+      <c r="D231" s="26" t="n"/>
+      <c r="E231" s="26" t="n"/>
+      <c r="F231" s="26" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="27" t="inlineStr">
+        <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B231" s="26" t="inlineStr">
+      <c r="B232" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="232" ht="30" customHeight="1">
-      <c r="A232" s="27" t="n">
+    <row r="233" ht="30" customHeight="1">
+      <c r="A233" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B232" s="28" t="inlineStr">
-        <is>
-          <t>학생·학부모에게 수강신청 링크를 안내해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="30" customHeight="1">
-      <c r="A233" s="27" t="n">
+      <c r="B233" s="30" t="inlineStr">
+        <is>
+          <t>왼쪽 메뉴 맨 위의 ‹ 접기를 눌러요. 메뉴가 아이콘 띠로 줄어들며 본문이 넓어져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="30" customHeight="1">
+      <c r="A234" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B233" s="28" t="inlineStr">
-        <is>
-          <t>학생이 강사 → 수업 옵션(주 횟수·기간·수업 길이) → 요일·시간 순으로 고릅니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="30" customHeight="1">
-      <c r="A234" s="27" t="n">
+      <c r="B234" s="30" t="inlineStr">
+        <is>
+          <t>다시 펼치려면 같은 자리의 › 버튼을 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="30" customHeight="1">
+      <c r="A235" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B234" s="28" t="inlineStr">
-        <is>
-          <t>시간 확인이 통과돼야 결제 버튼이 열립니다(충돌 시 결제 불가).</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" ht="30" customHeight="1">
-      <c r="A235" s="27" t="n">
+      <c r="B235" s="30" t="inlineStr">
+        <is>
+          <t>접은 상태는 다음 접속 때도 그대로 기억됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="30" customHeight="1">
+      <c r="A236" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B235" s="28" t="inlineStr">
-        <is>
-          <t>결제가 확정되면 회차가 한꺼번에 생성됩니다. 관리자 화면 수업 목록에서 확인해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="30" customHeight="1">
-      <c r="A236" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="B236" s="28" t="inlineStr">
-        <is>
-          <t>본사 단가·할인율은 단가표 화면에서 관리합니다.</t>
+      <c r="B236" s="30" t="inlineStr">
+        <is>
+          <t>메뉴가 많아 찾기 어려우면 위쪽 메뉴 검색에 이름을 쳐 보세요.</t>
         </is>
       </c>
     </row>
     <row r="237" ht="24" customHeight="1">
-      <c r="A237" s="29" t="inlineStr">
+      <c r="A237" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B237" s="30" t="inlineStr">
-        <is>
-          <t>멱등 처리돼서 결제 알림이 중복 들어와도 회차가 두 번 생기지 않아요.</t>
-        </is>
-      </c>
-      <c r="C237" s="31" t="n"/>
-      <c r="D237" s="31" t="n"/>
-      <c r="E237" s="31" t="n"/>
-      <c r="F237" s="31" t="n"/>
+      <c r="B237" s="32" t="inlineStr">
+        <is>
+          <t>표·목록이 많은 화면에서 가로 공간이 크게 늘어나요.</t>
+        </is>
+      </c>
+      <c r="C237" s="33" t="n"/>
+      <c r="D237" s="33" t="n"/>
+      <c r="E237" s="33" t="n"/>
+      <c r="F237" s="33" t="n"/>
     </row>
     <row r="238" ht="24" customHeight="1">
-      <c r="A238" s="29" t="inlineStr">
+      <c r="A238" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B238" s="30" t="inlineStr">
-        <is>
-          <t>공휴일·기존 수업과 겹치면 뒤로 밀어서 회차 수를 채웁니다.</t>
-        </is>
-      </c>
-      <c r="C238" s="31" t="n"/>
-      <c r="D238" s="31" t="n"/>
-      <c r="E238" s="31" t="n"/>
-      <c r="F238" s="31" t="n"/>
+      <c r="B238" s="32" t="inlineStr">
+        <is>
+          <t>하위 메뉴 15장까지 밝은 테마로 통일돼 화면 간 색 차이가 사라졌어요.</t>
+        </is>
+      </c>
+      <c r="C238" s="33" t="n"/>
+      <c r="D238" s="33" t="n"/>
+      <c r="E238" s="33" t="n"/>
+      <c r="F238" s="33" t="n"/>
     </row>
     <row r="239" ht="24" customHeight="1">
-      <c r="A239" s="29" t="inlineStr">
+      <c r="A239" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B239" s="30" t="inlineStr">
-        <is>
-          <t>기간 할인(6개월 -5% · 12개월 -10%)이 금액에 자동 반영됩니다.</t>
-        </is>
-      </c>
-      <c r="C239" s="31" t="n"/>
-      <c r="D239" s="31" t="n"/>
-      <c r="E239" s="31" t="n"/>
-      <c r="F239" s="31" t="n"/>
-    </row>
-    <row r="240" ht="26" customHeight="1">
+      <c r="B239" s="32" t="inlineStr">
+        <is>
+          <t>저사양 PC에서도 버벅이지 않도록 접기 애니메이션을 없앴습니다.</t>
+        </is>
+      </c>
+      <c r="C239" s="33" t="n"/>
+      <c r="D239" s="33" t="n"/>
+      <c r="E239" s="33" t="n"/>
+      <c r="F239" s="33" t="n"/>
+    </row>
+    <row r="240" ht="30" customHeight="1">
       <c r="A240" s="34" t="inlineStr">
         <is>
-          <t>⚠️ 알아두기 · 현재는 1단계(등록 → 결제 → 회차 자동 생성) 까지 열려 있습니다. 이후 단계는 순차 반영 예정입니다.</t>
+          <t>💡 꿀팁 · 정산·급여처럼 표가 넓은 화면은 접어 놓고 보면 훨씬 편합니다.</t>
         </is>
       </c>
       <c r="B240" s="35" t="n"/>
@@ -4580,590 +5482,2113 @@
       <c r="E240" s="35" t="n"/>
       <c r="F240" s="35" t="n"/>
     </row>
-    <row r="241" ht="30" customHeight="1">
-      <c r="A241" s="32" t="inlineStr">
+    <row r="242" ht="26" customHeight="1">
+      <c r="A242" s="21" t="inlineStr">
+        <is>
+          <t>20  🌐 화면 언어가 자동으로 맞춰져요  —  해외 스태프·강사는 영어로 시작</t>
+        </is>
+      </c>
+      <c r="B242" s="22" t="n"/>
+      <c r="C242" s="22" t="n"/>
+      <c r="D242" s="22" t="n"/>
+      <c r="E242" s="22" t="n"/>
+      <c r="F242" s="22" t="n"/>
+    </row>
+    <row r="243" ht="42" customHeight="1">
+      <c r="A243" s="23" t="inlineStr">
+        <is>
+          <t>📖 필리핀 강사와 해외 스태프가 처음부터 영어 화면으로 시작합니다. 계정의 국적 정보를 기준으로 화면 언어가 정해지고, 강사 계정은 이름·이전 선택과 무관하게 항상 영어로 뜹니다. 물론 상단 🌐 EN / KR 버튼으로 언제든 직접 바꿀 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B243" s="24" t="n"/>
+      <c r="C243" s="24" t="n"/>
+      <c r="D243" s="24" t="n"/>
+      <c r="E243" s="24" t="n"/>
+      <c r="F243" s="24" t="n"/>
+    </row>
+    <row r="244" ht="24" customHeight="1">
+      <c r="A244" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 국적   ›   2 🌐 EN / KR   ›   3 그 계정에만   ›   4 영어판으로 함께</t>
+        </is>
+      </c>
+      <c r="B244" s="26" t="n"/>
+      <c r="C244" s="26" t="n"/>
+      <c r="D244" s="26" t="n"/>
+      <c r="E244" s="26" t="n"/>
+      <c r="F244" s="26" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B245" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="30" customHeight="1">
+      <c r="A246" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B246" s="30" t="inlineStr">
+        <is>
+          <t>계정에 국적이 등록돼 있으면 로그인할 때 자동으로 맞는 언어가 뜹니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="30" customHeight="1">
+      <c r="A247" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B247" s="30" t="inlineStr">
+        <is>
+          <t>직접 바꾸려면 상단의 🌐 EN / KR 버튼을 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="30" customHeight="1">
+      <c r="A248" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B248" s="30" t="inlineStr">
+        <is>
+          <t>직접 고른 언어는 그 계정에만 저장돼요 — 같은 PC를 여러 명이 써도 섞이지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="30" customHeight="1">
+      <c r="A249" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B249" s="30" t="inlineStr">
+        <is>
+          <t>강사용 안내 슬라이드·안내서도 영어판으로 함께 바뀝니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="24" customHeight="1">
+      <c r="A250" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B250" s="32" t="inlineStr">
+        <is>
+          <t>강사 계정은 무조건 영어 — 한국어 화면 때문에 헤매는 일이 없어요.</t>
+        </is>
+      </c>
+      <c r="C250" s="33" t="n"/>
+      <c r="D250" s="33" t="n"/>
+      <c r="E250" s="33" t="n"/>
+      <c r="F250" s="33" t="n"/>
+    </row>
+    <row r="251" ht="24" customHeight="1">
+      <c r="A251" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B251" s="32" t="inlineStr">
+        <is>
+          <t>이름에 붙은 한글 직함 때문에 영문 이름 계정이 한국어로 뜨던 문제도 고쳤어요.</t>
+        </is>
+      </c>
+      <c r="C251" s="33" t="n"/>
+      <c r="D251" s="33" t="n"/>
+      <c r="E251" s="33" t="n"/>
+      <c r="F251" s="33" t="n"/>
+    </row>
+    <row r="252" ht="24" customHeight="1">
+      <c r="A252" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B252" s="32" t="inlineStr">
+        <is>
+          <t>언어 선택이 계정별로 분리돼 해외 계정이 남의 선택에 덮이지 않아요.</t>
+        </is>
+      </c>
+      <c r="C252" s="33" t="n"/>
+      <c r="D252" s="33" t="n"/>
+      <c r="E252" s="33" t="n"/>
+      <c r="F252" s="33" t="n"/>
+    </row>
+    <row r="253" ht="26" customHeight="1">
+      <c r="A253" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 국적이 비어 있는 계정은 기존 방식(이름·아이디 규칙)으로 판단합니다. 강사 등록 시 국적을 꼭 넣어 주세요.</t>
+        </is>
+      </c>
+      <c r="B253" s="37" t="n"/>
+      <c r="C253" s="37" t="n"/>
+      <c r="D253" s="37" t="n"/>
+      <c r="E253" s="37" t="n"/>
+      <c r="F253" s="37" t="n"/>
+    </row>
+    <row r="254" ht="30" customHeight="1">
+      <c r="A254" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 새 강사를 등록할 때 국적을 함께 입력하면 첫 로그인부터 영어 화면으로 시작해 문의가 줄어듭니다.</t>
+        </is>
+      </c>
+      <c r="B254" s="35" t="n"/>
+      <c r="C254" s="35" t="n"/>
+      <c r="D254" s="35" t="n"/>
+      <c r="E254" s="35" t="n"/>
+      <c r="F254" s="35" t="n"/>
+    </row>
+    <row r="256" ht="26" customHeight="1">
+      <c r="A256" s="21" t="inlineStr">
+        <is>
+          <t>21  💳 수강 등록 · 결제 → 수업 자동 생성  —  결제 확정되면 회차 전량이 자동으로 잡힙니다</t>
+        </is>
+      </c>
+      <c r="B256" s="22" t="n"/>
+      <c r="C256" s="22" t="n"/>
+      <c r="D256" s="22" t="n"/>
+      <c r="E256" s="22" t="n"/>
+      <c r="F256" s="22" t="n"/>
+    </row>
+    <row r="257" ht="42" customHeight="1">
+      <c r="A257" s="23" t="inlineStr">
+        <is>
+          <t>📖 수강신청 화면에서 학생이 강사·요일·시간을 고르고 결제하면, 결제 확정 시점에 수업 회차가 전량 자동 생성됩니다. 예전처럼 결제 확인 후 사람이 일일이 시간표를 넣던 작업이 사라졌어요. 같은 시간에 이미 잡힌 수업이 있으면 결제 전에 충돌을 감지해 알려 줍니다.</t>
+        </is>
+      </c>
+      <c r="B257" s="24" t="n"/>
+      <c r="C257" s="24" t="n"/>
+      <c r="D257" s="24" t="n"/>
+      <c r="E257" s="24" t="n"/>
+      <c r="F257" s="24" t="n"/>
+    </row>
+    <row r="258" ht="24" customHeight="1">
+      <c r="A258" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 수강신청 링크   ›   2 강사 → 수업 옵션(주…   ›   3 시간 확인   ›   4 회차가 한꺼번에 생성   ›   5 단가표 화면</t>
+        </is>
+      </c>
+      <c r="B258" s="26" t="n"/>
+      <c r="C258" s="26" t="n"/>
+      <c r="D258" s="26" t="n"/>
+      <c r="E258" s="26" t="n"/>
+      <c r="F258" s="26" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B259" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="30" customHeight="1">
+      <c r="A260" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B260" s="30" t="inlineStr">
+        <is>
+          <t>학생·학부모에게 수강신청 링크를 안내해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="30" customHeight="1">
+      <c r="A261" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B261" s="30" t="inlineStr">
+        <is>
+          <t>학생이 강사 → 수업 옵션(주 횟수·기간·수업 길이) → 요일·시간 순으로 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="30" customHeight="1">
+      <c r="A262" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B262" s="30" t="inlineStr">
+        <is>
+          <t>시간 확인이 통과돼야 결제 버튼이 열립니다(충돌 시 결제 불가).</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="30" customHeight="1">
+      <c r="A263" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B263" s="30" t="inlineStr">
+        <is>
+          <t>결제가 확정되면 회차가 한꺼번에 생성됩니다. 관리자 화면 수업 목록에서 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="30" customHeight="1">
+      <c r="A264" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B264" s="30" t="inlineStr">
+        <is>
+          <t>본사 단가·할인율은 단가표 화면에서 관리합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="24" customHeight="1">
+      <c r="A265" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B265" s="32" t="inlineStr">
+        <is>
+          <t>멱등 처리돼서 결제 알림이 중복 들어와도 회차가 두 번 생기지 않아요.</t>
+        </is>
+      </c>
+      <c r="C265" s="33" t="n"/>
+      <c r="D265" s="33" t="n"/>
+      <c r="E265" s="33" t="n"/>
+      <c r="F265" s="33" t="n"/>
+    </row>
+    <row r="266" ht="24" customHeight="1">
+      <c r="A266" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B266" s="32" t="inlineStr">
+        <is>
+          <t>공휴일·기존 수업과 겹치면 뒤로 밀어서 회차 수를 채웁니다.</t>
+        </is>
+      </c>
+      <c r="C266" s="33" t="n"/>
+      <c r="D266" s="33" t="n"/>
+      <c r="E266" s="33" t="n"/>
+      <c r="F266" s="33" t="n"/>
+    </row>
+    <row r="267" ht="24" customHeight="1">
+      <c r="A267" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B267" s="32" t="inlineStr">
+        <is>
+          <t>기간 할인(6개월 -5% · 12개월 -10%)이 금액에 자동 반영됩니다.</t>
+        </is>
+      </c>
+      <c r="C267" s="33" t="n"/>
+      <c r="D267" s="33" t="n"/>
+      <c r="E267" s="33" t="n"/>
+      <c r="F267" s="33" t="n"/>
+    </row>
+    <row r="268" ht="26" customHeight="1">
+      <c r="A268" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 현재는 1단계(등록 → 결제 → 회차 자동 생성) 까지 열려 있습니다. 이후 단계는 순차 반영 예정입니다.</t>
+        </is>
+      </c>
+      <c r="B268" s="37" t="n"/>
+      <c r="C268" s="37" t="n"/>
+      <c r="D268" s="37" t="n"/>
+      <c r="E268" s="37" t="n"/>
+      <c r="F268" s="37" t="n"/>
+    </row>
+    <row r="269" ht="30" customHeight="1">
+      <c r="A269" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 상담 → 레벨테스트 → 수강신청 링크 전달 순서로 안내하면 등록 전환이 매끄럽습니다.</t>
         </is>
       </c>
-      <c r="B241" s="33" t="n"/>
-      <c r="C241" s="33" t="n"/>
-      <c r="D241" s="33" t="n"/>
-      <c r="E241" s="33" t="n"/>
-      <c r="F241" s="33" t="n"/>
-    </row>
-    <row r="243" ht="26" customHeight="1">
-      <c r="A243" s="21" t="inlineStr">
+      <c r="B269" s="35" t="n"/>
+      <c r="C269" s="35" t="n"/>
+      <c r="D269" s="35" t="n"/>
+      <c r="E269" s="35" t="n"/>
+      <c r="F269" s="35" t="n"/>
+    </row>
+    <row r="271" ht="26" customHeight="1">
+      <c r="A271" s="21" t="inlineStr">
         <is>
           <t>22  🗂️ 강사 통합 관리 개편 (명부 필터 · 그룹 · 상세 탭)  —  찾기 쉬운 명부 · 한눈에 보는 상세</t>
         </is>
       </c>
-      <c r="B243" s="22" t="n"/>
-      <c r="C243" s="22" t="n"/>
-      <c r="D243" s="22" t="n"/>
-      <c r="E243" s="22" t="n"/>
-      <c r="F243" s="22" t="n"/>
-    </row>
-    <row r="244" ht="42" customHeight="1">
-      <c r="A244" s="23" t="inlineStr">
+      <c r="B271" s="22" t="n"/>
+      <c r="C271" s="22" t="n"/>
+      <c r="D271" s="22" t="n"/>
+      <c r="E271" s="22" t="n"/>
+      <c r="F271" s="22" t="n"/>
+    </row>
+    <row r="272" ht="42" customHeight="1">
+      <c r="A272" s="23" t="inlineStr">
         <is>
           <t>📖 강사 관리 화면이 찾기 쉽고 보기 편하게 정리됐어요. 흩어져 있던 메뉴를 네 묶음으로 그룹지어 사이드바에 담았고, 강사 명부 위에는 구분·상태·그룹 드롭다운 필터와 적용된 필터 칩이 생겼어요. 강사를 누르면 프로필·급여·평가 탭으로 나뉜 상세 화면이 열리고, 매니저 배지와 재직 상태(재직·휴직·퇴사) 가 한눈에 표시돼요.</t>
         </is>
       </c>
-      <c r="B244" s="24" t="n"/>
-      <c r="C244" s="24" t="n"/>
-      <c r="D244" s="24" t="n"/>
-      <c r="E244" s="24" t="n"/>
-      <c r="F244" s="24" t="n"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="25" t="inlineStr">
+      <c r="B272" s="24" t="n"/>
+      <c r="C272" s="24" t="n"/>
+      <c r="D272" s="24" t="n"/>
+      <c r="E272" s="24" t="n"/>
+      <c r="F272" s="24" t="n"/>
+    </row>
+    <row r="273" ht="24" customHeight="1">
+      <c r="A273" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 강사 통합   ›   2 상태·그룹 드롭다운   ›   3 칩   ›   4 프로필 / 급여 / 평가   ›   5 급여·평가 탭의 요약 숫…</t>
+        </is>
+      </c>
+      <c r="B273" s="26" t="n"/>
+      <c r="C273" s="26" t="n"/>
+      <c r="D273" s="26" t="n"/>
+      <c r="E273" s="26" t="n"/>
+      <c r="F273" s="26" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B245" s="26" t="inlineStr">
+      <c r="B274" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="246" ht="30" customHeight="1">
-      <c r="A246" s="27" t="n">
+    <row r="275" ht="30" customHeight="1">
+      <c r="A275" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B246" s="28" t="inlineStr">
+      <c r="B275" s="30" t="inlineStr">
         <is>
           <t>관리자 메뉴 강사 통합을 열어요(메뉴가 네 묶음으로 정리돼 있어요).</t>
         </is>
       </c>
     </row>
-    <row r="247" ht="30" customHeight="1">
-      <c r="A247" s="27" t="n">
+    <row r="276" ht="30" customHeight="1">
+      <c r="A276" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B247" s="28" t="inlineStr">
+      <c r="B276" s="30" t="inlineStr">
         <is>
           <t>명부 위 상태·그룹 드롭다운으로 원하는 강사만 걸러요.</t>
         </is>
       </c>
     </row>
-    <row r="248" ht="30" customHeight="1">
-      <c r="A248" s="27" t="n">
+    <row r="277" ht="30" customHeight="1">
+      <c r="A277" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B248" s="28" t="inlineStr">
+      <c r="B277" s="30" t="inlineStr">
         <is>
           <t>적용된 필터는 칩으로 표시되고, 칩을 지우면 해제돼요.</t>
         </is>
       </c>
     </row>
-    <row r="249" ht="30" customHeight="1">
-      <c r="A249" s="27" t="n">
+    <row r="278" ht="30" customHeight="1">
+      <c r="A278" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B249" s="28" t="inlineStr">
+      <c r="B278" s="30" t="inlineStr">
         <is>
           <t>강사를 누르면 프로필 / 급여 / 평가 탭 상세가 열려요.</t>
         </is>
       </c>
     </row>
-    <row r="250" ht="30" customHeight="1">
-      <c r="A250" s="27" t="n">
+    <row r="279" ht="30" customHeight="1">
+      <c r="A279" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B250" s="28" t="inlineStr">
+      <c r="B279" s="30" t="inlineStr">
         <is>
           <t>급여·평가 탭의 요약 숫자는 열 때 필요한 만큼만 불러옵니다.</t>
         </is>
       </c>
     </row>
-    <row r="251" ht="24" customHeight="1">
-      <c r="A251" s="29" t="inlineStr">
+    <row r="280" ht="24" customHeight="1">
+      <c r="A280" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B251" s="30" t="inlineStr">
+      <c r="B280" s="32" t="inlineStr">
         <is>
           <t>매니저는 배지로 구분되고, 재직 상태가 재직·휴직·퇴사 3가지로 표시돼요.</t>
         </is>
       </c>
-      <c r="C251" s="31" t="n"/>
-      <c r="D251" s="31" t="n"/>
-      <c r="E251" s="31" t="n"/>
-      <c r="F251" s="31" t="n"/>
-    </row>
-    <row r="252" ht="24" customHeight="1">
-      <c r="A252" s="29" t="inlineStr">
+      <c r="C280" s="33" t="n"/>
+      <c r="D280" s="33" t="n"/>
+      <c r="E280" s="33" t="n"/>
+      <c r="F280" s="33" t="n"/>
+    </row>
+    <row r="281" ht="24" customHeight="1">
+      <c r="A281" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B252" s="30" t="inlineStr">
+      <c r="B281" s="32" t="inlineStr">
         <is>
           <t>이름이 비어도 아이디로 대체 표기돼 빈칸이 없어요.</t>
         </is>
       </c>
-      <c r="C252" s="31" t="n"/>
-      <c r="D252" s="31" t="n"/>
-      <c r="E252" s="31" t="n"/>
-      <c r="F252" s="31" t="n"/>
-    </row>
-    <row r="253" ht="24" customHeight="1">
-      <c r="A253" s="29" t="inlineStr">
+      <c r="C281" s="33" t="n"/>
+      <c r="D281" s="33" t="n"/>
+      <c r="E281" s="33" t="n"/>
+      <c r="F281" s="33" t="n"/>
+    </row>
+    <row r="282" ht="24" customHeight="1">
+      <c r="A282" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B253" s="30" t="inlineStr">
+      <c r="B282" s="32" t="inlineStr">
         <is>
           <t>상세 탭은 기존 API를 재사용해 빠르게 뜨고, 화면은 한/영 병기예요.</t>
         </is>
       </c>
-      <c r="C253" s="31" t="n"/>
-      <c r="D253" s="31" t="n"/>
-      <c r="E253" s="31" t="n"/>
-      <c r="F253" s="31" t="n"/>
-    </row>
-    <row r="254" ht="24" customHeight="1">
-      <c r="A254" s="29" t="inlineStr">
+      <c r="C282" s="33" t="n"/>
+      <c r="D282" s="33" t="n"/>
+      <c r="E282" s="33" t="n"/>
+      <c r="F282" s="33" t="n"/>
+    </row>
+    <row r="283" ht="24" customHeight="1">
+      <c r="A283" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B254" s="30" t="inlineStr">
+      <c r="B283" s="32" t="inlineStr">
         <is>
           <t>중복이던 급여 입구를 정리하고 버그 접수는 별도 시스템으로 옮겼어요.</t>
         </is>
       </c>
-      <c r="C254" s="31" t="n"/>
-      <c r="D254" s="31" t="n"/>
-      <c r="E254" s="31" t="n"/>
-      <c r="F254" s="31" t="n"/>
-    </row>
-    <row r="255" ht="26" customHeight="1">
-      <c r="A255" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 필터·상세 정리 작업이에요. 강사 등록·수정·삭제 기능 자체는 그대로예요.</t>
-        </is>
-      </c>
-      <c r="B255" s="35" t="n"/>
-      <c r="C255" s="35" t="n"/>
-      <c r="D255" s="35" t="n"/>
-      <c r="E255" s="35" t="n"/>
-      <c r="F255" s="35" t="n"/>
-    </row>
-    <row r="256" ht="30" customHeight="1">
-      <c r="A256" s="32" t="inlineStr">
+      <c r="C283" s="33" t="n"/>
+      <c r="D283" s="33" t="n"/>
+      <c r="E283" s="33" t="n"/>
+      <c r="F283" s="33" t="n"/>
+    </row>
+    <row r="284" ht="26" customHeight="1">
+      <c r="A284" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 필터·상세 정리 작업이에요. 강사 등록·수정·삭제 기능 자체는 그대로예요.</t>
+        </is>
+      </c>
+      <c r="B284" s="37" t="n"/>
+      <c r="C284" s="37" t="n"/>
+      <c r="D284" s="37" t="n"/>
+      <c r="E284" s="37" t="n"/>
+      <c r="F284" s="37" t="n"/>
+    </row>
+    <row r="285" ht="30" customHeight="1">
+      <c r="A285" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 강사가 많을수록 상태·그룹 필터가 큰 힘을 발휘해요. 자주 보는 조건은 필터를 걸어 두고 쓰세요.</t>
         </is>
       </c>
-      <c r="B256" s="33" t="n"/>
-      <c r="C256" s="33" t="n"/>
-      <c r="D256" s="33" t="n"/>
-      <c r="E256" s="33" t="n"/>
-      <c r="F256" s="33" t="n"/>
-    </row>
-    <row r="258" ht="26" customHeight="1">
-      <c r="A258" s="21" t="inlineStr">
+      <c r="B285" s="35" t="n"/>
+      <c r="C285" s="35" t="n"/>
+      <c r="D285" s="35" t="n"/>
+      <c r="E285" s="35" t="n"/>
+      <c r="F285" s="35" t="n"/>
+    </row>
+    <row r="287" ht="26" customHeight="1">
+      <c r="A287" s="21" t="inlineStr">
         <is>
           <t>23  🌟 학부모 월간 성적표 (오각형) 발송  —  5축 그래프 성적표를 미리보고 링크로</t>
         </is>
       </c>
-      <c r="B258" s="22" t="n"/>
-      <c r="C258" s="22" t="n"/>
-      <c r="D258" s="22" t="n"/>
-      <c r="E258" s="22" t="n"/>
-      <c r="F258" s="22" t="n"/>
-    </row>
-    <row r="259" ht="42" customHeight="1">
-      <c r="A259" s="23" t="inlineStr">
+      <c r="B287" s="22" t="n"/>
+      <c r="C287" s="22" t="n"/>
+      <c r="D287" s="22" t="n"/>
+      <c r="E287" s="22" t="n"/>
+      <c r="F287" s="22" t="n"/>
+    </row>
+    <row r="288" ht="42" customHeight="1">
+      <c r="A288" s="23" t="inlineStr">
         <is>
           <t>📖 학부모에게 보내는 월간 성적표가 오각형 5축 그래프로 새로워졌어요. 발음·유창성 / 어휘 / 문장 구성력 / 수업 태도 / 참여도 를 한눈에 보여 주고, 출결·판단력·담임의 한마디가 함께 담깁니다. 관리자·교사는 학생 ID와 월을 넣어 미리보기한 뒤 카카오톡 링크로 보냅니다.</t>
         </is>
       </c>
-      <c r="B259" s="24" t="n"/>
-      <c r="C259" s="24" t="n"/>
-      <c r="D259" s="24" t="n"/>
-      <c r="E259" s="24" t="n"/>
-      <c r="F259" s="24" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="25" t="inlineStr">
+      <c r="B288" s="24" t="n"/>
+      <c r="C288" s="24" t="n"/>
+      <c r="D288" s="24" t="n"/>
+      <c r="E288" s="24" t="n"/>
+      <c r="F288" s="24" t="n"/>
+    </row>
+    <row r="289" ht="24" customHeight="1">
+      <c r="A289" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 월간 리포트   ›   2 학생 ID   ›   3 오각형과 담임의 한마디를…   ›   4 ?uid=학생ID&amp;per…</t>
+        </is>
+      </c>
+      <c r="B289" s="26" t="n"/>
+      <c r="C289" s="26" t="n"/>
+      <c r="D289" s="26" t="n"/>
+      <c r="E289" s="26" t="n"/>
+      <c r="F289" s="26" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B260" s="26" t="inlineStr">
+      <c r="B290" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="261" ht="30" customHeight="1">
-      <c r="A261" s="27" t="n">
+    <row r="291" ht="30" customHeight="1">
+      <c r="A291" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B261" s="28" t="inlineStr">
+      <c r="B291" s="30" t="inlineStr">
         <is>
           <t>월간 리포트 화면을 열어요.</t>
         </is>
       </c>
     </row>
-    <row r="262" ht="30" customHeight="1">
-      <c r="A262" s="27" t="n">
+    <row r="292" ht="30" customHeight="1">
+      <c r="A292" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B262" s="28" t="inlineStr">
+      <c r="B292" s="30" t="inlineStr">
         <is>
           <t>학생 ID와 월을 넣고 레포트 보기를 눌러 미리봐요.</t>
         </is>
       </c>
     </row>
-    <row r="263" ht="30" customHeight="1">
-      <c r="A263" s="27" t="n">
+    <row r="293" ht="30" customHeight="1">
+      <c r="A293" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B263" s="28" t="inlineStr">
+      <c r="B293" s="30" t="inlineStr">
         <is>
           <t>오각형과 담임의 한마디를 확인하고, 필요하면 평가를 보완해요.</t>
         </is>
       </c>
     </row>
-    <row r="264" ht="30" customHeight="1">
-      <c r="A264" s="27" t="n">
+    <row r="294" ht="30" customHeight="1">
+      <c r="A294" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B264" s="28" t="inlineStr">
+      <c r="B294" s="30" t="inlineStr">
         <is>
           <t>주소에 ?uid=학생ID&amp;period=YYYY-MM 를 붙여 카카오톡 링크로 보냅니다.</t>
         </is>
       </c>
     </row>
-    <row r="265" ht="24" customHeight="1">
-      <c r="A265" s="29" t="inlineStr">
+    <row r="295" ht="24" customHeight="1">
+      <c r="A295" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B265" s="30" t="inlineStr">
+      <c r="B295" s="32" t="inlineStr">
         <is>
           <t>실제 기록이 있는 축만 채워져 신뢰할 수 있어요.</t>
         </is>
       </c>
-      <c r="C265" s="31" t="n"/>
-      <c r="D265" s="31" t="n"/>
-      <c r="E265" s="31" t="n"/>
-      <c r="F265" s="31" t="n"/>
-    </row>
-    <row r="266" ht="24" customHeight="1">
-      <c r="A266" s="29" t="inlineStr">
+      <c r="C295" s="33" t="n"/>
+      <c r="D295" s="33" t="n"/>
+      <c r="E295" s="33" t="n"/>
+      <c r="F295" s="33" t="n"/>
+    </row>
+    <row r="296" ht="24" customHeight="1">
+      <c r="A296" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B266" s="30" t="inlineStr">
+      <c r="B296" s="32" t="inlineStr">
         <is>
           <t>2개월 주기로 정리해 학부모 피로 없이 변화를 전달해요.</t>
         </is>
       </c>
-      <c r="C266" s="31" t="n"/>
-      <c r="D266" s="31" t="n"/>
-      <c r="E266" s="31" t="n"/>
-      <c r="F266" s="31" t="n"/>
-    </row>
-    <row r="267" ht="24" customHeight="1">
-      <c r="A267" s="29" t="inlineStr">
+      <c r="C296" s="33" t="n"/>
+      <c r="D296" s="33" t="n"/>
+      <c r="E296" s="33" t="n"/>
+      <c r="F296" s="33" t="n"/>
+    </row>
+    <row r="297" ht="24" customHeight="1">
+      <c r="A297" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B267" s="30" t="inlineStr">
+      <c r="B297" s="32" t="inlineStr">
         <is>
           <t>인쇄/PDF 버튼으로 상담용 종이 성적표도 즉시 만들 수 있어요.</t>
         </is>
       </c>
-      <c r="C267" s="31" t="n"/>
-      <c r="D267" s="31" t="n"/>
-      <c r="E267" s="31" t="n"/>
-      <c r="F267" s="31" t="n"/>
-    </row>
-    <row r="268" ht="26" customHeight="1">
-      <c r="A268" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 성적표 열람은 승인 게이트를 거쳐요. 관리자는 로그인 세션으로, 학부모는 발급된 링크(토큰)로만 열립니다.</t>
-        </is>
-      </c>
-      <c r="B268" s="35" t="n"/>
-      <c r="C268" s="35" t="n"/>
-      <c r="D268" s="35" t="n"/>
-      <c r="E268" s="35" t="n"/>
-      <c r="F268" s="35" t="n"/>
-    </row>
-    <row r="269" ht="30" customHeight="1">
-      <c r="A269" s="32" t="inlineStr">
+      <c r="C297" s="33" t="n"/>
+      <c r="D297" s="33" t="n"/>
+      <c r="E297" s="33" t="n"/>
+      <c r="F297" s="33" t="n"/>
+    </row>
+    <row r="298" ht="26" customHeight="1">
+      <c r="A298" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 성적표 열람은 승인 게이트를 거쳐요. 관리자는 로그인 세션으로, 학부모는 발급된 링크(토큰)로만 열립니다.</t>
+        </is>
+      </c>
+      <c r="B298" s="37" t="n"/>
+      <c r="C298" s="37" t="n"/>
+      <c r="D298" s="37" t="n"/>
+      <c r="E298" s="37" t="n"/>
+      <c r="F298" s="37" t="n"/>
+    </row>
+    <row r="299" ht="30" customHeight="1">
+      <c r="A299" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 상담 예약과 함께 성적표 링크를 미리 보내면 상담이 훨씬 매끄러워요.</t>
         </is>
       </c>
-      <c r="B269" s="33" t="n"/>
-      <c r="C269" s="33" t="n"/>
-      <c r="D269" s="33" t="n"/>
-      <c r="E269" s="33" t="n"/>
-      <c r="F269" s="33" t="n"/>
+      <c r="B299" s="35" t="n"/>
+      <c r="C299" s="35" t="n"/>
+      <c r="D299" s="35" t="n"/>
+      <c r="E299" s="35" t="n"/>
+      <c r="F299" s="35" t="n"/>
+    </row>
+    <row r="301" ht="26" customHeight="1">
+      <c r="A301" s="21" t="inlineStr">
+        <is>
+          <t>24  📅 학부모 주간 리포트 (재등록을 잇는 무기)  —  경쟁사가 못 보여 주는 ‘성장의 증거’를 매주</t>
+        </is>
+      </c>
+      <c r="B301" s="22" t="n"/>
+      <c r="C301" s="22" t="n"/>
+      <c r="D301" s="22" t="n"/>
+      <c r="E301" s="22" t="n"/>
+      <c r="F301" s="22" t="n"/>
+    </row>
+    <row r="302" ht="42" customHeight="1">
+      <c r="A302" s="23" t="inlineStr">
+        <is>
+          <t>📖 아이의 한 주 활동(출석·AI 친구 대화·판단력·정복한 단어·발음)을 담아 학부모에게 보내는 리포트입니다. 목적은 분명합니다 — 경쟁사가 보여 주지 못하는 ‘성장의 증거’를 매주 전달해 재등록으로 잇는 것입니다. 관리자 화면에서 미리보기 → 테스트 발송 → 대상 집계 → 발송 로그를 모두 확인할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="B302" s="24" t="n"/>
+      <c r="C302" s="24" t="n"/>
+      <c r="D302" s="24" t="n"/>
+      <c r="E302" s="24" t="n"/>
+      <c r="F302" s="24" t="n"/>
+    </row>
+    <row r="303" ht="24" customHeight="1">
+      <c r="A303" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 📅 학부모 주간 리포트   ›   2 미리보기   ›   3 이 학부모에게 실제 발송   ›   4 발송 대상 집계   ›   5 최근 발송 로그</t>
+        </is>
+      </c>
+      <c r="B303" s="26" t="n"/>
+      <c r="C303" s="26" t="n"/>
+      <c r="D303" s="26" t="n"/>
+      <c r="E303" s="26" t="n"/>
+      <c r="F303" s="26" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B304" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="30" customHeight="1">
+      <c r="A305" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B305" s="30" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 📅 학부모 주간 리포트를 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="30" customHeight="1">
+      <c r="A306" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B306" s="30" t="inlineStr">
+        <is>
+          <t>학생 ID를 넣고 미리보기로 내용을 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="30" customHeight="1">
+      <c r="A307" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B307" s="30" t="inlineStr">
+        <is>
+          <t>필요하면 이 학부모에게 실제 발송으로 한 명에게만 테스트해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="30" customHeight="1">
+      <c r="A308" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B308" s="30" t="inlineStr">
+        <is>
+          <t>발송 대상 집계로 지금 받을 수 있는 학생 수(전화번호 등록자)를 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="30" customHeight="1">
+      <c r="A309" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B309" s="30" t="inlineStr">
+        <is>
+          <t>최근 발송 로그로 실제로 나간 기록을 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="24" customHeight="1">
+      <c r="A310" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B310" s="32" t="inlineStr">
+        <is>
+          <t>리포트에 담기는 것: 📅 출석 일수 · 🔥 연속 출석 · 🤖 AI 대화 · 📚 정복 단어 · 🧠 판단력 · 🎤 발음.</t>
+        </is>
+      </c>
+      <c r="C310" s="33" t="n"/>
+      <c r="D310" s="33" t="n"/>
+      <c r="E310" s="33" t="n"/>
+      <c r="F310" s="33" t="n"/>
+    </row>
+    <row r="311" ht="24" customHeight="1">
+      <c r="A311" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B311" s="32" t="inlineStr">
+        <is>
+          <t>전화번호가 등록된 학생만 받을 수 있어요 — 집계 화면이 미등록 인원을 함께 알려 줍니다.</t>
+        </is>
+      </c>
+      <c r="C311" s="33" t="n"/>
+      <c r="D311" s="33" t="n"/>
+      <c r="E311" s="33" t="n"/>
+      <c r="F311" s="33" t="n"/>
+    </row>
+    <row r="312" ht="24" customHeight="1">
+      <c r="A312" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B312" s="32" t="inlineStr">
+        <is>
+          <t>매주 금요일 저녁 자동 발송(크론) 이 준비돼 있습니다.</t>
+        </is>
+      </c>
+      <c r="C312" s="33" t="n"/>
+      <c r="D312" s="33" t="n"/>
+      <c r="E312" s="33" t="n"/>
+      <c r="F312" s="33" t="n"/>
+    </row>
+    <row r="313" ht="26" customHeight="1">
+      <c r="A313" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 🔴 전체 자동 발송은 기본으로 꺼져 있습니다. 관리자가 KV 스위치를 켠 뒤에만 실제 문자가 나갑니다 — 실수로 29,000명에게 발송되는 사고를 막기 위한 안전장치입니다. 알림톡 템플릿 승인과 대표 결정 뒤에 켜세요.</t>
+        </is>
+      </c>
+      <c r="B313" s="37" t="n"/>
+      <c r="C313" s="37" t="n"/>
+      <c r="D313" s="37" t="n"/>
+      <c r="E313" s="37" t="n"/>
+      <c r="F313" s="37" t="n"/>
+    </row>
+    <row r="314" ht="30" customHeight="1">
+      <c r="A314" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 먼저 미리보기 → 한 명 테스트 발송까지만 해 보세요. 문구가 확정되면 그때 전체 스위치를 켜면 됩니다.</t>
+        </is>
+      </c>
+      <c r="B314" s="35" t="n"/>
+      <c r="C314" s="35" t="n"/>
+      <c r="D314" s="35" t="n"/>
+      <c r="E314" s="35" t="n"/>
+      <c r="F314" s="35" t="n"/>
+    </row>
+    <row r="316" ht="26" customHeight="1">
+      <c r="A316" s="21" t="inlineStr">
+        <is>
+          <t>25  🏠 홈 첫 화면 개편 (처음 온 학부모 · 기존 회원 자동 분리)  —  상담 전화가 줄고 체험 신청이 늘어나는 구조</t>
+        </is>
+      </c>
+      <c r="B316" s="22" t="n"/>
+      <c r="C316" s="22" t="n"/>
+      <c r="D316" s="22" t="n"/>
+      <c r="E316" s="22" t="n"/>
+      <c r="F316" s="22" t="n"/>
+    </row>
+    <row r="317" ht="42" customHeight="1">
+      <c r="A317" s="23" t="inlineStr">
+        <is>
+          <t>📖 홈페이지 첫 화면(히어로)이 보는 사람에 따라 두 가지로 나뉘어 표시됩니다. 처음 온 학부모에게는 &lt;b&gt;무료 체험 신청&lt;/b&gt;이 가장 큰 버튼으로, 이미 로그인한 회원에게는 &lt;b&gt;수업 입장&lt;/b&gt;이 가장 큰 버튼으로 뜹니다. 경쟁사 4곳(캠블리키즈·민병철유폰·엔구·링글)을 실제로 확인한 결과 모두 첫 버튼이 신규 상담·체험 신청이었고, 이를 반영한 개편입니다.</t>
+        </is>
+      </c>
+      <c r="B317" s="24" t="n"/>
+      <c r="C317" s="24" t="n"/>
+      <c r="D317" s="24" t="n"/>
+      <c r="E317" s="24" t="n"/>
+      <c r="F317" s="24" t="n"/>
+    </row>
+    <row r="318" ht="24" customHeight="1">
+      <c r="A318" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 홈 주소   ›   2 무료 체험 신청 · 강사…   ›   3 수업 입장 · AI와 친…   ›   4 홈 주소 그대로</t>
+        </is>
+      </c>
+      <c r="B318" s="26" t="n"/>
+      <c r="C318" s="26" t="n"/>
+      <c r="D318" s="26" t="n"/>
+      <c r="E318" s="26" t="n"/>
+      <c r="F318" s="26" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B319" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="30" customHeight="1">
+      <c r="A320" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B320" s="30" t="inlineStr">
+        <is>
+          <t>새 창(시크릿 모드)으로 홈 주소를 열어 비회원 화면을 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="30" customHeight="1">
+      <c r="A321" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B321" s="30" t="inlineStr">
+        <is>
+          <t>무료 체험 신청 · 강사 둘러보기 두 버튼이 크게 보이는지 봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="30" customHeight="1">
+      <c r="A322" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B322" s="30" t="inlineStr">
+        <is>
+          <t>로그인한 뒤 같은 화면을 열면 수업 입장 · AI와 친구하기로 바뀌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="30" customHeight="1">
+      <c r="A323" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B323" s="30" t="inlineStr">
+        <is>
+          <t>홍보물·문자에는 홈 주소 그대로 넣으면 됩니다 — 별도 랜딩페이지가 필요 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="24" customHeight="1">
+      <c r="A324" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B324" s="32" t="inlineStr">
+        <is>
+          <t>페이지를 새로 만들지 않았어요. 같은 주소가 로그인 여부만 보고 알아서 바뀝니다.</t>
+        </is>
+      </c>
+      <c r="C324" s="33" t="n"/>
+      <c r="D324" s="33" t="n"/>
+      <c r="E324" s="33" t="n"/>
+      <c r="F324" s="33" t="n"/>
+    </row>
+    <row r="325" ht="24" customHeight="1">
+      <c r="A325" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B325" s="32" t="inlineStr">
+        <is>
+          <t>비회원 화면에도 작은 ‘수업 입장’ 링크를 남겼어요 — 기기를 바꾸거나 로그인이 풀린 기존 학생이 수업에 못 들어가는 사고를 막습니다.</t>
+        </is>
+      </c>
+      <c r="C325" s="33" t="n"/>
+      <c r="D325" s="33" t="n"/>
+      <c r="E325" s="33" t="n"/>
+      <c r="F325" s="33" t="n"/>
+    </row>
+    <row r="326" ht="24" customHeight="1">
+      <c r="A326" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B326" s="32" t="inlineStr">
+        <is>
+          <t>판정에 실패하면 무조건 비회원 화면으로 떨어집니다 — 화면이 비는 일이 없어요.</t>
+        </is>
+      </c>
+      <c r="C326" s="33" t="n"/>
+      <c r="D326" s="33" t="n"/>
+      <c r="E326" s="33" t="n"/>
+      <c r="F326" s="33" t="n"/>
+    </row>
+    <row r="327" ht="24" customHeight="1">
+      <c r="A327" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B327" s="32" t="inlineStr">
+        <is>
+          <t>깜빡임이 없습니다. 화면이 그려지기 전에 판정이 끝나요.</t>
+        </is>
+      </c>
+      <c r="C327" s="33" t="n"/>
+      <c r="D327" s="33" t="n"/>
+      <c r="E327" s="33" t="n"/>
+      <c r="F327" s="33" t="n"/>
+    </row>
+    <row r="328" ht="26" customHeight="1">
+      <c r="A328" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 비회원 화면의 작은 ‘수업 입장’ 링크는 절대 빼면 안 됩니다. 로그인이 30일 만에 만료되거나 기기를 바꾼 기존 회원도 이 화면을 보기 때문입니다.</t>
+        </is>
+      </c>
+      <c r="B328" s="37" t="n"/>
+      <c r="C328" s="37" t="n"/>
+      <c r="D328" s="37" t="n"/>
+      <c r="E328" s="37" t="n"/>
+      <c r="F328" s="37" t="n"/>
+    </row>
+    <row r="329" ht="30" customHeight="1">
+      <c r="A329" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 체험 신청 전환을 보고 싶다면 시크릿 창으로 홈에 들어가 보세요. 학부모가 처음 보는 화면이 그대로 나옵니다.</t>
+        </is>
+      </c>
+      <c r="B329" s="35" t="n"/>
+      <c r="C329" s="35" t="n"/>
+      <c r="D329" s="35" t="n"/>
+      <c r="E329" s="35" t="n"/>
+      <c r="F329" s="35" t="n"/>
+    </row>
+    <row r="331" ht="26" customHeight="1">
+      <c r="A331" s="21" t="inlineStr">
+        <is>
+          <t>26  ⚡ 관리자 화면이 훨씬 빨라졌어요  —  누르면 멈추던 현상 제거</t>
+        </is>
+      </c>
+      <c r="B331" s="22" t="n"/>
+      <c r="C331" s="22" t="n"/>
+      <c r="D331" s="22" t="n"/>
+      <c r="E331" s="22" t="n"/>
+      <c r="F331" s="22" t="n"/>
+    </row>
+    <row r="332" ht="42" customHeight="1">
+      <c r="A332" s="23" t="inlineStr">
+        <is>
+          <t>📖 관리자 화면에서 무엇을 누르면 잠깐 멈추던 현상을 없앴습니다. 원인은 누른 기능이 아니라, 글자를 읽기 좋게 만들어 주는 보정 기능이 접혀 있는 카드까지 매번 다시 계산하고 있었던 것입니다. 접힌 카드는 건너뛰고, 이미 처리한 곳은 다시 만지지 않도록 고쳤습니다.</t>
+        </is>
+      </c>
+      <c r="B332" s="24" t="n"/>
+      <c r="C332" s="24" t="n"/>
+      <c r="D332" s="24" t="n"/>
+      <c r="E332" s="24" t="n"/>
+      <c r="F332" s="24" t="n"/>
+    </row>
+    <row r="333" ht="24" customHeight="1">
+      <c r="A333" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 관리자 화면을 평소처럼…   ›   2 멈춤 없이 바로 열리는지   ›   3 새로고침(Ctrl+F5)</t>
+        </is>
+      </c>
+      <c r="B333" s="26" t="n"/>
+      <c r="C333" s="26" t="n"/>
+      <c r="D333" s="26" t="n"/>
+      <c r="E333" s="26" t="n"/>
+      <c r="F333" s="26" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B334" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="30" customHeight="1">
+      <c r="A335" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B335" s="30" t="inlineStr">
+        <is>
+          <t>관리자 화면을 평소처럼 사용해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="30" customHeight="1">
+      <c r="A336" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B336" s="30" t="inlineStr">
+        <is>
+          <t>메뉴·카드를 눌렀을 때 멈춤 없이 바로 열리는지 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="30" customHeight="1">
+      <c r="A337" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B337" s="30" t="inlineStr">
+        <is>
+          <t>느리게 느껴지면 브라우저에서 새로고침(Ctrl+F5) 을 한 번 해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="24" customHeight="1">
+      <c r="A338" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B338" s="32" t="inlineStr">
+        <is>
+          <t>클릭 시 멈춤 396ms → 57ms, 대기 중 부하 366ms → 0ms 로 줄었습니다.</t>
+        </is>
+      </c>
+      <c r="C338" s="33" t="n"/>
+      <c r="D338" s="33" t="n"/>
+      <c r="E338" s="33" t="n"/>
+      <c r="F338" s="33" t="n"/>
+    </row>
+    <row r="339" ht="24" customHeight="1">
+      <c r="A339" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B339" s="32" t="inlineStr">
+        <is>
+          <t>화면 모양과 색은 전혀 바뀌지 않았습니다 — 속도만 좋아졌어요.</t>
+        </is>
+      </c>
+      <c r="C339" s="33" t="n"/>
+      <c r="D339" s="33" t="n"/>
+      <c r="E339" s="33" t="n"/>
+      <c r="F339" s="33" t="n"/>
+    </row>
+    <row r="340" ht="24" customHeight="1">
+      <c r="A340" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B340" s="32" t="inlineStr">
+        <is>
+          <t>카드가 많은 화면(강사·학생 목록)일수록 체감이 큽니다.</t>
+        </is>
+      </c>
+      <c r="C340" s="33" t="n"/>
+      <c r="D340" s="33" t="n"/>
+      <c r="E340" s="33" t="n"/>
+      <c r="F340" s="33" t="n"/>
+    </row>
+    <row r="341" ht="26" customHeight="1">
+      <c r="A341" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 브라우저에 옛 화면이 남아 있으면 개선이 바로 느껴지지 않을 수 있어요. 강력 새로고침(Ctrl+F5) 을 한 번 해 주세요.</t>
+        </is>
+      </c>
+      <c r="B341" s="37" t="n"/>
+      <c r="C341" s="37" t="n"/>
+      <c r="D341" s="37" t="n"/>
+      <c r="E341" s="37" t="n"/>
+      <c r="F341" s="37" t="n"/>
+    </row>
+    <row r="342" ht="30" customHeight="1">
+      <c r="A342" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 그래도 느리다면 브라우저 탭을 너무 많이 열어 두지 않았는지 확인해 보세요.</t>
+        </is>
+      </c>
+      <c r="B342" s="35" t="n"/>
+      <c r="C342" s="35" t="n"/>
+      <c r="D342" s="35" t="n"/>
+      <c r="E342" s="35" t="n"/>
+      <c r="F342" s="35" t="n"/>
+    </row>
+    <row r="344" ht="26" customHeight="1">
+      <c r="A344" s="21" t="inlineStr">
+        <is>
+          <t>27  🔎 학원 검색칸 (이름으로 바로 찾기)  —  목록을 훑지 않고 바로</t>
+        </is>
+      </c>
+      <c r="B344" s="22" t="n"/>
+      <c r="C344" s="22" t="n"/>
+      <c r="D344" s="22" t="n"/>
+      <c r="E344" s="22" t="n"/>
+      <c r="F344" s="22" t="n"/>
+    </row>
+    <row r="345" ht="42" customHeight="1">
+      <c r="A345" s="23" t="inlineStr">
+        <is>
+          <t>📖 학원(지사·대리점) 목록에서 이름을 입력해 바로 찾을 수 있는 검색칸이 생겼습니다. 학원 수가 많아 목록을 위아래로 훑어야 했던 불편을 없앴습니다.</t>
+        </is>
+      </c>
+      <c r="B345" s="24" t="n"/>
+      <c r="C345" s="24" t="n"/>
+      <c r="D345" s="24" t="n"/>
+      <c r="E345" s="24" t="n"/>
+      <c r="F345" s="24" t="n"/>
+    </row>
+    <row r="346" ht="24" customHeight="1">
+      <c r="A346" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 학원 목록   ›   2 검색칸   ›   3 해당 학원만   ›   4 전체 목록</t>
+        </is>
+      </c>
+      <c r="B346" s="26" t="n"/>
+      <c r="C346" s="26" t="n"/>
+      <c r="D346" s="26" t="n"/>
+      <c r="E346" s="26" t="n"/>
+      <c r="F346" s="26" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B347" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="30" customHeight="1">
+      <c r="A348" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B348" s="30" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 학원 목록 화면을 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="30" customHeight="1">
+      <c r="A349" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B349" s="30" t="inlineStr">
+        <is>
+          <t>목록 위 검색칸에 학원 이름 일부를 입력해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="30" customHeight="1">
+      <c r="A350" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B350" s="30" t="inlineStr">
+        <is>
+          <t>입력하는 즉시 해당 학원만 목록에 남아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="30" customHeight="1">
+      <c r="A351" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B351" s="30" t="inlineStr">
+        <is>
+          <t>검색칸을 비우면 전체 목록으로 돌아와요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="24" customHeight="1">
+      <c r="A352" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B352" s="32" t="inlineStr">
+        <is>
+          <t>이름 일부만 입력해도 찾아집니다.</t>
+        </is>
+      </c>
+      <c r="C352" s="33" t="n"/>
+      <c r="D352" s="33" t="n"/>
+      <c r="E352" s="33" t="n"/>
+      <c r="F352" s="33" t="n"/>
+    </row>
+    <row r="353" ht="24" customHeight="1">
+      <c r="A353" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B353" s="32" t="inlineStr">
+        <is>
+          <t>기존 목록·기능은 그대로이고 찾는 방법만 추가됐습니다.</t>
+        </is>
+      </c>
+      <c r="C353" s="33" t="n"/>
+      <c r="D353" s="33" t="n"/>
+      <c r="E353" s="33" t="n"/>
+      <c r="F353" s="33" t="n"/>
+    </row>
+    <row r="354" ht="30" customHeight="1">
+      <c r="A354" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 자주 확인하는 학원이 있다면 이름 두세 글자만 외워 두세요. 클릭 없이 바로 걸러집니다.</t>
+        </is>
+      </c>
+      <c r="B354" s="35" t="n"/>
+      <c r="C354" s="35" t="n"/>
+      <c r="D354" s="35" t="n"/>
+      <c r="E354" s="35" t="n"/>
+      <c r="F354" s="35" t="n"/>
+    </row>
+    <row r="356" ht="26" customHeight="1">
+      <c r="A356" s="21" t="inlineStr">
+        <is>
+          <t>28  💳 신규 결제 화면 단계형 개편  —  상품 12개를 한꺼번에 보여 주지 않아요</t>
+        </is>
+      </c>
+      <c r="B356" s="22" t="n"/>
+      <c r="C356" s="22" t="n"/>
+      <c r="D356" s="22" t="n"/>
+      <c r="E356" s="22" t="n"/>
+      <c r="F356" s="22" t="n"/>
+    </row>
+    <row r="357" ht="42" customHeight="1">
+      <c r="A357" s="23" t="inlineStr">
+        <is>
+          <t>📖 신규 결제 화면이 ‘대상 먼저 고르기’ 단계형으로 바뀌었습니다. 예전에는 첫 화면에 상품 12개가 한꺼번에 떠서 학부모가 무엇을 골라야 할지 막막했습니다. 이제 키즈 · 일반 1:1 · 그룹 · 비즈니스 · 시험 · 기업 중 대상을 먼저 고르면 해당 상품만 보입니다.</t>
+        </is>
+      </c>
+      <c r="B357" s="24" t="n"/>
+      <c r="C357" s="24" t="n"/>
+      <c r="D357" s="24" t="n"/>
+      <c r="E357" s="24" t="n"/>
+      <c r="F357" s="24" t="n"/>
+    </row>
+    <row r="358" ht="24" customHeight="1">
+      <c r="A358" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 신규 결제   ›   2 대상   ›   3 상품만   ›   4 전체 요금표 보기</t>
+        </is>
+      </c>
+      <c r="B358" s="26" t="n"/>
+      <c r="C358" s="26" t="n"/>
+      <c r="D358" s="26" t="n"/>
+      <c r="E358" s="26" t="n"/>
+      <c r="F358" s="26" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B359" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="30" customHeight="1">
+      <c r="A360" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B360" s="30" t="inlineStr">
+        <is>
+          <t>학부모에게 신규 결제 화면을 안내해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="30" customHeight="1">
+      <c r="A361" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B361" s="30" t="inlineStr">
+        <is>
+          <t>대상(키즈·일반 1:1·그룹·비즈니스·시험·기업)을 먼저 고르게 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="30" customHeight="1">
+      <c r="A362" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B362" s="30" t="inlineStr">
+        <is>
+          <t>고른 대상에 맞는 상품만 화면에 남아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="30" customHeight="1">
+      <c r="A363" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B363" s="30" t="inlineStr">
+        <is>
+          <t>전체를 비교하고 싶어 하면 전체 요금표 보기를 눌러 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="24" customHeight="1">
+      <c r="A364" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B364" s="32" t="inlineStr">
+        <is>
+          <t>상품 카드와 결제 로직은 하나도 바뀌지 않았어요 — 보여 주기만 나눈 것이라 안전합니다.</t>
+        </is>
+      </c>
+      <c r="C364" s="33" t="n"/>
+      <c r="D364" s="33" t="n"/>
+      <c r="E364" s="33" t="n"/>
+      <c r="F364" s="33" t="n"/>
+    </row>
+    <row r="365" ht="24" customHeight="1">
+      <c r="A365" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B365" s="32" t="inlineStr">
+        <is>
+          <t>초기 3개(무료체험·기타·규정) → 키즈 선택 시 4개 → 전체 12개로 확인됐습니다.</t>
+        </is>
+      </c>
+      <c r="C365" s="33" t="n"/>
+      <c r="D365" s="33" t="n"/>
+      <c r="E365" s="33" t="n"/>
+      <c r="F365" s="33" t="n"/>
+    </row>
+    <row r="366" ht="24" customHeight="1">
+      <c r="A366" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B366" s="32" t="inlineStr">
+        <is>
+          <t>전체 요금표 보기를 남겨 두었어요 — 가격을 숨긴다는 인상을 주면 역효과이기 때문입니다.</t>
+        </is>
+      </c>
+      <c r="C366" s="33" t="n"/>
+      <c r="D366" s="33" t="n"/>
+      <c r="E366" s="33" t="n"/>
+      <c r="F366" s="33" t="n"/>
+    </row>
+    <row r="367" ht="30" customHeight="1">
+      <c r="A367" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 상담 전화에서 ‘어떤 걸 고를지 모르겠다’는 말이 나오면, 대상만 먼저 고르게 안내하세요.</t>
+        </is>
+      </c>
+      <c r="B367" s="35" t="n"/>
+      <c r="C367" s="35" t="n"/>
+      <c r="D367" s="35" t="n"/>
+      <c r="E367" s="35" t="n"/>
+      <c r="F367" s="35" t="n"/>
+    </row>
+    <row r="369" ht="26" customHeight="1">
+      <c r="A369" s="21" t="inlineStr">
+        <is>
+          <t>29  📋 계정 없는 학부모용 샘플 평가표  —  로그인 벽 앞에서 보여 줄 것이 생겼어요</t>
+        </is>
+      </c>
+      <c r="B369" s="22" t="n"/>
+      <c r="C369" s="22" t="n"/>
+      <c r="D369" s="22" t="n"/>
+      <c r="E369" s="22" t="n"/>
+      <c r="F369" s="22" t="n"/>
+    </row>
+    <row r="370" ht="42" customHeight="1">
+      <c r="A370" s="23" t="inlineStr">
+        <is>
+          <t>📖 계정이 없는 가망 학부모에게 보여 줄 것이 아무것도 없던 문제를 해결했습니다. 평가표 화면에 ‘계정이 없어요 — 샘플 평가표 먼저 보기’ 가 생겨, 로그인 없이 5축 점수 + 강사 코멘트 + AI 분석이 어떻게 나오는지 미리 보여 줄 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="B370" s="24" t="n"/>
+      <c r="C370" s="24" t="n"/>
+      <c r="D370" s="24" t="n"/>
+      <c r="E370" s="24" t="n"/>
+      <c r="F370" s="24" t="n"/>
+    </row>
+    <row r="371" ht="24" customHeight="1">
+      <c r="A371" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 평가표 화면   ›   2 계정이 없어요 — 샘플…   ›   3 5축 점수·강사 코멘트·…   ›   4 ‘우리 아이 것도 이렇게…</t>
+        </is>
+      </c>
+      <c r="B371" s="26" t="n"/>
+      <c r="C371" s="26" t="n"/>
+      <c r="D371" s="26" t="n"/>
+      <c r="E371" s="26" t="n"/>
+      <c r="F371" s="26" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B372" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="30" customHeight="1">
+      <c r="A373" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B373" s="30" t="inlineStr">
+        <is>
+          <t>상담 중 학부모에게 평가표 화면을 열어 보여 줘요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="30" customHeight="1">
+      <c r="A374" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B374" s="30" t="inlineStr">
+        <is>
+          <t>계정이 없어요 — 샘플 평가표 먼저 보기를 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="30" customHeight="1">
+      <c r="A375" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B375" s="30" t="inlineStr">
+        <is>
+          <t>5축 점수·강사 코멘트·AI 분석 구성을 함께 보며 설명해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="30" customHeight="1">
+      <c r="A376" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B376" s="30" t="inlineStr">
+        <is>
+          <t>‘우리 아이 것도 이렇게 나옵니다’로 체험 신청을 연결해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="24" customHeight="1">
+      <c r="A377" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B377" s="32" t="inlineStr">
+        <is>
+          <t>⚠️ 값은 전부 예시입니다. 제목과 상단 배너에 ‘샘플/예시’ 표시가 들어가 있어요.</t>
+        </is>
+      </c>
+      <c r="C377" s="33" t="n"/>
+      <c r="D377" s="33" t="n"/>
+      <c r="E377" s="33" t="n"/>
+      <c r="F377" s="33" t="n"/>
+    </row>
+    <row r="378" ht="24" customHeight="1">
+      <c r="A378" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B378" s="32" t="inlineStr">
+        <is>
+          <t>이 표시는 절대 지우면 안 됩니다 — 실제 기록으로 오해되면 신뢰 문제가 됩니다.</t>
+        </is>
+      </c>
+      <c r="C378" s="33" t="n"/>
+      <c r="D378" s="33" t="n"/>
+      <c r="E378" s="33" t="n"/>
+      <c r="F378" s="33" t="n"/>
+    </row>
+    <row r="379" ht="26" customHeight="1">
+      <c r="A379" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 샘플은 실제 학생 데이터를 쓰지 않습니다. 상담 자료로만 활용하세요.</t>
+        </is>
+      </c>
+      <c r="B379" s="37" t="n"/>
+      <c r="C379" s="37" t="n"/>
+      <c r="D379" s="37" t="n"/>
+      <c r="E379" s="37" t="n"/>
+      <c r="F379" s="37" t="n"/>
+    </row>
+    <row r="380" ht="30" customHeight="1">
+      <c r="A380" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 상담 첫 3분에 샘플 평가표를 보여 주면 ‘무엇을 받게 되는지’가 명확해져 체험 전환이 올라갑니다.</t>
+        </is>
+      </c>
+      <c r="B380" s="35" t="n"/>
+      <c r="C380" s="35" t="n"/>
+      <c r="D380" s="35" t="n"/>
+      <c r="E380" s="35" t="n"/>
+      <c r="F380" s="35" t="n"/>
+    </row>
+    <row r="382" ht="26" customHeight="1">
+      <c r="A382" s="21" t="inlineStr">
+        <is>
+          <t>30  📞 상담 창구·운영시간 통일 (카카오 1순위)  —  화면마다 달랐던 안내를 한 값으로</t>
+        </is>
+      </c>
+      <c r="B382" s="22" t="n"/>
+      <c r="C382" s="22" t="n"/>
+      <c r="D382" s="22" t="n"/>
+      <c r="E382" s="22" t="n"/>
+      <c r="F382" s="22" t="n"/>
+    </row>
+    <row r="383" ht="42" customHeight="1">
+      <c r="A383" s="23" t="inlineStr">
+        <is>
+          <t>📖 상담 운영시간이 화면마다 09-22 / 10-20 / 오후 7시로 제각각이던 문제를 10:00~23:00 (주말·공휴일 휴무) 한 값으로 통일했습니다. 또한 카카오 채널을 1순위 창구로 올리고, 전화 카드에도 ‘카카오가 더 빠릅니다’를 함께 표기했습니다.</t>
+        </is>
+      </c>
+      <c r="B383" s="24" t="n"/>
+      <c r="C383" s="24" t="n"/>
+      <c r="D383" s="24" t="n"/>
+      <c r="E383" s="24" t="n"/>
+      <c r="F383" s="24" t="n"/>
+    </row>
+    <row r="384" ht="24" customHeight="1">
+      <c r="A384" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 문의하기   ›   2 카카오 채널을 먼저   ›   3 10:00~23:00 (…</t>
+        </is>
+      </c>
+      <c r="B384" s="26" t="n"/>
+      <c r="C384" s="26" t="n"/>
+      <c r="D384" s="26" t="n"/>
+      <c r="E384" s="26" t="n"/>
+      <c r="F384" s="26" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B385" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="30" customHeight="1">
+      <c r="A386" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B386" s="30" t="inlineStr">
+        <is>
+          <t>문의하기 화면에서 카드 순서가 카카오 → 전화 인지 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" ht="30" customHeight="1">
+      <c r="A387" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B387" s="30" t="inlineStr">
+        <is>
+          <t>학부모 안내 시 카카오 채널을 먼저 안내해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="30" customHeight="1">
+      <c r="A388" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B388" s="30" t="inlineStr">
+        <is>
+          <t>운영시간은 10:00~23:00 (주말·공휴일 휴무) 로 통일해 안내해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="24" customHeight="1">
+      <c r="A389" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B389" s="32" t="inlineStr">
+        <is>
+          <t>고친 곳: 문의 화면·홈 메뉴·FAQ(한/영)·AI 상담사 사실블록·학생 FAQ까지 전부 같은 값입니다.</t>
+        </is>
+      </c>
+      <c r="C389" s="33" t="n"/>
+      <c r="D389" s="33" t="n"/>
+      <c r="E389" s="33" t="n"/>
+      <c r="F389" s="33" t="n"/>
+    </row>
+    <row r="390" ht="24" customHeight="1">
+      <c r="A390" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B390" s="32" t="inlineStr">
+        <is>
+          <t>쓰지 않는 팩스 번호와 자리표시자 전화번호는 삭제했습니다.</t>
+        </is>
+      </c>
+      <c r="C390" s="33" t="n"/>
+      <c r="D390" s="33" t="n"/>
+      <c r="E390" s="33" t="n"/>
+      <c r="F390" s="33" t="n"/>
+    </row>
+    <row r="391" ht="24" customHeight="1">
+      <c r="A391" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B391" s="32" t="inlineStr">
+        <is>
+          <t>AI 상담사도 같은 시간·같은 창구 순서로 안내합니다.</t>
+        </is>
+      </c>
+      <c r="C391" s="33" t="n"/>
+      <c r="D391" s="33" t="n"/>
+      <c r="E391" s="33" t="n"/>
+      <c r="F391" s="33" t="n"/>
+    </row>
+    <row r="392" ht="26" customHeight="1">
+      <c r="A392" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 실제 운영시간이 바뀌면 이 값들을 한꺼번에 고쳐야 합니다. 한 곳만 고치면 다시 화면마다 달라집니다.</t>
+        </is>
+      </c>
+      <c r="B392" s="37" t="n"/>
+      <c r="C392" s="37" t="n"/>
+      <c r="D392" s="37" t="n"/>
+      <c r="E392" s="37" t="n"/>
+      <c r="F392" s="37" t="n"/>
+    </row>
+    <row r="393" ht="30" customHeight="1">
+      <c r="A393" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 필리핀 콜센터 번호가 필요하면 실번호를 알려 주세요 — 자리표시자였던 번호는 삭제된 상태입니다.</t>
+        </is>
+      </c>
+      <c r="B393" s="35" t="n"/>
+      <c r="C393" s="35" t="n"/>
+      <c r="D393" s="35" t="n"/>
+      <c r="E393" s="35" t="n"/>
+      <c r="F393" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="246">
+  <mergeCells count="356">
+    <mergeCell ref="B209:F209"/>
+    <mergeCell ref="A369:F369"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B276:F276"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B238:F238"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B278:F278"/>
+    <mergeCell ref="A318:F318"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A186:F186"/>
+    <mergeCell ref="A257:F257"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B135:F135"/>
+    <mergeCell ref="B306:F306"/>
+    <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B199:F199"/>
+    <mergeCell ref="B291:F291"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="A204:F204"/>
+    <mergeCell ref="A269:F269"/>
+    <mergeCell ref="B293:F293"/>
+    <mergeCell ref="B322:F322"/>
+    <mergeCell ref="A141:F141"/>
+    <mergeCell ref="A333:F333"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B388:F388"/>
+    <mergeCell ref="B304:F304"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="B375:F375"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B319:F319"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="A153:F153"/>
+    <mergeCell ref="A346:F346"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A217:F217"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A129:F129"/>
+    <mergeCell ref="B259:F259"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B274:F274"/>
+    <mergeCell ref="B249:F249"/>
+    <mergeCell ref="B363:F363"/>
+    <mergeCell ref="B373:F373"/>
+    <mergeCell ref="A383:F383"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A370:F370"/>
+    <mergeCell ref="B325:F325"/>
+    <mergeCell ref="B154:F154"/>
+    <mergeCell ref="A271:F271"/>
+    <mergeCell ref="B390:F390"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="B389:F389"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B327:F327"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A273:F273"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B264:F264"/>
+    <mergeCell ref="B320:F320"/>
+    <mergeCell ref="B220:F220"/>
+    <mergeCell ref="B391:F391"/>
+    <mergeCell ref="B247:F247"/>
+    <mergeCell ref="B385:F385"/>
+    <mergeCell ref="A302:F302"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="A298:F298"/>
+    <mergeCell ref="B262:F262"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B211:F211"/>
+    <mergeCell ref="B338:F338"/>
+    <mergeCell ref="A284:F284"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B275:F275"/>
+    <mergeCell ref="B340:F340"/>
+    <mergeCell ref="B35:F35"/>
     <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B277:F277"/>
+    <mergeCell ref="B252:F252"/>
+    <mergeCell ref="A317:F317"/>
+    <mergeCell ref="B366:F366"/>
+    <mergeCell ref="A384:F384"/>
+    <mergeCell ref="B180:F180"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A152:F152"/>
+    <mergeCell ref="B234:F234"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B172:F172"/>
+    <mergeCell ref="A289:F289"/>
+    <mergeCell ref="A226:F226"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="B265:F265"/>
+    <mergeCell ref="A243:F243"/>
+    <mergeCell ref="B185:F185"/>
+    <mergeCell ref="A163:F163"/>
+    <mergeCell ref="B347:F347"/>
+    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="A254:F254"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="A392:F392"/>
+    <mergeCell ref="A112:F112"/>
+    <mergeCell ref="B171:F171"/>
+    <mergeCell ref="A127:F127"/>
+    <mergeCell ref="A176:F176"/>
+    <mergeCell ref="A314:F314"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A191:F191"/>
+    <mergeCell ref="B359:F359"/>
+    <mergeCell ref="A178:F178"/>
+    <mergeCell ref="B207:F207"/>
+    <mergeCell ref="B198:F198"/>
+    <mergeCell ref="A218:F218"/>
+    <mergeCell ref="B296:F296"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A242:F242"/>
+    <mergeCell ref="A313:F313"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="A244:F244"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A371:F371"/>
+    <mergeCell ref="A342:F342"/>
+    <mergeCell ref="A231:F231"/>
+    <mergeCell ref="A165:F165"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="B349:F349"/>
+    <mergeCell ref="A344:F344"/>
+    <mergeCell ref="A229:F229"/>
+    <mergeCell ref="B364:F364"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="B222:F222"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B248:F248"/>
+    <mergeCell ref="A219:F219"/>
+    <mergeCell ref="B297:F297"/>
+    <mergeCell ref="B235:F235"/>
+    <mergeCell ref="B362:F362"/>
+    <mergeCell ref="B337:F337"/>
+    <mergeCell ref="B312:F312"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="B376:F376"/>
+    <mergeCell ref="B339:F339"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="A187:F187"/>
+    <mergeCell ref="A174:F174"/>
     <mergeCell ref="A205:F205"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B200:F200"/>
-    <mergeCell ref="A84:F84"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B252:F252"/>
-    <mergeCell ref="B209:F209"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="A133:F133"/>
+    <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B365:F365"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B292:F292"/>
+    <mergeCell ref="A189:F189"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B236:F236"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B307:F307"/>
+    <mergeCell ref="B223:F223"/>
+    <mergeCell ref="B294:F294"/>
+    <mergeCell ref="B350:F350"/>
+    <mergeCell ref="B195:F195"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="A200:F200"/>
+    <mergeCell ref="A357:F357"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A258:F258"/>
+    <mergeCell ref="A329:F329"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="A358:F358"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B213:F213"/>
+    <mergeCell ref="B378:F378"/>
+    <mergeCell ref="B305:F305"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B386:F386"/>
+    <mergeCell ref="B208:F208"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="B210:F210"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A240:F240"/>
+    <mergeCell ref="A215:F215"/>
+    <mergeCell ref="A190:F190"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B308:F308"/>
+    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B360:F360"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B239:F239"/>
+    <mergeCell ref="B372:F372"/>
+    <mergeCell ref="B310:F310"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B374:F374"/>
+    <mergeCell ref="B361:F361"/>
+    <mergeCell ref="A379:F379"/>
+    <mergeCell ref="A268:F268"/>
+    <mergeCell ref="B232:F232"/>
+    <mergeCell ref="B321:F321"/>
+    <mergeCell ref="A139:F139"/>
+    <mergeCell ref="A272:F272"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B263:F263"/>
+    <mergeCell ref="B323:F323"/>
+    <mergeCell ref="A203:F203"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B145:F145"/>
+    <mergeCell ref="B387:F387"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B245:F245"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="B260:F260"/>
+    <mergeCell ref="A287:F287"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="A256:F256"/>
+    <mergeCell ref="B334:F334"/>
+    <mergeCell ref="A354:F354"/>
+    <mergeCell ref="B309:F309"/>
+    <mergeCell ref="A345:F345"/>
+    <mergeCell ref="A316:F316"/>
+    <mergeCell ref="B336:F336"/>
+    <mergeCell ref="A356:F356"/>
+    <mergeCell ref="B311:F311"/>
+    <mergeCell ref="A380:F380"/>
+    <mergeCell ref="B377:F377"/>
+    <mergeCell ref="A382:F382"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B266:F266"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B197:F197"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B324:F324"/>
     <mergeCell ref="B261:F261"/>
-    <mergeCell ref="A50:F50"/>
     <mergeCell ref="B184:F184"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B236:F236"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B223:F223"/>
-    <mergeCell ref="B238:F238"/>
-    <mergeCell ref="B195:F195"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B253:F253"/>
-    <mergeCell ref="A144:F144"/>
-    <mergeCell ref="B231:F231"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A134:F134"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="A301:F301"/>
+    <mergeCell ref="A393:F393"/>
+    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A331:F331"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A303:F303"/>
+    <mergeCell ref="B179:F179"/>
     <mergeCell ref="B250:F250"/>
-    <mergeCell ref="A121:F121"/>
-    <mergeCell ref="B234:F234"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B116:F116"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="A202:F202"/>
-    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B166:F166"/>
+    <mergeCell ref="A332:F332"/>
+    <mergeCell ref="A288:F288"/>
+    <mergeCell ref="B352:F352"/>
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A258:F258"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B279:F279"/>
+    <mergeCell ref="B168:F168"/>
+    <mergeCell ref="B143:F143"/>
     <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="A73:F73"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="A226:F226"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="B281:F281"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="A241:F241"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B213:F213"/>
-    <mergeCell ref="B265:F265"/>
-    <mergeCell ref="B160:F160"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="B135:F135"/>
-    <mergeCell ref="B233:F233"/>
-    <mergeCell ref="A243:F243"/>
-    <mergeCell ref="B224:F224"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B125:F125"/>
-    <mergeCell ref="B185:F185"/>
-    <mergeCell ref="B199:F199"/>
-    <mergeCell ref="B208:F208"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="B121:F121"/>
     <mergeCell ref="A214:F214"/>
-    <mergeCell ref="A101:F101"/>
-    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="A285:F285"/>
+    <mergeCell ref="A341:F341"/>
     <mergeCell ref="B96:F96"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B105:F105"/>
-    <mergeCell ref="A204:F204"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B176:F176"/>
-    <mergeCell ref="B219:F219"/>
-    <mergeCell ref="A269:F269"/>
-    <mergeCell ref="B210:F210"/>
-    <mergeCell ref="B120:F120"/>
-    <mergeCell ref="A259:F259"/>
+    <mergeCell ref="B167:F167"/>
+    <mergeCell ref="B111:F111"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="A141:F141"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A240:F240"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B175:F175"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="B148:F148"/>
-    <mergeCell ref="A190:F190"/>
-    <mergeCell ref="B162:F162"/>
     <mergeCell ref="B267:F267"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="B171:F171"/>
     <mergeCell ref="A230:F230"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="A167:F167"/>
-    <mergeCell ref="B99:F99"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A114:F114"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B239:F239"/>
-    <mergeCell ref="B254:F254"/>
-    <mergeCell ref="A216:F216"/>
-    <mergeCell ref="A191:F191"/>
-    <mergeCell ref="A178:F178"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B207:F207"/>
-    <mergeCell ref="B76:F76"/>
-    <mergeCell ref="B189:F189"/>
+    <mergeCell ref="B251:F251"/>
     <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B251:F251"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B198:F198"/>
-    <mergeCell ref="A153:F153"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B188:F188"/>
     <mergeCell ref="A227:F227"/>
-    <mergeCell ref="B126:F126"/>
-    <mergeCell ref="B75:F75"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="A177:F177"/>
     <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B218:F218"/>
-    <mergeCell ref="A268:F268"/>
-    <mergeCell ref="A217:F217"/>
-    <mergeCell ref="B232:F232"/>
+    <mergeCell ref="B280:F280"/>
+    <mergeCell ref="B351:F351"/>
     <mergeCell ref="A164:F164"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B193:F193"/>
+    <mergeCell ref="B295:F295"/>
     <mergeCell ref="B46:F46"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="B263:F263"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="A181:F181"/>
-    <mergeCell ref="B136:F136"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="A131:F131"/>
-    <mergeCell ref="B145:F145"/>
-    <mergeCell ref="A244:F244"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="A165:F165"/>
-    <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="B249:F249"/>
-    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B282:F282"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A253:F253"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="A299:F299"/>
     <mergeCell ref="A93:F93"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B245:F245"/>
-    <mergeCell ref="A229:F229"/>
-    <mergeCell ref="A111:F111"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="A143:F143"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="B260:F260"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A328:F328"/>
     <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A103:F103"/>
-    <mergeCell ref="B222:F222"/>
-    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="B335:F335"/>
     <mergeCell ref="B212:F212"/>
-    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B206:F206"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B221:F221"/>
-    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B326:F326"/>
+    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="B130:F130"/>
+    <mergeCell ref="B353:F353"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B290:F290"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="B196:F196"/>
+    <mergeCell ref="B283:F283"/>
+    <mergeCell ref="B348:F348"/>
+    <mergeCell ref="A201:F201"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A367:F367"/>
     <mergeCell ref="B237:F237"/>
-    <mergeCell ref="A256:F256"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B100:F100"/>
-    <mergeCell ref="A193:F193"/>
-    <mergeCell ref="A255:F255"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B264:F264"/>
-    <mergeCell ref="B220:F220"/>
-    <mergeCell ref="A104:F104"/>
-    <mergeCell ref="B247:F247"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="B130:F130"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="B117:F117"/>
-    <mergeCell ref="B248:F248"/>
-    <mergeCell ref="B262:F262"/>
-    <mergeCell ref="B151:F151"/>
-    <mergeCell ref="A194:F194"/>
-    <mergeCell ref="B235:F235"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="A156:F156"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B196:F196"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="A155:F155"/>
-    <mergeCell ref="B246:F246"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="A201:F201"/>
-    <mergeCell ref="B211:F211"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="A123:F123"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B266:F266"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B197:F197"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5194,7 +7619,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>확인 항목</t>
         </is>
@@ -5206,95 +7631,95 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>오늘 지사 매출·재원·출석 지표를 확인했나요?</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr"/>
+      <c r="C4" s="41" t="inlineStr"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>부진한 대리점을 파악하고 지원했나요?</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr"/>
+      <c r="C5" s="44" t="inlineStr"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>이번 달 정산(수령·배분)을 점검했나요?</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr"/>
+      <c r="C6" s="41" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>미납·환불 건을 확인했나요?</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr"/>
+      <c r="C7" s="44" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>이탈위험 학생·대리점을 챙겼나요?</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr"/>
+      <c r="C8" s="41" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>신규 대리점 온보딩을 진행했나요?</t>
         </is>
       </c>
-      <c r="C9" s="42" t="inlineStr"/>
+      <c r="C9" s="44" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>월간 리포트를 공유했나요?</t>
         </is>
       </c>
-      <c r="C10" s="39" t="inlineStr"/>
+      <c r="C10" s="41" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5325,19 +7750,19 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>질문 (Q)</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>답변 (A)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>어디서 접속하나요?</t>
         </is>
@@ -5349,7 +7774,7 @@
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>다른 지사 데이터도 보이나요?</t>
         </is>
@@ -5361,7 +7786,7 @@
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>정산은 어떻게 계산되나요?</t>
         </is>
@@ -5373,7 +7798,7 @@
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>대리점 성과가 부진해요.</t>
         </is>
@@ -5385,7 +7810,7 @@
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>시스템 문제가 생겼어요.</t>
         </is>
@@ -5425,120 +7850,120 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="inlineStr">
+      <c r="A3" s="47" t="inlineStr">
         <is>
           <t>대리점별 재원생(예시)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B4" s="46" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>강남점</t>
         </is>
       </c>
-      <c r="B5" s="48" t="n">
+      <c r="B5" s="50" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>분당점</t>
         </is>
       </c>
-      <c r="B6" s="48" t="n">
+      <c r="B6" s="50" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>일산점</t>
         </is>
       </c>
-      <c r="B7" s="48" t="n">
+      <c r="B7" s="50" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="49" t="inlineStr">
         <is>
           <t>수원점</t>
         </is>
       </c>
-      <c r="B8" s="48" t="n">
+      <c r="B8" s="50" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>인천점</t>
         </is>
       </c>
-      <c r="B9" s="48" t="n">
+      <c r="B9" s="50" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>정산 흐름(예시 비중)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="49" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B13" s="49" t="inlineStr">
+      <c r="B13" s="51" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="49" t="inlineStr">
         <is>
           <t>본사 수수료</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="29" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>지사 몫</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="29" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="A16" s="49" t="inlineStr">
         <is>
           <t>대리점 배분</t>
         </is>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="29" t="n">
         <v>50</v>
       </c>
     </row>
@@ -5565,21 +7990,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="50" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>🏁 마무리 · 지사 성장을 위한 실천 가이드</t>
         </is>
       </c>
     </row>
     <row r="2" ht="54" customHeight="1">
-      <c r="A2" s="51" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>지사의 역할은 본사와 대리점을 잇는 다리예요. 우리 지사 지표를 챙기고, 산하 대리점이 잘 크도록 지원하며, 정산을 투명하게 처리하면 지사 전체가 함께 성장합니다. 이 리듬만 지켜도 운영이 훨씬 안정적이에요.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>🔄 하루 흐름 한눈에</t>
         </is>
@@ -5587,67 +8012,67 @@
       <c r="B4" s="22" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>아침 (5분)</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>지사 대시보드에서 매출·재원·출석 확인, AI 인사이트로 상태 파악</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>오전</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>대리점별 성과·수납 점검, 미납·환불 확인</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>오후</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>부진 대리점 지원·코칭, 이탈위험 학생 케어(리텐션)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>주간</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>신규 대리점 온보딩, 우수 사례 공유</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>월간</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>본사→지사→대리점 정산 확인·배포, 월간 리포트 공유</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="53" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t>⭐ 핵심 원칙</t>
         </is>
@@ -5655,113 +8080,113 @@
       <c r="B11" s="2" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="27" t="n">
+      <c r="A12" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>지표는 매일 아침 5분 — 지사·대리점 이상 신호를 빨리 잡아요.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>대리점을 파트너로 — 성과 편차를 코칭·지원으로 좁혀요.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>정산은 투명하게 — 기준을 미리 공지하면 신뢰가 쌓여요.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>이탈은 조기 개입 — 위험 대리점·학생을 먼저 챙겨요.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>우수 사례를 확산 — 잘하는 대리점 방식을 전체로 공유해요.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="54" t="inlineStr">
+      <c r="A18" s="56" t="inlineStr">
         <is>
           <t>📌 꼭 기억하세요</t>
         </is>
       </c>
-      <c r="B18" s="55" t="n"/>
+      <c r="B18" s="57" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="56" t="inlineStr">
+      <c r="A19" s="58" t="inlineStr">
         <is>
           <t>📌</t>
         </is>
       </c>
-      <c r="B19" s="57" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>접속은 admin.mangoi.co.kr, 데이터는 우리 지사 범위로 자동 한정돼요</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="56" t="inlineStr">
+      <c r="A20" s="58" t="inlineStr">
         <is>
           <t>📌</t>
         </is>
       </c>
-      <c r="B20" s="57" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>정산은 본사→지사→대리점 트리 구조로 자동 계산돼요</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="56" t="inlineStr">
+      <c r="A21" s="58" t="inlineStr">
         <is>
           <t>📌</t>
         </is>
       </c>
-      <c r="B21" s="57" t="inlineStr">
+      <c r="B21" s="59" t="inlineStr">
         <is>
           <t>‘입장 안 됨’ 등 현장 문의의 대부분은 브라우저·권한 문제예요</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="56" t="inlineStr">
+      <c r="A22" s="58" t="inlineStr">
         <is>
           <t>📌</t>
         </is>
       </c>
-      <c r="B22" s="57" t="inlineStr">
+      <c r="B22" s="59" t="inlineStr">
         <is>
           <t>운영 리듬은 ‘점검 → 지원 → 정산 → 리포트’!</t>
         </is>
       </c>
     </row>
     <row r="24" ht="66" customHeight="1">
-      <c r="A24" s="58" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>🍊 좋은 지사는 대리점이 잘되게 돕는 지사예요. 지표로 상황을 읽고, 파트너를 지원하고, 정산을 투명하게 하면 지사와 대리점이 함께 성장합니다. 궁금한 점은 언제든 본사 고객센터로 — 든든한 지사 운영을 응원합니다! 🍊</t>
         </is>
